--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -4500,37 +4500,37 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の継続を困難にしている要因の把握。第2章第5節（在宅生活の課題）、第5章基本目標2（在宅生活の支援）の根拠。代表KPI H06（在宅生活継続の支援）の基準値。</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
+          <t>在宅生活の継続を困難にしている要因の把握。第2章第5節（在宅生活の課題）、第5章基本目標2（在宅生活の支援）の根拠。代表KPI H06（在宅生活継続困難割合）の基準値。</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>一部受領</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>契約締結後に貸与される予定。現時点では第9期計画の記載を暫定的に引用しており、本文では［要確認］としている。</t>
+          <t>第9期計画に掲載された令和5年5月25日実施分（居宅介護支援事業所12事業所・91人）を再整理し、図表集12シートに結果概要としてまとめた（要介護度別内訳を含む）。第10期分の調査票・回答データ・集計資料は未受領のため、クロス集計とH06の基準値の算定ができない。</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -4550,37 +4550,37 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>在宅から施設・住まいへの移行の実態把握。第2章第6節（住まいと施設）、第6章第2節（施設・居住系の見込量）の根拠。代表KPI H11（住み慣れた地域での生活の継続）の基準値。</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
+          <t>在宅から施設・住まいへの移行の実態把握。第2章第6節（住まいと施設）、第6章第2節（施設・居住系の見込量）の根拠。代表KPI H11（供給不足を理由とする住替え割合）の基準値。</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>一部受領</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>契約締結後に貸与される予定。介護老人福祉施設の定員が234人から160人へ減少しており、移行先の実態把握が第6章の見込量算定に直結する。</t>
+          <t>第9期計画に掲載された令和5年5月25日実施分（施設・居住系21施設回答）を再整理し、図表集11シートに結果概要としてまとめた（退居・退所者の居所変更／死亡の別を含む）。第10期分は未受領。介護老人福祉施設の定員が234人から160人へ減少しており、移行先の実態把握が第6章の見込量算定に直結する。</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -4603,34 +4603,34 @@
           <t>介護人材の確保・定着の実態把握。第2章第7節（介護人材）、第5章基本目標4（人材の確保）の根拠。代表KPI H13・H14（人材の確保と定着）の基準値。</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>一部受領</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>契約締結後に貸与される予定。北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と年間の採用者数・退職者数を要する。</t>
+          <t>第9期計画に掲載された令和5年5月25日実施分（施設系35事業所中27施設回答・回収率77.1％・該当職員405人）を再整理し、図表集13シートにまとめた。第10期分は未受領。北海道の評価指標⑥と同じ「採用率と離職率の差」（H14）の算定には、各年9月30日現在の在籍者数と年間の採用者数・退職者数を要する。</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -4651,42 +4651,42 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>高齢者の健康状態、社会参加、生活支援ニーズの把握。第2章第4節（高齢者の状況）、第5章基本目標1（介護予防・社会参加）の根拠。代表KPI H01〜H05（介護予防と社会参加）の基準値。</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>高齢者の健康状態、社会参加、生活支援ニーズの把握。第2章第4節（高齢者の状況）、第5章基本目標1（介護予防・社会参加）の根拠。代表KPI H04（フレイル該当割合）・H05（社会参加率）の基準値。</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>契約締結後に貸与される予定。JAGESは全国共通様式のため、全国平均・他自治体との比較が可能であり、比較対象の指定を要する。</t>
+          <t>令和7年11月17日〜12月8日実施分を受領済（65歳以上7,121人対象・回収4,798票・回収率67.4％・集計4,729票）。20指標について年齢階級別（広域連合）及び町別の集計を行い、図表集08シート（データ）・09シート（グラフ）に整理、素案の図8・図8-2として掲載した。H04＝19.1％（R7）、H05の基準値を確定済み。属性を掛け合わせた追加のクロス集計には個票データ（Excel・CSV）を要する。</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>3, 8, 9</t>
+          <t>8, 9</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr"/>
     </row>
-    <row r="17" ht="28" customHeight="1">
+    <row r="17" ht="39" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）現時点では4調査とも資料を受領していないため、計画素案の該当箇所は第9期計画の記載又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
+          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は受領済であり、20指標を年齢階級別及び町別に集計して素案及び図表集に反映している。他の3調査は第9期計画に掲載された令和5年調査分を再整理した段階であり、第10期分の調査票・回答データ・集計資料は未受領である。このため計画素案の該当箇所は令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1124,7 +1124,8 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>図表集 08〜13シート
+          <t>調査クロス集計・分析（13シート）
+図表集 08〜13シート
 妥当性検証報告書 11シート
 素案第10稿 第2章第4〜6節</t>
         </is>
@@ -1135,7 +1136,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -1144,7 +1145,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>第10期分の在宅生活改善調査・居所変更実態調査・介護人材実態調査の確定集計が未受領（確認No.8）。健康とくらしの調査（令和7年度）は受領・分析済み。4調査を横断したクロス集計は資料受領後に実施</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了し、小学校区12地区別の集計、年齢調整による地域比較、社会参加・世帯構成・経済状況・移動制約との関連分析を行った（作業項目①⑥完了）。第10期分の在宅生活改善調査・居所変更実態調査・介護人材実態調査が未受領のため、②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -4039,7 +4040,8 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx（33シート133点）
+          <t>第10期計画_調査クロス集計・分析.xlsx（13シート）
+第10期計画_図表集_白黒.xlsx（33シート133点）
 第10期計画_妥当性検証報告書.xlsx（24シート）
 第10期計画_追加調査報告書.xlsx（8シート）
 第10期計画_施策体系新旧対照表.xlsx（5シート）
@@ -4058,7 +4060,7 @@
         </is>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -4067,7 +4069,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>①推計資料（人口推計・サービス見込量・保険料算定）が未作成。②クロス集計表は4調査のデータ受領後に作成する。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
+          <t>①推計資料（人口推計・サービス見込量・保険料算定）が未作成。②クロス集計表は健康とくらしの調査分を作成済み。他の3調査分は第10期データの受領後に作成する。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -4666,27 +4668,27 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>令和7年11月17日〜12月8日実施分を受領済（65歳以上7,121人対象・回収4,798票・回収率67.4％・集計4,729票）。20指標について年齢階級別（広域連合）及び町別の集計を行い、図表集08シート（データ）・09シート（グラフ）に整理、素案の図8・図8-2として掲載した。H04＝19.1％（R7）、H05の基準値を確定済み。属性を掛け合わせた追加のクロス集計には個票データ（Excel・CSV）を要する。</t>
+          <t>令和7年11月17日〜12月8日実施分の個票データ4,729票を受領済（65歳以上7,121人対象・回収4,798票・回収率67.4％）。20指標の年齢階級別・町別集計に加え、小学校区12地区別の集計、年齢調整による地域比較、社会参加・世帯構成・経済状況・移動制約・在宅生活の課題との関連分析を実施し、調査クロス集計・分析（13シート）として取りまとめた。H04＝19.1％、H05の基準値を確定。大雪独自設問によりH06・H07・H08・H11の代替データ源を特定した（確認No.4）。計画素案への反映は次稿で行う。</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>8, 9</t>
+          <t>4, 8, 9</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4839,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は受領済であり、20指標を年齢階級別及び町別に集計して素案及び図表集に反映している。他の3調査は第9期計画に掲載された令和5年調査分を再整理した段階であり、第10期分の調査票・回答データ・集計資料は未受領である。このため計画素案の該当箇所は令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
+          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は第9期計画に掲載された令和5年調査分を再整理した段階であり、第10期分の調査票・回答データ・集計資料は未受領である。このため計画素案の該当箇所は令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1115,6 +1115,7 @@
       <c r="D7" s="5" t="inlineStr">
         <is>
           <t>①健康とくらしの調査（JAGES）の集計・分析
+①-2 第9期の課題・第10期の施策に対する妥当性レビューと追加分析
 ②在宅生活改善調査の集計・分析
 ③居所変更実態調査の集計・分析
 ④介護人材実態調査の集計・分析
@@ -1136,7 +1137,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -1145,12 +1146,12 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了し、小学校区12地区別の集計、年齢調整による地域比較、社会参加・世帯構成・経済状況・移動制約との関連分析を行った（作業項目①⑥完了）。第10期分の在宅生活改善調査・居所変更実態調査・介護人材実態調査が未受領のため、②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全19シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。第10期分の3調査が未受領のため②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>8, 9, 10</t>
+          <t>4, 8, 9, 10, 27, 28</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2526,7 +2527,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査に事業所実態調査・在宅介護実態調査が含まれておらず、「新たなアンケート調査の企画、設計、配布、回収、入力及び督促は行わない」とされている。一方、代表KPIのH07・H08・H12・H16はこれらをデータ源としている。①発注者が実施する、②代理指標へ振り替える、③指標から外す、のいずれかの決定を要する。</t>
+          <t>仕様書４（3）の対象4調査に事業所実態調査・在宅介護実態調査が含まれておらず、「新たなアンケート調査の企画、設計、配布、回収、入力及び督促は行わない」とされている。一方、代表KPIのH07・H08・H12・H16はこれらをデータ源としている。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。H12・H16は事業所側の情報を要するため算定できない。①発注者が実施する、②代理指標へ振り替える、③指標から外す、のいずれかの決定を要する。</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2901,13 +2902,14 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。</t>
+          <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
-圏域別分析資料</t>
+圏域別分析資料
+調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3583,72 +3585,128 @@
       </c>
       <c r="J30" s="11" t="inlineStr"/>
     </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>調査クロス集計・分析 14シート
+素案 第2章第4節</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>調査対象者の範囲の確認</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>調査クロス集計・分析 13・14シート
+H06・H11の基準値</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B33" s="4">
-        <f>COUNTIF(H5:H30,"完了")</f>
-        <v/>
-      </c>
-      <c r="C33" s="5" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B34" s="4">
-        <f>COUNTIF(H5:H30,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
       <c r="B35" s="4">
-        <f>COUNTIF(H5:H30,"確認待ち")</f>
+        <f>COUNTIF(H5:H32,"完了")</f>
         <v/>
       </c>
       <c r="C35" s="5" t="inlineStr"/>
@@ -3661,13 +3719,13 @@
       <c r="J35" s="5" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B36" s="4">
-        <f>COUNTIF(H5:H30,"未着手")</f>
+        <f>COUNTIF(H5:H32,"実施中")</f>
         <v/>
       </c>
       <c r="C36" s="5" t="inlineStr"/>
@@ -3680,13 +3738,13 @@
       <c r="J36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B37" s="4">
-        <f>COUNTIF(H5:H30,"対象外")</f>
+        <f>COUNTIF(H5:H32,"確認待ち")</f>
         <v/>
       </c>
       <c r="C37" s="5" t="inlineStr"/>
@@ -3698,72 +3756,72 @@
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
     </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B38" s="4">
+        <f>COUNTIF(H5:H32,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C38" s="5" t="inlineStr"/>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B39" s="4">
+        <f>COUNTIF(H5:H32,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B40" s="4">
-        <f>COUNTIF(G5:G30,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="B41" s="4">
-        <f>COUNTIF(G5:G30,"発注者・3町")</f>
-        <v/>
-      </c>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B42" s="4">
-        <f>COUNTIF(G5:G30,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G32,"発注者")</f>
         <v/>
       </c>
       <c r="C42" s="5" t="inlineStr"/>
@@ -3778,11 +3836,11 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B43" s="4">
-        <f>COUNTIF(G5:G30,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G32,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C43" s="5" t="inlineStr"/>
@@ -3797,11 +3855,11 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B44" s="4">
-        <f>COUNTIF(G5:G30,"北海道")</f>
+        <f>COUNTIF(G5:G32,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C44" s="5" t="inlineStr"/>
@@ -3813,8 +3871,46 @@
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
     </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="B45" s="4">
+        <f>COUNTIF(G5:G32,"発注者・3町・北海道")</f>
+        <v/>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B46" s="4">
+        <f>COUNTIF(G5:G32,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -3823,10 +3919,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A48:J48"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H30">
+  <conditionalFormatting sqref="H5:H32">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -3844,7 +3940,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全19シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。第10期分の3調査が未受領のため②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全19シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。第10期分の3調査が未受領のため②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>4, 8, 9, 10, 27, 28</t>
+          <t>3, 4, 8, 9, 10, 27, 28</t>
         </is>
       </c>
     </row>
@@ -1188,6 +1188,7 @@
         <is>
           <t>妥当性検証報告書 03〜06・13・14・21・22シート
 図表集 01〜31シート
+調査クロス集計・分析 01・02・19〜21シート
 素案第10稿 第2章</t>
         </is>
       </c>
@@ -1197,7 +1198,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -1206,9 +1207,9 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>①類似保険者との比較が未実施（見える化のδ3系列が提供不可。選定条件の決定が必要。確認No.3）
-②構成町別の分析は令和5年までの前回計画掲載値による。令和6〜8年の町別データが未受領（確認No.11）
-③日常生活圏域別の分析が未実施（圏域別データが未受領。確認No.12）</t>
+          <t>⑥類似保険者との比較は、健康とくらしの調査の同規模保険者40との比較により住民の状態・社会参加の領域を実施済み。給付・供給面は見える化のδ3系列が提供不可のため比較対象の選定条件の決定を要する（確認No.3）
+⑦構成町別の分析は、健康とくらしの調査により3町別の20指標を整理済み。人口・世帯は令和5年までの前回計画掲載値による。令和6〜8年の町別データが未受領（確認No.11）
+⑧日常生活圏域別の分析は、健康とくらしの調査の小学校区12地区別集計により着手済み。小学校区と6圏域の対応関係及び圏域別の給付データが未受領（確認No.12）</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -2480,7 +2481,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
+          <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>5, 6, 7, 23</t>
+          <t>5, 6, 7, 23, 32</t>
         </is>
       </c>
     </row>
@@ -1249,6 +1249,7 @@
         <is>
           <t>素案第10稿 第6章
 追加調査報告書 06シート
+保険料と施策評価の他団体比較（9シート）
 推計資料（見える化の総括表）</t>
         </is>
       </c>
@@ -1258,7 +1259,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1272,7 +1273,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>14, 15, 16</t>
+          <t>14, 15, 16, 29, 30, 31</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3680,110 +3681,222 @@
       </c>
       <c r="J32" s="11" t="inlineStr"/>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>重度化の速度の前提</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第1節
+認定者数・給付費の推計</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>重度化の速度の前提
+保険料と施策評価の他団体比較 05シート</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>給付適正化の実施予定と推計での扱い</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第2節・第5章・第7章
+給付費の推計</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>第7期の保険料基準額</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>見える化システムの値は6,077円であるが、計画素案の第9稿までは5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第6節
+保険料の推移</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B35" s="4">
-        <f>COUNTIF(H5:H32,"完了")</f>
-        <v/>
-      </c>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B36" s="4">
-        <f>COUNTIF(H5:H32,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="B37" s="4">
-        <f>COUNTIF(H5:H32,"確認待ち")</f>
-        <v/>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="B38" s="4">
-        <f>COUNTIF(H5:H32,"未着手")</f>
-        <v/>
-      </c>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
       <c r="B39" s="4">
-        <f>COUNTIF(H5:H32,"対象外")</f>
+        <f>COUNTIF(H5:H36,"完了")</f>
         <v/>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
@@ -3795,34 +3908,52 @@
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="B40" s="4">
+        <f>COUNTIF(H5:H36,"実施中")</f>
+        <v/>
+      </c>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="B41" s="4">
+        <f>COUNTIF(H5:H36,"確認待ち")</f>
+        <v/>
+      </c>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B42" s="4">
-        <f>COUNTIF(G5:G32,"発注者")</f>
+        <f>COUNTIF(H5:H36,"未着手")</f>
         <v/>
       </c>
       <c r="C42" s="5" t="inlineStr"/>
@@ -3835,13 +3966,13 @@
       <c r="J42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
         </is>
       </c>
       <c r="B43" s="4">
-        <f>COUNTIF(G5:G32,"発注者・3町")</f>
+        <f>COUNTIF(H5:H36,"対象外")</f>
         <v/>
       </c>
       <c r="C43" s="5" t="inlineStr"/>
@@ -3853,52 +3984,34 @@
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="B44" s="4">
-        <f>COUNTIF(G5:G32,"発注者・北海道")</f>
-        <v/>
-      </c>
-      <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町・北海道</t>
-        </is>
-      </c>
-      <c r="B45" s="4">
-        <f>COUNTIF(G5:G32,"発注者・3町・北海道")</f>
-        <v/>
-      </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B46" s="4">
-        <f>COUNTIF(G5:G32,"北海道")</f>
+        <f>COUNTIF(G5:G36,"発注者")</f>
         <v/>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
@@ -3910,8 +4023,84 @@
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
     </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="B47" s="4">
+        <f>COUNTIF(G5:G36,"発注者・3町")</f>
+        <v/>
+      </c>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="B48" s="4">
+        <f>COUNTIF(G5:G36,"発注者・北海道")</f>
+        <v/>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="B49" s="4">
+        <f>COUNTIF(G5:G36,"発注者・3町・北海道")</f>
+        <v/>
+      </c>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B50" s="4">
+        <f>COUNTIF(G5:G36,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -3919,11 +4108,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A48:J48"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H32">
+  <conditionalFormatting sqref="H5:H36">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -3941,7 +4130,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4137,7 +4326,8 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx（13シート）
+          <t>第10期計画_調査クロス集計・分析.xlsx（22シート）
+第10期計画_保険料と施策評価の他団体比較.xlsx（9シート）
 第10期計画_図表集_白黒.xlsx（33シート133点）
 第10期計画_妥当性検証報告書.xlsx（24シート）
 第10期計画_追加調査報告書.xlsx（8シート）
@@ -4305,7 +4495,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>14, 15, 16</t>
+          <t>14, 15, 16, 29, 30, 31</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>5, 6, 7, 23, 32</t>
+          <t>5, 6, 7, 23, 32, 34</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>3, 11, 12, 13, 26</t>
+          <t>3, 11, 12, 13, 26, 35</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>14, 15, 16, 29, 30, 31</t>
+          <t>14, 15, 16, 29, 30, 31, 33, 36</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3869,110 +3869,222 @@
       </c>
       <c r="J36" s="11" t="inlineStr"/>
     </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>第10期の政令改正の内容（所得段階）</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>第10期の段階設計
+保険料の算定</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>国の情報</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>第9段階の乗率の経緯</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>第10期の段階設計
+保険料の所得段階と低所得者軽減の検証 08シート</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>所得段階別被保険者数の実績と収納率</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>所得段階別被保険者数の推計
+保険料の算定
+素案 第6章第7節</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B39" s="4">
-        <f>COUNTIF(H5:H36,"完了")</f>
-        <v/>
-      </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B40" s="4">
-        <f>COUNTIF(H5:H36,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="B41" s="4">
-        <f>COUNTIF(H5:H36,"確認待ち")</f>
-        <v/>
-      </c>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="B42" s="4">
-        <f>COUNTIF(H5:H36,"未着手")</f>
-        <v/>
-      </c>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
       <c r="B43" s="4">
-        <f>COUNTIF(H5:H36,"対象外")</f>
+        <f>COUNTIF(H5:H40,"完了")</f>
         <v/>
       </c>
       <c r="C43" s="5" t="inlineStr"/>
@@ -3984,34 +4096,52 @@
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
     </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="B44" s="4">
+        <f>COUNTIF(H5:H40,"実施中")</f>
+        <v/>
+      </c>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="B45" s="4">
+        <f>COUNTIF(H5:H40,"確認待ち")</f>
+        <v/>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B46" s="4">
-        <f>COUNTIF(G5:G36,"発注者")</f>
+        <f>COUNTIF(H5:H40,"未着手")</f>
         <v/>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
@@ -4024,13 +4154,13 @@
       <c r="J46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
         </is>
       </c>
       <c r="B47" s="4">
-        <f>COUNTIF(G5:G36,"発注者・3町")</f>
+        <f>COUNTIF(H5:H40,"対象外")</f>
         <v/>
       </c>
       <c r="C47" s="5" t="inlineStr"/>
@@ -4042,52 +4172,34 @@
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="B48" s="4">
-        <f>COUNTIF(G5:G36,"発注者・北海道")</f>
-        <v/>
-      </c>
-      <c r="C48" s="5" t="inlineStr"/>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町・北海道</t>
-        </is>
-      </c>
-      <c r="B49" s="4">
-        <f>COUNTIF(G5:G36,"発注者・3町・北海道")</f>
-        <v/>
-      </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B50" s="4">
-        <f>COUNTIF(G5:G36,"北海道")</f>
+        <f>COUNTIF(G5:G40,"発注者")</f>
         <v/>
       </c>
       <c r="C50" s="5" t="inlineStr"/>
@@ -4099,8 +4211,84 @@
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="B51" s="4">
+        <f>COUNTIF(G5:G40,"発注者・3町")</f>
+        <v/>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="B52" s="4">
+        <f>COUNTIF(G5:G40,"発注者・北海道")</f>
+        <v/>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="B53" s="4">
+        <f>COUNTIF(G5:G40,"発注者・3町・北海道")</f>
+        <v/>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B54" s="4">
+        <f>COUNTIF(G5:G40,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -4108,11 +4296,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A56:J56"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H36">
+  <conditionalFormatting sqref="H5:H40">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4130,7 +4318,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4328,6 +4516,7 @@
         <is>
           <t>第10期計画_調査クロス集計・分析.xlsx（22シート）
 第10期計画_保険料と施策評価の他団体比較.xlsx（9シート）
+第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx（10シート）
 第10期計画_図表集_白黒.xlsx（33シート133点）
 第10期計画_妥当性検証報告書.xlsx（24シート）
 第10期計画_追加調査報告書.xlsx（8シート）
@@ -4495,7 +4684,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>14, 15, 16, 29, 30, 31</t>
+          <t>14, 15, 16, 29, 30, 31, 33, 36</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析（13シート）
+          <t>調査クロス集計・分析（22シート）
 図表集 08〜13シート
 妥当性検証報告書 11シート
 素案第10稿 第2章第4〜6節</t>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全19シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。第10期分の3調査が未受領のため②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全22シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。第10期分の3調査が未受領のため②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1062,14 +1062,16 @@
 ③保険者機能強化推進交付金等による外部評価の分析
 ④給付実績の分析（受給率・利用率・サービス別給付動向）
 ⑤地域支援事業の実績整理
-⑥令和6〜8年度の事業実績による達成度の再判定</t>
+⑥令和6〜8年度の事業実績による達成度の再判定
+⑦評価そのもののレッドチームレビュー（指摘18件）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>妥当性検証報告書 01・02・12・23シート
 素案第10稿 第3章
-施策体系新旧対照表</t>
+施策体系新旧対照表
+第9期評価のレッドチームレビュー（8シート）</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -1078,7 +1080,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -1087,12 +1089,12 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する</t>
+          <t>レッドチームレビューの結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>5, 6, 7, 23, 32, 34</t>
+          <t>5, 6, 7, 23, 32, 34, 37, 38</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1127,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析（22シート）
+          <t>調査クロス集計・分析（24シート）
 図表集 08〜13シート
 妥当性検証報告書 11シート
 素案第10稿 第2章第4〜6節</t>
@@ -1146,7 +1148,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全22シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。第10期分の3調査が未受領のため②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。第10期分の3調査が未受領のため②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -2287,7 +2289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4057,72 +4059,128 @@
       </c>
       <c r="J40" s="11" t="inlineStr"/>
     </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>年齢階級別・要介護度別の認定率</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（レッドチームレビュー No.1）。</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>素案 第3章第4節
+妥当性検証 所見7</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（レッドチームレビュー No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>素案 第3章第4節
+妥当性検証 所見18・19</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B43" s="4">
-        <f>COUNTIF(H5:H40,"完了")</f>
-        <v/>
-      </c>
-      <c r="C43" s="5" t="inlineStr"/>
-      <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B44" s="4">
-        <f>COUNTIF(H5:H40,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
       <c r="B45" s="4">
-        <f>COUNTIF(H5:H40,"確認待ち")</f>
+        <f>COUNTIF(H5:H42,"完了")</f>
         <v/>
       </c>
       <c r="C45" s="5" t="inlineStr"/>
@@ -4135,13 +4193,13 @@
       <c r="J45" s="5" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B46" s="4">
-        <f>COUNTIF(H5:H40,"未着手")</f>
+        <f>COUNTIF(H5:H42,"実施中")</f>
         <v/>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
@@ -4154,13 +4212,13 @@
       <c r="J46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B47" s="4">
-        <f>COUNTIF(H5:H40,"対象外")</f>
+        <f>COUNTIF(H5:H42,"確認待ち")</f>
         <v/>
       </c>
       <c r="C47" s="5" t="inlineStr"/>
@@ -4172,72 +4230,72 @@
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
     </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B48" s="4">
+        <f>COUNTIF(H5:H42,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B49" s="4">
+        <f>COUNTIF(H5:H42,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B50" s="4">
-        <f>COUNTIF(G5:G40,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="B51" s="4">
-        <f>COUNTIF(G5:G40,"発注者・3町")</f>
-        <v/>
-      </c>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B52" s="4">
-        <f>COUNTIF(G5:G40,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G42,"発注者")</f>
         <v/>
       </c>
       <c r="C52" s="5" t="inlineStr"/>
@@ -4252,11 +4310,11 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B53" s="4">
-        <f>COUNTIF(G5:G40,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G42,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C53" s="5" t="inlineStr"/>
@@ -4271,11 +4329,11 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B54" s="4">
-        <f>COUNTIF(G5:G40,"北海道")</f>
+        <f>COUNTIF(G5:G42,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C54" s="5" t="inlineStr"/>
@@ -4287,8 +4345,46 @@
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
     </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="B55" s="4">
+        <f>COUNTIF(G5:G42,"発注者・3町・北海道")</f>
+        <v/>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B56" s="4">
+        <f>COUNTIF(G5:G42,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -4296,11 +4392,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A58:J58"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A56:J56"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H40">
+  <conditionalFormatting sqref="H5:H42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4318,7 +4414,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4514,9 +4610,10 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx（22シート）
+          <t>第10期計画_調査クロス集計・分析.xlsx（24シート）
 第10期計画_保険料と施策評価の他団体比較.xlsx（9シート）
 第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx（10シート）
+第10期計画_第9期評価のレッドチームレビュー.xlsx（8シート）
 第10期計画_図表集_白黒.xlsx（33シート133点）
 第10期計画_妥当性検証報告書.xlsx（24シート）
 第10期計画_追加調査報告書.xlsx（8シート）

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1063,7 +1063,8 @@
 ④給付実績の分析（受給率・利用率・サービス別給付動向）
 ⑤地域支援事業の実績整理
 ⑥令和6〜8年度の事業実績による達成度の再判定
-⑦評価そのもののレッドチームレビュー（指摘18件）</t>
+⑦評価そのもののレッドチームレビュー（指摘18件）
+⑧レビュー指摘への対応（記述の修正16件・訂正1件）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1080,7 +1081,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -1089,7 +1090,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>レッドチームレビューの結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
+          <t>レッドチームレビューの指摘18件のうち、追加データを要しない16件への対応を完了した（記述の修正・表現の限定・注記の追加）。うちNo.5は指摘が的中し、「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見を「数値目標を設定しているのは東川町のみ」に訂正した。残る2件（人口推計の検証・保険者の自己評価）は資料の受領を要する。レッドチームレビューの結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -4613,7 +4614,7 @@
           <t>第10期計画_調査クロス集計・分析.xlsx（24シート）
 第10期計画_保険料と施策評価の他団体比較.xlsx（9シート）
 第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx（10シート）
-第10期計画_第9期評価のレッドチームレビュー.xlsx（8シート）
+第10期計画_第9期評価のレッドチームレビュー.xlsx（9シート）
 第10期計画_図表集_白黒.xlsx（33シート133点）
 第10期計画_妥当性検証報告書.xlsx（24シート）
 第10期計画_追加調査報告書.xlsx（8シート）

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>レッドチームレビューの指摘18件のうち、追加データを要しない16件への対応を完了した（記述の修正・表現の限定・注記の追加）。うちNo.5は指摘が的中し、「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見を「数値目標を設定しているのは東川町のみ」に訂正した。残る2件（人口推計の検証・保険者の自己評価）は資料の受領を要する。レッドチームレビューの結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
+          <t>レッドチームレビューの指摘18件のうち、追加データを要しない16件への対応を完了した（記述の修正・表現の限定・注記の追加）。うち2件（No.5・No.1）は指摘が的中し、評価の記述を訂正した。No.5は「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見を「数値目標を設定しているのは東川町のみ」に訂正。No.1は見える化B4・B5・B6系列の受領により年齢調整分析を実施し、従来の説明「軽度は改善・中重度は悪化」が逆であることが判明したため撤回した（認定率の年齢調整分析 7シート）。残る2件（人口推計の検証・保険者の自己評価）は資料の受領を要する。レッドチームレビューの結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -4095,9 +4095,9 @@
           <t>発注者</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -4105,7 +4105,11 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="88" customHeight="1">
       <c r="A42" s="4" t="n">
@@ -4615,6 +4619,7 @@
 第10期計画_保険料と施策評価の他団体比較.xlsx（9シート）
 第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx（10シート）
 第10期計画_第9期評価のレッドチームレビュー.xlsx（9シート）
+第10期計画_認定率の年齢調整分析.xlsx（7シート）
 第10期計画_図表集_白黒.xlsx（33シート133点）
 第10期計画_妥当性検証報告書.xlsx（24シート）
 第10期計画_追加調査報告書.xlsx（8シート）

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_確認事項一覧" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_成果品管理" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_調査別の状況" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_資料提供依頼一覧" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -100,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -122,11 +123,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,6 +231,11 @@
     <xf numFmtId="9" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -593,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -762,134 +812,158 @@
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr"/>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>06_資料提供依頼一覧</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>成果物の主張を確定するために提供を要する資料15件を、領域別・優先度別に管理する。03シートが「決定」を求めるのに対し、本シートは「資料の提供」を求めるものである。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>受託者が随時追加。状態欄は受領時に更新</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>色</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>当該項目の作業が終わり、成果物を提出済み又は提出可能な状態にある</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>着手しているが完了していない</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>受託者の作業は終わっており、発注者・3町・北海道からの回答又は資料の提供を待っている</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr"/>
+          <t>着手しているが完了していない</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>工程上まだ着手していない、又は前提条件が整っていない</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr"/>
+          <t>受託者の作業は終わっており、発注者・3町・北海道からの回答又は資料の提供を待っている</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>本業務の範囲外、又は該当がない</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr"/>
+          <t>工程上まだ着手していない、又は前提条件が整っていない</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
     </row>
-    <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>本業務の範囲外、又は該当がない</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="39" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>【本表の位置づけ】計画素案（第10稿）の本文には、確認事項や作業上の留意点を注記として書き込まない方針とする。本文の注記は、計画の読み手（住民・委員・関係機関）が計画を理解するために必要なものに限り、受託者と発注者の間の作業管理に関する事項は本表で管理する。確定していない数値は、本文では［要協議］［要確認］［要内訳］として空欄扱いのまま残し、その解消に必要な作業と確認事項は本表03シートで管理する。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>【段階承認について】仕様書５は「受託者は各工程終了後、発注者が指定する期日までに成果物を提出し、発注者の確認を受けた上で次工程へ進むものとする」と定めている。02シートの「発注者確認」欄は、この段階承認を記録するためのものである。確認日と確認者を記入いただくことで、次工程への移行が可能となる。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。</t>
+    <row r="23" ht="78" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘26件）、主張の根拠水準の棚卸しと再レビュー（8シート）を作成した。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5526,4 +5600,996 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>資料提供依頼一覧（15件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>成果物の主張を確定するために提供を要する資料を一覧化する。03シートの確認事項が発注者・3町・北海道の「決定」を求めるものであるのに対し、本シートは「資料の提供」を求めるものである。根拠及び各資料が確定する主張は、「主張の根拠水準の棚卸しと再レビュー」06シートに対応する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>領域</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>資料</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>確定する主張</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>入手先</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>希望時期</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>第9期のプロセス評価（事業が計画どおり実施されたか）に必要。現時点で最大の空白。</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>第9期の評価の完成</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.1と対応。仕様書４（2）が完了しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>調査票、回答データ、集計資料、分析資料、報告書。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.8・9と対応。仕様書４（3）が完了しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>訪問・通所困難地域の判定</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>北海道・広域連合</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.15と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>3町</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.11と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.6・38と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>区域内事業所による給付の割合（自給率）を算定し、給付水準の高さが区域内の供給によるものか区域外利用によるものかを判別する。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>給付水準の要因、区域外利用の有無</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>発注者・国保連</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.30と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>第6章の見込量算定に直結</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.23と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>第9期の剰余額（現在は概算）</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.16と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>第10期の段階設計と保険料算定</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>国の情報</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>国の告示を待つ。受託者が随時確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>第7期（平成30〜令和2年度）の保険料条例</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>基準額が6,077円か5,900円かを確定する。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>第7期の保険料基準額</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.32と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>小学校区と日常生活圏域の対応関係</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>圏域別の分析、圏域設定の見直し</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町・3町</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.20と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>評価の枠組みの整理</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.7と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>受託者側で出力を試行する</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>高齢者単身世帯・夫婦世帯の最新値。公表され次第。</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>世帯構成の現状</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>総務省・3町</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>公表後</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>公表待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.14 在宅生活改善調査・居所変更実態調査・介護人材</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.15 第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="23" t="n"/>
+    </row>
+    <row r="27" ht="39" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査の第10期分）は、いずれも業務内容そのものが進まない資料である。No.13がなければ仕様書４（2）のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の8件は、いずれも成果物の主張の根拠を推論・仮説から算定又は確認に引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する手段である。注3）本シートは令和8年7月29日の主張の棚卸し（全成果物46主張のMECEな分類）に基づく。各資料が確定する主張の詳細は、「主張の根拠水準の棚卸しと再レビュー」01・06シートに示している。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="C23:J23"/>
+  </mergeCells>
+  <conditionalFormatting sqref="I5:I19">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"完了"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"実施中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"確認待ち"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"未着手"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"対象外"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="I5:I19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -825,7 +825,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>成果物の主張を確定するために提供を要する資料15件を、領域別・優先度別に管理する。03シートが「決定」を求めるのに対し、本シートは「資料の提供」を求めるものである。</t>
+          <t>成果物の主張を確定するために提供を要する資料を、領域別・優先度別に管理する。03シートが「決定」を求めるのに対し、本シートは「資料の提供」を求めるものである。</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -3934,9 +3934,9 @@
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -3944,7 +3944,11 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="88" customHeight="1">
       <c r="A37" s="4" t="n">
@@ -5608,7 +5612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5626,7 +5630,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料提供依頼一覧（15件）</t>
+          <t>資料提供依頼一覧（18件）</t>
         </is>
       </c>
     </row>
@@ -5950,17 +5954,17 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>区域内事業所による給付の割合（自給率）を算定し、給付水準の高さが区域内の供給によるものか区域外利用によるものかを判別する。</t>
+          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>給付水準の要因、区域外利用の有無</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -5980,12 +5984,12 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.30と対応</t>
+          <t>確認事項No.30と対応。No.17・No.18に分割</t>
         </is>
       </c>
     </row>
@@ -6191,41 +6195,41 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>第7期（平成30〜令和2年度）の保険料条例</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>基準額が6,077円か5,900円かを確定する。</t>
+          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>第7期の保険料基準額</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -6235,47 +6239,47 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.32と対応</t>
+          <t>自給率（δ）は受領済（R8.7.30）。金額換算に必要</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
+          <t>区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>区域外利用の内訳</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -6285,32 +6289,32 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.20と対応</t>
+          <t>依頼No.6の残る部分。自給率では所在地が分からない</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>第7期（平成30〜令和2年度）の保険料条例</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
+          <t>基準額が6,077円か5,900円かを確定する。</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>第7期の保険料基準額</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -6330,42 +6334,42 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.7と対応</t>
+          <t>見える化C1により6,077円を確認（R8.7.30）。依頼は解消</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -6373,166 +6377,250 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>受託者側で出力を試行する</t>
+          <t>確認事項No.20と対応</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>評価の枠組みの整理</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.7と対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>見える化システムD49の指標定義</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>地域差指数の分解の可否</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>見える化システム・厚生労働省</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>受託者側で確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>受託者側で出力を試行する</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。公表され次第。</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>公表待ち</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>最高</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.14 在宅生活改善調査・居所変更実態調査・介護人材</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="22" t="n"/>
-      <c r="F22" s="22" t="n"/>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="22" t="n"/>
-      <c r="I22" s="22" t="n"/>
-      <c r="J22" s="23" t="n"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="22" t="n"/>
-      <c r="I23" s="22" t="n"/>
-      <c r="J23" s="23" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.15 第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="22" t="n"/>
-      <c r="I24" s="22" t="n"/>
-      <c r="J24" s="23" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
       <c r="B25" s="21" t="n">
@@ -6540,7 +6628,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.14 在宅生活改善調査・居所変更実態調査・介護人材</t>
         </is>
       </c>
       <c r="D25" s="22" t="n"/>
@@ -6551,24 +6639,90 @@
       <c r="I25" s="22" t="n"/>
       <c r="J25" s="23" t="n"/>
     </row>
-    <row r="27" ht="39" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査の第10期分）は、いずれも業務内容そのものが進まない資料である。No.13がなければ仕様書４（2）のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の8件は、いずれも成果物の主張の根拠を推論・仮説から算定又は確認に引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する手段である。注3）本シートは令和8年7月29日の主張の棚卸し（全成果物46主張のMECEな分類）に基づく。各資料が確定する主張の詳細は、「主張の根拠水準の棚卸しと再レビュー」01・06シートに示している。</t>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="23" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.15 第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="23" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="23" t="n"/>
+    </row>
+    <row r="30" ht="39" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査の第10期分）は、いずれも業務内容そのものが進まない資料である。No.13がなければ仕様書４（2）のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の資料は、いずれも成果物の主張の根拠を推論・仮説から算定又は確認に引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する手段である。注3）本シートは令和8年7月29日の主張の棚卸し（全成果物46主張のMECEな分類）に基づく。各資料が確定する主張の詳細は、「主張の根拠水準の棚卸しと再レビュー」01・06シートに示している。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="C26:J26"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="C25:J25"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C27:J27"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="C23:J23"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I19">
+  <conditionalFormatting sqref="I5:I22">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -6586,7 +6740,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -950,10 +950,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="78" customHeight="1">
+    <row r="23" ht="91" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘26件）、主張の根拠水準の棚卸しと再レビュー（8シート）を作成した。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
+          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）を作成した。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,9 @@
 ④給付実績の分析（受給率・利用率・サービス別給付動向）
 ⑤地域支援事業の実績整理
 ⑥令和6〜8年度の事業実績による達成度の再判定
-⑦評価そのもののレッドチームレビュー（指摘18件）
+⑦評価そのもののレッドチームレビュー（指摘29件）
+⑧全成果物の主張の棚卸し（54主張・根拠水準5階層）
+⑨地域差の分析（自給率・地域差指数・保険料の管内比較）
 ⑧レビュー指摘への対応（記述の修正16件・訂正1件）</t>
         </is>
       </c>
@@ -1164,7 +1166,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>レッドチームレビューの指摘18件のうち、追加データを要しない16件への対応を完了した（記述の修正・表現の限定・注記の追加）。うち2件（No.5・No.1）は指摘が的中し、評価の記述を訂正した。No.5は「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見を「数値目標を設定しているのは東川町のみ」に訂正。No.1は見える化B4・B5・B6系列の受領により年齢調整分析を実施し、従来の説明「軽度は改善・中重度は悪化」が逆であることが判明したため撤回した（認定率の年齢調整分析 7シート）。残る2件（人口推計の検証・保険者の自己評価）は資料の受領を要する。レッドチームレビューの結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
+          <t>レッドチームレビューの指摘29件のうち、記述の修正により対応できる22件への対応を進めた（記述の修正・表現の限定・注記の追加）。うち2件（No.5・No.1）は指摘が的中し、評価の記述を訂正した。No.5は「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見を「数値目標を設定しているのは東川町のみ」に訂正。No.1は見える化B4・B5・B6系列の受領により年齢調整分析を実施し、従来の説明「軽度は改善・中重度は悪化」が逆であることが判明したため撤回した（認定率の年齢調整分析 7シート）。残る2件（人口推計の検証・保険者の自己評価）は資料の受領を要する。レッドチームレビューの結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1381,7 +1383,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>素案第10稿（565段落98表34図）
+          <t>素案第10稿（542段落97表34図）
 修正指示書（66件）</t>
         </is>
       </c>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -953,7 +953,7 @@
     <row r="23" ht="91" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）を作成した。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
+          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）を作成した。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
         </is>
       </c>
     </row>
@@ -1140,6 +1140,7 @@
 ⑦評価そのもののレッドチームレビュー（指摘29件）
 ⑧全成果物の主張の棚卸し（54主張・根拠水準5階層）
 ⑨地域差の分析（自給率・地域差指数・保険料の管内比較）
+⑩人口推計の基礎の検証（見える化A系列 2000〜2050年）
 ⑧レビュー指摘への対応（記述の修正16件・訂正1件）</t>
         </is>
       </c>
@@ -1334,11 +1335,11 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1347,7 +1348,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>自然体推計の構造と補正手順は整理済み（追加調査報告書06シート）。令和6〜8年度の実績確定後に着手する。総人口・被保険者数を社人研推計とするか3町の総合計画等による推計に差し替えるかの決定が必要（確認No.14）</t>
+          <t>自然体推計の構造と補正手順は整理済み（追加調査報告書06シート）。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、基礎データの整理を完了した（人口推計の基礎の検証9シート）。第10期期間中は65歳以上人口がほぼ横ばい（▲0.1％）で、増えるのは80〜84歳と85歳以上のみであることを確認した。総人口・被保険者数を社人研推計とするか3町の総合計画等による推計に差し替えるかの決定（確認No.14）と、令和6〜8年度の実績確定を待って推計に着手する</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -953,7 +953,7 @@
     <row r="23" ht="91" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）を作成した。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
+          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）を作成した。人口推計の基礎は社人研推計とすることが令和8年7月30日に決定した。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
         </is>
       </c>
     </row>
@@ -1141,6 +1141,7 @@
 ⑧全成果物の主張の棚卸し（54主張・根拠水準5階層）
 ⑨地域差の分析（自給率・地域差指数・保険料の管内比較）
 ⑩人口推計の基礎の検証（見える化A系列 2000〜2050年）
+⑪将来推計 第1段階（人口と認定者数・3シナリオ）
 ⑧レビュー指摘への対応（記述の修正16件・訂正1件）</t>
         </is>
       </c>
@@ -1339,7 +1340,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1348,7 +1349,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>自然体推計の構造と補正手順は整理済み（追加調査報告書06シート）。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、基礎データの整理を完了した（人口推計の基礎の検証9シート）。第10期期間中は65歳以上人口がほぼ横ばい（▲0.1％）で、増えるのは80〜84歳と85歳以上のみであることを確認した。総人口・被保険者数を社人研推計とするか3町の総合計画等による推計に差し替えるかの決定（確認No.14）と、令和6〜8年度の実績確定を待って推計に着手する</t>
+          <t>令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎を社人研推計とすることが決定した（同日）。第1段階（人口と認定者数）を完了し、将来推計（8シート）として取りまとめた。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、要介護度別認定者数の受領（資料依頼No.19）と認定率のシナリオの決定を待って着手する</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -5615,7 +5616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5633,7 +5634,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料提供依頼一覧（18件）</t>
+          <t>資料提供依頼一覧（19件）</t>
         </is>
       </c>
     </row>
@@ -5798,41 +5799,41 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域</t>
+          <t>要介護度別認定者数の実績（令和元年〜令和8年度・各年3月末）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。</t>
+          <t>要支援1・2、要介護1〜5の別。サービス見込量は要介護度別の利用率により算定する。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定</t>
+          <t>将来推計の第2段階（サービス見込量）</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北海道・広域連合</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>最高</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -5842,42 +5843,42 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.15と対応</t>
+          <t>認定者数の合計は将来推計01〜04シートで推計済み</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
+          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>訪問・通所困難地域の判定</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>北海道・広域連合</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -5892,37 +5893,37 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.11と対応</t>
+          <t>確認事項No.15と対応</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
+          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -5942,42 +5943,42 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.6・38と対応</t>
+          <t>確認事項No.11と対応</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
+          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -5987,42 +5988,42 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.30と対応。No.17・No.18に分割</t>
+          <t>確認事項No.6・38と対応</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
+          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -6037,42 +6038,42 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>第6章の見込量算定に直結</t>
+          <t>確認事項No.30と対応。No.17・No.18に分割</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
+          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -6092,32 +6093,32 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.23と対応</t>
+          <t>第6章の見込量算定に直結</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
+          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -6142,13 +6143,13 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.16と対応</t>
+          <t>確認事項No.23と対応</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
@@ -6157,27 +6158,27 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
+          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -6187,47 +6188,47 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>国の告示を待つ。受託者が随時確認する</t>
+          <t>確認事項No.16と対応</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
+          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -6237,37 +6238,37 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>自給率（δ）は受領済（R8.7.30）。金額換算に必要</t>
+          <t>国の告示を待つ。受託者が随時確認する</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地）</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。</t>
+          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>区域外利用の内訳</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -6292,87 +6293,87 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>依頼No.6の残る部分。自給率では所在地が分からない</t>
+          <t>自給率（δ）は受領済（R8.7.30）。金額換算に必要</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>第7期（平成30〜令和2年度）の保険料条例</t>
+          <t>指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>基準額が6,077円か5,900円かを確定する。</t>
+          <t>区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>第7期の保険料基準額</t>
+          <t>区域外利用の内訳</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>見える化C1により6,077円を確認（R8.7.30）。依頼は解消</t>
+          <t>依頼No.6の残る部分。自給率では所在地が分からない</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第7期（平成30〜令和2年度）の保険料条例</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
+          <t>基準額が6,077円か5,900円かを確定する。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>第7期の保険料基準額</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -6387,42 +6388,42 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.20と対応</t>
+          <t>見える化C1により6,077円を確認（R8.7.30）。依頼は解消</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -6442,42 +6443,42 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.7と対応</t>
+          <t>確認事項No.20と対応</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
+          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -6487,52 +6488,52 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>受託者側で確認する</t>
+          <t>確認事項No.7と対応</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>見える化システムD49の指標定義</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>地域差指数の分解の可否</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>見える化システム・厚生労働省</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -6542,118 +6543,146 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>受託者側で出力を試行する</t>
+          <t>受託者側で確認する</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>受託者側で出力を試行する</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。公表され次第。</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>公表待ち</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.14 在宅生活改善調査・居所変更実態調査・介護人材</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="22" t="n"/>
-      <c r="J25" s="23" t="n"/>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="B26" s="21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）</t>
+          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.19 要介護度別認定者数の実績（令和元年〜令和8年</t>
         </is>
       </c>
       <c r="D26" s="22" t="n"/>
@@ -6665,17 +6694,17 @@
       <c r="J26" s="23" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B27" s="21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.15 第9期の自己評価と北海道への報告の実績</t>
+          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D27" s="22" t="n"/>
@@ -6687,17 +6716,17 @@
       <c r="J27" s="23" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="B28" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.15 第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D28" s="22" t="n"/>
@@ -6708,8 +6737,30 @@
       <c r="I28" s="22" t="n"/>
       <c r="J28" s="23" t="n"/>
     </row>
-    <row r="30" ht="39" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="23" t="n"/>
+    </row>
+    <row r="31" ht="39" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査の第10期分）は、いずれも業務内容そのものが進まない資料である。No.13がなければ仕様書４（2）のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の資料は、いずれも成果物の主張の根拠を推論・仮説から算定又は確認に引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する手段である。注3）本シートは令和8年7月29日の主張の棚卸し（全成果物46主張のMECEな分類）に基づく。各資料が確定する主張の詳細は、「主張の根拠水準の棚卸しと再レビュー」01・06シートに示している。</t>
         </is>
@@ -6719,13 +6770,13 @@
   <mergeCells count="7">
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="C28:J28"/>
     <mergeCell ref="C27:J27"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I22">
+  <conditionalFormatting sqref="I5:I23">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -6743,7 +6794,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -5616,7 +5616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5634,7 +5634,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料提供依頼一覧（19件）</t>
+          <t>資料提供依頼一覧（20件）</t>
         </is>
       </c>
     </row>
@@ -6549,162 +6549,190 @@
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>―</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料第3稿の自己点検で、12件中5件がこの類であった。</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>会議資料・委員会資料の記述の正確性</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>受託者側で出力を試行する</t>
+          <t>キックオフ資料の点検結果05シートに手順を記録</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>受託者側で出力を試行する</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。公表され次第。</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>公表待ち</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B27" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.19 要介護度別認定者数の実績（令和元年〜令和8年</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="22" t="n"/>
-      <c r="I26" s="22" t="n"/>
-      <c r="J26" s="23" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D27" s="22" t="n"/>
@@ -6716,17 +6744,17 @@
       <c r="J27" s="23" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B28" s="21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.15 第9期の自己評価と北海道への報告の実績</t>
+          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D28" s="22" t="n"/>
@@ -6738,17 +6766,17 @@
       <c r="J28" s="23" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="B29" s="21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.20 （受託者の作業）会議資料・委員会資料の作成時、No.15 第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D29" s="22" t="n"/>
@@ -6759,8 +6787,30 @@
       <c r="I29" s="22" t="n"/>
       <c r="J29" s="23" t="n"/>
     </row>
-    <row r="31" ht="39" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="23" t="n"/>
+    </row>
+    <row r="32" ht="39" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査の第10期分）は、いずれも業務内容そのものが進まない資料である。No.13がなければ仕様書４（2）のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の資料は、いずれも成果物の主張の根拠を推論・仮説から算定又は確認に引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する手段である。注3）本シートは令和8年7月29日の主張の棚卸し（全成果物46主張のMECEな分類）に基づく。各資料が確定する主張の詳細は、「主張の根拠水準の棚卸しと再レビュー」01・06シートに示している。</t>
         </is>
@@ -6768,15 +6818,15 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C26:J26"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A32:J32"/>
     <mergeCell ref="C29:J29"/>
-    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="C30:J30"/>
     <mergeCell ref="C28:J28"/>
     <mergeCell ref="C27:J27"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I23">
+  <conditionalFormatting sqref="I5:I24">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -6794,7 +6844,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -950,10 +950,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="91" customHeight="1">
+    <row r="23" ht="104" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）を作成した。人口推計の基礎は社人研推計とすることが令和8年7月30日に決定した。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
+          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）を作成した。人口推計の基礎は、社人研推計をそのまま用いることを受託者の案とし、これを作業上の前提として仮に置いて試算している（キックオフ会議でご意向を確認する）。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎を社人研推計とすることが決定した（同日）。第1段階（人口と認定者数）を完了し、将来推計（8シート）として取りまとめた。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、要介護度別認定者数の受領（資料依頼No.19）と認定率のシナリオの決定を待って着手する</t>
+          <t>令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて第1段階（人口と認定者数）を試算し、将来推計（8シート）として取りまとめた（基礎の採用はキックオフ会議でご意向を確認する。確認No.14）。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、要介護度別認定者数の受領（資料依頼No.19）と認定率のシナリオの決定を待って着手する</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1227,7 +1227,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。第10期分の3調査が未受領のため②③④は令和5年調査分の再整理にとどまり、⑤4調査横断のクロス集計は未着手（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 10シート）。点検事項29件のうち重大3件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>JAGES調査は分析済み。他3調査は第10期分の確定集計が未受領。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
+          <t>4調査すべてを受領し集計済。3調査は点検事項29件の解消待ち。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1951,7 +1951,7 @@
       <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>3調査の確定集計の受領が前提。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
+          <t>3調査の点検事項の重大3件の解消が前提。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>3調査の確定集計</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査（第10期分）の調査票、回答データ（Excel、CSV等）、集計資料、分析資料及び報告書。仕様書４（3）は契約締結後に貸与するとしている。</t>
+          <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大3件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>一部受領</t>
+          <t>受領済</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>第9期計画に掲載された令和5年5月25日実施分（居宅介護支援事業所12事業所・91人）を再整理し、図表集12シートに結果概要としてまとめた（要介護度別内訳を含む）。第10期分の調査票・回答データ・集計資料は未受領のため、クロス集計とH06の基準値の算定ができない。</t>
+          <t>第9期計画に掲載された令和5年5月25日実施分（居宅介護支援事業所12事業所・91人）を再整理し、図表集12シートに結果概要としてまとめた（要介護度別内訳を含む）。令和8年8月4日に第10期分（事業所票15件・利用者票99票）を受領し集計した。利用者票の所在地区の記入形式が不統一であり地区別集計はできない。回答の36.4％が同一法人の小規模多機能2事業所からの提出である。</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>一部受領</t>
+          <t>受領済</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>第9期計画に掲載された令和5年5月25日実施分（施設・居住系21施設回答）を再整理し、図表集11シートに結果概要としてまとめた（退居・退所者の居所変更／死亡の別を含む）。第10期分は未受領。介護老人福祉施設の定員が234人から160人へ減少しており、移行先の実態把握が第6章の見込量算定に直結する。</t>
+          <t>第9期計画に掲載された令和5年5月25日実施分（施設・居住系21施設回答）を再整理し、図表集11シートに結果概要としてまとめた（退居・退所者の居所変更／死亡の別を含む）。令和8年8月4日に第10期分（施設等票18件・定員652人・入所者536人）を受領し集計した。新規入所335人の入所前の居場所は病院・診療所57.0％・自宅27.5％、退去349人の退去先は病院・診療所47.0％・死亡27.2％・自宅12.3％である。</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>一部受領</t>
+          <t>受領済</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>第9期計画に掲載された令和5年5月25日実施分（施設系35事業所中27施設回答・回収率77.1％・該当職員405人）を再整理し、図表集13シートにまとめた。第10期分は未受領。北海道の評価指標⑥と同じ「採用率と離職率の差」（H14）の算定には、各年9月30日現在の在籍者数と年間の採用者数・退職者数を要する。</t>
+          <t>第9期計画に掲載された令和5年5月25日実施分（施設系35事業所中27施設回答・回収率77.1％・該当職員405人）を再整理し、図表集13シートにまとめた。令和8年8月4日に第10期分（事業所票27件・職員個票317人・職員票26件）を受領し集計した。介護職員348人（重複を除く）、介護福祉士67.1％、勤続1年未満19.9％、外国人職員11.6％、令和6年度の採用83人・離職65人である。北海道の評価指標⑥と同じ「採用率と離職率の差」（H14）の算定には、各年9月30日現在の在籍者数を要するが、本調査は令和7年4月1日現在である。</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -5500,7 +5500,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は第9期計画に掲載された令和5年調査分を再整理した段階であり、第10期分の調査票・回答データ・集計資料は未受領である。このため計画素案の該当箇所は令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
+          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項29件のうち重大3件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
         </is>
       </c>
     </row>
@@ -5749,26 +5749,26 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+          <t>要介護度別認定者数の実績（令和元年〜令和8年度・各年3月末）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>調査票、回答データ、集計資料、分析資料、報告書。</t>
+          <t>要支援1・2、要介護1〜5の別。サービス見込量は要介護度別の利用率により算定する。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>将来推計の第2段階（サービス見込量）</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -5793,47 +5793,47 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.8・9と対応。仕様書４（3）が完了しない</t>
+          <t>認定者数の合計は将来推計01〜04シートで推計済み</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>要介護度別認定者数の実績（令和元年〜令和8年度・各年3月末）</t>
+          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>要支援1・2、要介護1〜5の別。サービス見込量は要介護度別の利用率により算定する。</t>
+          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>将来推計の第2段階（サービス見込量）</t>
+          <t>訪問・通所困難地域の判定</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道・広域連合</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>最高</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -5843,42 +5843,42 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>認定者数の合計は将来推計01〜04シートで推計済み</t>
+          <t>確認事項No.15と対応</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。</t>
+          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北海道・広域連合</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -5893,37 +5893,37 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.15と対応</t>
+          <t>確認事項No.11と対応</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
+          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -5943,42 +5943,42 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.11と対応</t>
+          <t>確認事項No.6・38と対応</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
+          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -5988,42 +5988,42 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.6・38と対応</t>
+          <t>確認事項No.30と対応。No.17・No.18に分割</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
+          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -6038,42 +6038,42 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.30と対応。No.17・No.18に分割</t>
+          <t>第6章の見込量算定に直結</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
+          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -6093,32 +6093,32 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>第6章の見込量算定に直結</t>
+          <t>確認事項No.23と対応</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
+          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -6143,13 +6143,13 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.23と対応</t>
+          <t>確認事項No.16と対応</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
@@ -6158,27 +6158,27 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
+          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -6188,47 +6188,47 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.16と対応</t>
+          <t>国の告示を待つ。受託者が随時確認する</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
+          <t>令和8年8月4日に102ファイルを受領。残るのは点検事項29件の解消。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>国の告示を待つ。受託者が随時確認する</t>
+          <t>確認事項No.8・9と対応。重大3件の取扱いが決まると着手できる</t>
         </is>
       </c>
     </row>
@@ -6728,11 +6728,11 @@
         </is>
       </c>
       <c r="B27" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.19 要介護度別認定者数の実績（令和元年〜令和8年</t>
+          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.19 要介護度別認定者数の実績（令和元年〜令和8年</t>
         </is>
       </c>
       <c r="D27" s="22" t="n"/>
@@ -6750,11 +6750,11 @@
         </is>
       </c>
       <c r="B28" s="21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）</t>
+          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D28" s="22" t="n"/>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1227,7 +1227,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 10シート）。点検事項29件のうち重大3件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 10シート）。点検事項31件のうち重大4件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>4調査すべてを受領し集計済。3調査は点検事項29件の解消待ち。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
+          <t>4調査すべてを受領し集計済。3調査は点検事項31件の解消待ち。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1951,7 +1951,7 @@
       <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>3調査の点検事項の重大3件の解消が前提。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
+          <t>3調査の点検事項の重大4件の解消が前提。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大3件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
+          <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大4件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -5500,7 +5500,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項29件のうち重大3件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
+          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項31件のうち重大4件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -664,7 +664,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。作成日：令和8年7月29日。</t>
+          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。作成日：令和8年8月4日。</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,8 @@
           <t>調査クロス集計・分析（24シート）
 図表集 08〜13シート
 妥当性検証報告書 11シート
-素案第10稿 第2章第4〜6節</t>
+素案第10稿 第2章第4〜6節
+実施済み3調査の受領点検と集計（11シート）</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -1218,7 +1219,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -1227,7 +1228,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 10シート）。点検事項31件のうち重大4件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。点検事項31件のうち重大4件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1270,7 +1271,8 @@
           <t>妥当性検証報告書 03〜06・13・14・21・22シート
 図表集 01〜31シート
 調査クロス集計・分析 01・02・19〜21シート
-素案第10稿 第2章</t>
+素案第10稿 第2章
+実施済み3調査の受領点検と集計 05・10シート</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -1279,7 +1281,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -1290,7 +1292,8 @@
         <is>
           <t>⑥類似保険者との比較は、健康とくらしの調査の同規模保険者40との比較により住民の状態・社会参加の領域を実施済み。給付・供給面は見える化のδ3系列が提供不可のため比較対象の選定条件の決定を要する（確認No.3）
 ⑦構成町別の分析は、健康とくらしの調査により3町別の20指標を整理済み。人口・世帯は令和5年までの前回計画掲載値による。令和6〜8年の町別データが未受領（確認No.11）
-⑧日常生活圏域別の分析は、健康とくらしの調査の小学校区12地区別集計により着手済み。小学校区と6圏域の対応関係及び圏域別の給付データが未受領（確認No.12）</t>
+⑧日常生活圏域別の分析は、健康とくらしの調査の小学校区12地区別集計により着手済み。小学校区と6圏域の対応関係及び圏域別の給付データが未受領（確認No.12）。在宅生活改善調査の利用者票は所在地区の記入形式が統一されておらず、地区別の集計に用いられない（3調査の点検 No.3）
+④サービス提供体制は、介護人材実態調査と見える化のK系列・M2系列の突合により従事者数の把握範囲を確定した（3調査の点検 10シート）</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1895,7 +1898,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>貸与資料の受領と整理は先行実施済み。第9期計画の評価・検証は妥当性検証報告書（24シート）として先行して取りまとめ済み。キックオフ会議の日程が未確定</t>
+          <t>貸与資料の受領と整理は先行実施済み。第9期計画の評価・検証は妥当性検証報告書（24シート）として先行して取りまとめ済み。令和8年8月4日に3調査の第10期分102ファイルを受領し、点検・集計・見える化との突合を完了した。キックオフ会議資料は第4稿。キックオフ会議の日程が未確定</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -1908,7 +1911,7 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>キックオフ会議で、①事業所実態調査の取扱い、②工程の前倒しの可否、③委員会日程を決定いただきたい</t>
+          <t>キックオフ会議で、①事業所実態調査の取扱い、②人口推計の基礎及び認定率のシナリオ、③3調査の点検事項の重大4件の取扱い、④委員会日程についてご意向を確認する</t>
         </is>
       </c>
     </row>
@@ -4706,6 +4709,11 @@
 第10期計画_妥当性検証報告書.xlsx（24シート）
 第10期計画_追加調査報告書.xlsx（8シート）
 第10期計画_施策体系新旧対照表.xlsx（5シート）
+第10期計画_地域差の分析.xlsx（15シート）
+第10期計画_人口推計の基礎の検証.xlsx（9シート）
+第10期計画_将来推計_人口と認定者数.xlsx（8シート）
+第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx（8シート）
+第10期計画_実施済み3調査の受領点検と集計.xlsx（11シート）
 figures/*.png（34点）</t>
         </is>
       </c>
@@ -4721,7 +4729,7 @@
         </is>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -4730,7 +4738,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>①推計資料（人口推計・サービス見込量・保険料算定）が未作成。②クロス集計表は健康とくらしの調査分を作成済み。他の3調査分は第10期データの受領後に作成する。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
+          <t>①推計資料は第1段階（人口・認定者数）を作成済み。第2段階（サービス見込量）・第3段階（給付費・保険料）が未作成。②クロス集計表は健康とくらしの調査分を作成済み。他の3調査は集計まで完了し、4調査横断のクロス集計は点検事項の重大4件の解消を待つ。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -4751,9 +4759,15 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx（第8版）
+          <t>第10期計画_確認依頼書.docx（第9版）
 第10期計画素案_第9稿→第10稿_修正指示書.xlsx（66件）
-第10期計画_業務工程管理表.xlsx（本表）</t>
+第10期計画_業務工程管理表.xlsx（本表）
+第10期計画_キックオフ会議資料_第4稿.docx（13章18表）
+第10期計画_キックオフ会議ヒアリングシート.docx（13項目）
+第10期計画_キックオフ資料の点検結果.xlsx（6シート）
+第10期計画_必要事項の一覧.xlsx（8シート）
+第10期計画_計画素案の別管理表.xlsx（6シート）
+第10期計画_成果品一覧.xlsx（4シート）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -4767,7 +4781,7 @@
         </is>
       </c>
       <c r="F8" s="20" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -4776,7 +4790,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>①キックオフ会議資料は日程確定後に作成する。②運営協議会等への資料原案は開催日程と審議事項の確定を要する。③パブリックコメント資料は実施期間の確定を要する。</t>
+          <t>①キックオフ会議資料は第4稿まで作成済み。会議日程が未確定。②運営協議会等への資料原案は開催日程と審議事項の確定を要する。③パブリックコメント資料は実施期間の確定を要する。</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて第1段階（人口と認定者数）を試算し、将来推計（8シート）として取りまとめた（基礎の採用はキックオフ会議でご意向を確認する。確認No.14）。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、要介護度別認定者数の受領（資料依頼No.19）と認定率のシナリオの決定を待って着手する</t>
+          <t>令和8年8月4日に見える化B3系列（要介護度別認定者数・平成19年3月末〜令和8年3月末）を受領し、第2段階の前提となる要介護度別の内訳が整った（要介護認定データの確認 01シート）。残るのはサービス種別・要介護度別の受給者数（資料依頼No.19）である。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて第1段階（人口と認定者数）を試算し、将来推計（8シート）として取りまとめた（基礎の採用はキックオフ会議でご意向を確認する。確認No.14）。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、要介護度別認定者数の受領（資料依頼No.19）と認定率のシナリオの決定を待って着手する</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>要介護度別認定者数の実績（令和元年〜令和8年度・各年3月末）</t>
+          <t>サービス種別・要介護度別の受給者数（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>要支援1・2、要介護1〜5の別。サービス見込量は要介護度別の利用率により算定する。</t>
+          <t>要介護度別認定者数は令和8年8月4日に見える化B3系列で受領した。残るのは利用率の分子となるサービス種別・要介護度別の受給者数である。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>認定者数の合計は将来推計01〜04シートで推計済み</t>
+          <t>要介護度別認定者数は受領済（要介護認定データの確認 01シート）。見える化D系列で代替できるかを確認中</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.19 要介護度別認定者数の実績（令和元年〜令和8年</t>
+          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.19 サービス種別・要介護度別の受給者数（令和4〜</t>
         </is>
       </c>
       <c r="D27" s="22" t="n"/>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>令和8年8月4日に見える化B3系列（要介護度別認定者数・平成19年3月末〜令和8年3月末）を受領し、第2段階の前提となる要介護度別の内訳が整った（要介護認定データの確認 01シート）。残るのはサービス種別・要介護度別の受給者数（資料依頼No.19）である。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて第1段階（人口と認定者数）を試算し、将来推計（8シート）として取りまとめた（基礎の採用はキックオフ会議でご意向を確認する。確認No.14）。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、要介護度別認定者数の受領（資料依頼No.19）と認定率のシナリオの決定を待って着手する</t>
+          <t>令和8年8月4日に見える化B3系列（要介護度別認定者数）及びD系列（受給者数・利用率・1人当たり利用日数）を受領し、第2段階の算定チェーン（認定者数×利用率×1人当たり利用日数）が閉じた。同チェーンにより令和7年度の実績を1％未満の差で再現できることを検証した（サービス受給者数データの確認 05シート）。残るのは、利用率と1人当たり利用日数の置き方のご意向の確認、居住系・施設の種別別受給者数、総合事業の実績である。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて第1段階（人口と認定者数）を試算し、将来推計（8シート）として取りまとめた（基礎の採用はキックオフ会議でご意向を確認する。確認No.14）。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、要介護度別認定者数の受領（資料依頼No.19）と認定率のシナリオの決定を待って着手する</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -5763,86 +5763,86 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>サービス種別・要介護度別の受給者数（令和4〜7年度）</t>
+          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>要介護度別認定者数は令和8年8月4日に見える化B3系列で受領した。残るのは利用率の分子となるサービス種別・要介護度別の受給者数である。</t>
+          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>将来推計の第2段階（サービス見込量）</t>
+          <t>訪問・通所困難地域の判定</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道・広域連合</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>最高</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>要介護度別認定者数は受領済（要介護認定データの確認 01シート）。見える化D系列で代替できるかを確認中</t>
+          <t>確認事項No.15と対応</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。</t>
+          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北海道・広域連合</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -5857,37 +5857,37 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.15と対応</t>
+          <t>確認事項No.11と対応</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
+          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -5907,42 +5907,42 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.11と対応</t>
+          <t>確認事項No.6・38と対応</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
+          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -5952,42 +5952,42 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.6・38と対応</t>
+          <t>確認事項No.30と対応。No.17・No.18に分割</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
+          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -6002,42 +6002,42 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.30と対応。No.17・No.18に分割</t>
+          <t>第6章の見込量算定に直結</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
+          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -6057,32 +6057,32 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>第6章の見込量算定に直結</t>
+          <t>確認事項No.23と対応</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
+          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -6107,13 +6107,13 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.23と対応</t>
+          <t>確認事項No.16と対応</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
@@ -6122,27 +6122,27 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
+          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -6152,47 +6152,47 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.16と対応</t>
+          <t>国の告示を待つ。受託者が随時確認する</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
+          <t>令和8年8月4日に102ファイルを受領。残るのは点検事項29件の解消。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -6202,47 +6202,47 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>国の告示を待つ。受託者が随時確認する</t>
+          <t>確認事項No.8・9と対応。重大3件の取扱いが決まると着手できる</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月4日に102ファイルを受領。残るのは点検事項29件の解消。</t>
+          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -6252,37 +6252,37 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.8・9と対応。重大3件の取扱いが決まると着手できる</t>
+          <t>自給率（δ）は受領済（R8.7.30）。金額換算に必要</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
+          <t>区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>区域外利用の内訳</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -6307,37 +6307,37 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>自給率（δ）は受領済（R8.7.30）。金額換算に必要</t>
+          <t>依頼No.6の残る部分。自給率では所在地が分からない</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。</t>
+          <t>第2段階の算定チェーンは見える化B3・D45・D46系列により閉じた。残るのは、グループホーム・特定施設等の種別別受給者数と介護予防・日常生活支援総合事業の実績である。</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>区域外利用の内訳</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>依頼No.6の残る部分。自給率では所在地が分からない</t>
+          <t>施設・居住系は定員により見込むため代替可能。総合事業は広域連合の実績によるほかない</t>
         </is>
       </c>
     </row>
@@ -6742,11 +6742,11 @@
         </is>
       </c>
       <c r="B27" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象、No.19 サービス種別・要介護度別の受給者数（令和4〜</t>
+          <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象</t>
         </is>
       </c>
       <c r="D27" s="22" t="n"/>
@@ -6764,11 +6764,11 @@
         </is>
       </c>
       <c r="B28" s="21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）</t>
+          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）、No.19 居住系・施設サービスの種別別受給者数と総合事</t>
         </is>
       </c>
       <c r="D28" s="22" t="n"/>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -950,10 +950,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="104" customHeight="1">
+    <row r="23" ht="117" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）を作成した。人口推計の基礎は、社人研推計をそのまま用いることを受託者の案とし、これを作業上の前提として仮に置いて試算している（キックオフ会議でご意向を確認する）。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
+          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）、将来推計 第2段階（8シート）、実施済み3調査の受領点検と集計（16シート）、要介護認定データの確認（7シート）、サービス受給者数データの確認（7シート）を作成した。人口推計の基礎は、社人研推計をそのまま用いることを受託者の案とし、これを作業上の前提として仮に置いて試算している（キックオフ会議でご意向を確認する）。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
         </is>
       </c>
     </row>
@@ -1142,6 +1142,7 @@
 ⑨地域差の分析（自給率・地域差指数・保険料の管内比較）
 ⑩人口推計の基礎の検証（見える化A系列 2000〜2050年）
 ⑪将来推計 第1段階（人口と認定者数・3シナリオ）
+⑫将来推計 第2段階（サービス見込量・感度分析）
 ⑧レビュー指摘への対応（記述の修正16件・訂正1件）</t>
         </is>
       </c>
@@ -1343,7 +1344,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1352,7 +1353,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>令和8年8月4日に見える化B3系列（要介護度別認定者数）及びD系列（受給者数・利用率・1人当たり利用日数）を受領し、第2段階の算定チェーン（認定者数×利用率×1人当たり利用日数）が閉じた。同チェーンにより令和7年度の実績を1％未満の差で再現できることを検証した（サービス受給者数データの確認 05シート）。残るのは、利用率と1人当たり利用日数の置き方のご意向の確認、居住系・施設の種別別受給者数、総合事業の実績である。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて第1段階（人口と認定者数）を試算し、将来推計（8シート）として取りまとめた（基礎の採用はキックオフ会議でご意向を確認する。確認No.14）。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、要介護度別認定者数の受領（資料依頼No.19）と認定率のシナリオの決定を待って着手する</t>
+          <t>令和8年8月4日に見える化B3系列（要介護度別認定者数）及びD系列（受給者数・利用率・1人当たり利用日数）を受領し、第2段階の算定チェーン（認定者数×利用率×1人当たり利用日数）が閉じた。同チェーンにより令和7年度の実績を1％未満の差で再現できることを検証した（サービス受給者数データの確認 05シート）。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて第1段階（人口と認定者数）を試算し、将来推計（8シート）として取りまとめた（基礎の採用はキックオフ会議でご意向を確認する。確認No.14）。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、利用率と1人当たり利用日数・回数を令和7年度の値で固定する案を基本とし、趨勢を見込む場合を感度分析として併記する形で試算し、将来推計 第2段階（8シート）として取りまとめた（置き方はヒアリングシート項目6でご意向を確認する）。残るのは、居住系・施設の種別別受給者数、総合事業の実績、及び第3段階（給付費・保険料）である</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1984,12 +1985,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>地域課題の整理は先行実施済み（妥当性検証報告書 主要所見20件）。骨子案は計画素案（第10稿）に統合して先行作成済み。将来推計は未着手</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>地域課題の整理は先行実施済み（妥当性検証報告書 主要所見20件）。骨子案は計画素案（第10稿）に統合して先行作成済み。将来推計は第1段階（人口と認定者数）・第2段階（サービス見込量）を先行して試算済み。第3段階（給付費・保険料）が未着手</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -4712,8 +4713,11 @@
 第10期計画_地域差の分析.xlsx（15シート）
 第10期計画_人口推計の基礎の検証.xlsx（9シート）
 第10期計画_将来推計_人口と認定者数.xlsx（8シート）
+第10期計画_将来推計_第2段階_サービス見込量.xlsx（8シート）
 第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx（8シート）
-第10期計画_実施済み3調査の受領点検と集計.xlsx（11シート）
+第10期計画_実施済み3調査の受領点検と集計.xlsx（16シート）
+第10期計画_要介護認定データの確認.xlsx（7シート）
+第10期計画_サービス受給者数データの確認.xlsx（7シート）
 figures/*.png（34点）</t>
         </is>
       </c>
@@ -4729,7 +4733,7 @@
         </is>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -4738,7 +4742,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>①推計資料は第1段階（人口・認定者数）を作成済み。第2段階（サービス見込量）・第3段階（給付費・保険料）が未作成。②クロス集計表は健康とくらしの調査分を作成済み。他の3調査は集計まで完了し、4調査横断のクロス集計は点検事項の重大4件の解消を待つ。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
+          <t>①推計資料は第1段階（人口・認定者数）と第2段階（サービス見込量）を作成済み。第3段階（給付費・保険料）が未作成。②クロス集計表は健康とくらしの調査分を作成済み。他の3調査は集計まで完了し、4調査横断のクロス集計は点検事項の重大4件の解消を待つ。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -6357,7 +6361,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>施設・居住系は定員により見込むため代替可能。総合事業は広域連合の実績によるほかない</t>
+          <t>施設・居住系は定員により見込むため代替可能（将来推計 第2段階 06シートで区域内定員と突合済み）。総合事業は広域連合の実績によるほかない</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。点検事項31件のうち重大4件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であることを確認し、将来推計 第2段階06シートを訂正した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1912,7 +1912,7 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>キックオフ会議で、①事業所実態調査の取扱い、②人口推計の基礎及び認定率のシナリオ、③3調査の点検事項の重大4件の取扱い、④委員会日程についてご意向を確認する</t>
+          <t>キックオフ会議で、①事業所実態調査の取扱い、②人口推計の基礎及び認定率のシナリオ、③3調査の点検事項の重大5件の取扱い、④委員会日程についてご意向を確認する</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>4調査すべてを受領し集計済。3調査は点検事項31件の解消待ち。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
+          <t>4調査すべてを受領し集計済。3調査は点検事項32件の解消待ち。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1955,7 +1955,7 @@
       <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>3調査の点検事項の重大4件の解消が前提。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
+          <t>3調査の点検事項の重大5件の解消が前提。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大4件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
+          <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大5件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>①推計資料は第1段階（人口・認定者数）と第2段階（サービス見込量）を作成済み。第3段階（給付費・保険料）が未作成。②クロス集計表は健康とくらしの調査分を作成済み。他の3調査は集計まで完了し、4調査横断のクロス集計は点検事項の重大4件の解消を待つ。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
+          <t>①推計資料は第1段階（人口・認定者数）と第2段階（サービス見込量）を作成済み。第3段階（給付費・保険料）が未作成。②クロス集計表は健康とくらしの調査分を作成済み。他の3調査は集計まで完了し、4調査横断のクロス集計は点検事項の重大5件の解消を待つ。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -5518,7 +5518,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項31件のうち重大4件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
+          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項32件のうち重大5件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であることを確認し、将来推計 第2段階06シートを訂正した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -3037,23 +3037,24 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」（居宅サービスは北海道、地域密着型は広域連合が保有）、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。</t>
+          <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
-追加調査報告書 03シート</t>
+追加調査報告書 03シート
+住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -5767,36 +5768,36 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。</t>
+          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北海道・広域連合</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -5811,37 +5812,37 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.15と対応</t>
+          <t>確認事項No.11と対応</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
+          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -5861,42 +5862,42 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.11と対応</t>
+          <t>確認事項No.6・38と対応</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
+          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -5906,42 +5907,42 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.6・38と対応</t>
+          <t>確認事項No.30と対応。No.17・No.18に分割</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
+          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -5956,42 +5957,42 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.30と対応。No.17・No.18に分割</t>
+          <t>第6章の見込量算定に直結</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
+          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -6011,32 +6012,32 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>第6章の見込量算定に直結</t>
+          <t>確認事項No.23と対応</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
+          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -6061,13 +6062,13 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.23と対応</t>
+          <t>確認事項No.16と対応</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -6076,27 +6077,27 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
+          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -6106,47 +6107,47 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.16と対応</t>
+          <t>国の告示を待つ。受託者が随時確認する</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
+          <t>令和8年8月4日に102ファイルを受領。残るのは点検事項29件の解消。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -6156,47 +6157,47 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>国の告示を待つ。受託者が随時確認する</t>
+          <t>確認事項No.8・9と対応。重大3件の取扱いが決まると着手できる</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月4日に102ファイルを受領。残るのは点検事項29件の解消。</t>
+          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -6206,37 +6207,37 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.8・9と対応。重大3件の取扱いが決まると着手できる</t>
+          <t>自給率（δ）は受領済（R8.7.30）。金額換算に必要</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
+          <t>区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>区域外利用の内訳</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -6261,37 +6262,37 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>自給率（δ）は受領済（R8.7.30）。金額換算に必要</t>
+          <t>依頼No.6の残る部分。自給率では所在地が分からない</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。</t>
+          <t>第2段階の算定チェーンは見える化B3・D45・D46系列により閉じた。残るのは、グループホーム・特定施設等の種別別受給者数と介護予防・日常生活支援総合事業の実績である。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>区域外利用の内訳</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -6306,37 +6307,37 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>依頼No.6の残る部分。自給率では所在地が分からない</t>
+          <t>施設・居住系は定員により見込むため代替可能（将来推計 第2段階 06シートで区域内定員と突合済み）。総合事業は広域連合の実績によるほかない</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>第7期（平成30〜令和2年度）の保険料条例</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>第2段階の算定チェーンは見える化B3・D45・D46系列により閉じた。残るのは、グループホーム・特定施設等の種別別受給者数と介護予防・日常生活支援総合事業の実績である。</t>
+          <t>基準額が6,077円か5,900円かを確定する。</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>第7期の保険料基準額</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -6346,52 +6347,52 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>施設・居住系は定員により見込むため代替可能（将来推計 第2段階 06シートで区域内定員と突合済み）。総合事業は広域連合の実績によるほかない</t>
+          <t>見える化C1により6,077円を確認（R8.7.30）。依頼は解消</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>第7期（平成30〜令和2年度）の保険料条例</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>基準額が6,077円か5,900円かを確定する。</t>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>第7期の保険料基準額</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -6406,42 +6407,42 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>見える化C1により6,077円を確認（R8.7.30）。依頼は解消</t>
+          <t>確認事項No.20と対応</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
+          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -6461,42 +6462,42 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.20と対応</t>
+          <t>確認事項No.7と対応</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>見える化システムD49の指標定義</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
+          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>地域差指数の分解の可否</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>見える化システム・厚生労働省</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -6506,47 +6507,47 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.7と対応</t>
+          <t>受託者側で確認する</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>―</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
+          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料第3稿の自己点検で、12件中5件がこの類であった。</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>会議資料・委員会資料の記述の正確性</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>随時</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -6556,97 +6557,97 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>受託者側で確認する</t>
+          <t>キックオフ資料の点検結果05シートに手順を記録</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料第3稿の自己点検で、12件中5件がこの類であった。</t>
+          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>中重度・軽度の認定率の推移</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>見える化システム</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>キックオフ資料の点検結果05シートに手順を記録</t>
+          <t>受託者側で出力を試行する</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域【令和8年8月4日受領済】</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に収録されており、区域内124件を抽出して整理した。</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>訪問・通所困難地域の判定</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>北海道・広域連合</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>受領済</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -6656,12 +6657,12 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>受託者側で出力を試行する</t>
+          <t>確認事項No.15と対応。住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
     </row>
@@ -6768,11 +6769,11 @@
         </is>
       </c>
       <c r="B28" s="21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.2 訪問系・通所系事業所の運営規程における通常の、No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）、No.19 居住系・施設サービスの種別別受給者数と総合事</t>
+          <t>No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）、No.19 居住系・施設サービスの種別別受給者数と総合事</t>
         </is>
       </c>
       <c r="D28" s="22" t="n"/>
@@ -6812,11 +6813,11 @@
         </is>
       </c>
       <c r="B30" s="21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.2 訪問系・通所系事業所の運営規程における通常の、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="D30" s="22" t="n"/>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -4768,7 +4768,7 @@
 第10期計画素案_第9稿→第10稿_修正指示書.xlsx（66件）
 第10期計画_業務工程管理表.xlsx（本表）
 第10期計画_キックオフ会議資料_第4稿.docx（13章18表）
-第10期計画_キックオフ会議ヒアリングシート.docx（13項目）
+第10期計画_キックオフ会議ヒアリングシート.docx（14項目）
 第10期計画_キックオフ資料の点検結果.xlsx（6シート）
 第10期計画_必要事項の一覧.xlsx（8シート）
 第10期計画_計画素案の別管理表.xlsx（6シート）

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -939,7 +939,7 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>【本表の位置づけ】計画素案（第10稿）の本文には、確認事項や作業上の留意点を注記として書き込まない方針とする。本文の注記は、計画の読み手（住民・委員・関係機関）が計画を理解するために必要なものに限り、受託者と発注者の間の作業管理に関する事項は本表で管理する。確定していない数値は、本文では［要協議］［要確認］［要内訳］として空欄扱いのまま残し、その解消に必要な作業と確認事項は本表03シートで管理する。</t>
+          <t>【本表の位置づけ】計画素案（第11稿）の本文には、確認事項や作業上の留意点を注記として書き込まない方針とする。本文の注記は、計画の読み手（住民・委員・関係機関）が計画を理解するために必要なものに限り、受託者と発注者の間の作業管理に関する事項は本表で管理する。確定していない数値は、本文では［要協議］［要確認］［要内訳］として空欄扱いのまま残し、その解消に必要な作業と確認事項は本表03シートで管理する。</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
     <row r="23" ht="117" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第10稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）、将来推計 第2段階（8シート）、実施済み3調査の受領点検と集計（16シート）、要介護認定データの確認（7シート）、サービス受給者数データの確認（7シート）を作成した。人口推計の基礎は、社人研推計をそのまま用いることを受託者の案とし、これを作業上の前提として仮に置いて試算している（キックオフ会議でご意向を確認する）。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
+          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第11稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）、将来推計 第2段階（8シート）、実施済み3調査の受領点検と集計（16シート）、要介護認定データの確認（7シート）、サービス受給者数データの確認（7シート）を作成した。人口推計の基礎は、社人研推計をそのまま用いることを受託者の案とし、これを作業上の前提として仮に置いて試算している（キックオフ会議でご意向を確認する）。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）の取扱いが決まると⑤4調査横断のクロス集計に着手できる（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめた。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>素案は第10稿まで作成済み。骨子案は素案に統合している。第6章の推計値が未確定のため素案は暫定。概要版は未着手。3町の第10期計画に共通指標を掲載する合意が未了（確認No.17）</t>
+          <t>素案は第11稿まで作成済み。骨子案は素案に統合している。第6章の推計値が未確定のため素案は暫定。概要版は未着手。3町の第10期計画に共通指標を掲載する合意が未了（確認No.17）</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>4調査すべてを受領し集計済。3調査は点検事項32件の解消待ち。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1955,7 +1955,7 @@
       <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>3調査の点検事項の重大5件の解消が前提。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
+          <t>計画本文への反映は点検事項の重大5件の取扱いによる。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>地域課題の整理は先行実施済み（妥当性検証報告書 主要所見20件）。骨子案は計画素案（第10稿）に統合して先行作成済み。将来推計は第1段階（人口と認定者数）・第2段階（サービス見込量）を先行して試算済み。第3段階（給付費・保険料）が未着手</t>
+          <t>地域課題の整理は先行実施済み（妥当性検証報告書 主要所見20件）。骨子案は計画素案（第11稿）に統合して先行作成済み。将来推計は第1段階（人口と認定者数）・第2段階（サービス見込量）を先行して試算済み。第3段階（給付費・保険料）が未着手</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>素案は第10稿まで作成済み（暫定）。見込量・保険料は将来推計の完了後に確定する</t>
+          <t>素案は第11稿まで作成済み（暫定）。見込量・保険料は将来推計の完了後に確定する</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>仕様書は骨子案・計画素案・計画最終案・概要版原稿の作成を求めている。現在、骨子案の内容は計画素案（第10稿）に統合して先行作成しているが、骨子案を別に作成する必要があるかの確認。</t>
+          <t>仕様書は骨子案・計画素案・計画最終案・概要版原稿の作成を求めている。現在、骨子案の内容は計画素案（第11稿）に統合して先行作成しているが、骨子案を別に作成する必要があるかの確認。</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第10稿.docx
+          <t>第10期介護保険事業計画_素案_第11稿.docx
 （577段落・98表・34図）</t>
         </is>
       </c>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>①推計資料は第1段階（人口・認定者数）と第2段階（サービス見込量）を作成済み。第3段階（給付費・保険料）が未作成。②クロス集計表は健康とくらしの調査分を作成済み。他の3調査は集計まで完了し、4調査横断のクロス集計は点検事項の重大5件の解消を待つ。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
+          <t>①推計資料は第1段階（人口・認定者数）と第2段階（サービス見込量）を作成済み。第3段階（給付費・保険料）が未作成。②クロス集計表は4調査すべて作成済み。4調査横断のクロス集計は発注者のご意向により行わない（アンケート調査の集計分析報告書 13シート）。③図表の元数値はシート内に保持しているが、発注者側での再計算を想定した様式の指定があれば合わせる。</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>計画素案（第10稿）に統合して先行作成</t>
+          <t>計画素案（第11稿）に統合して先行作成</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第10稿.docx</t>
+          <t>第10期介護保険事業計画_素案_第11稿.docx</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめた。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表）を作成した。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表）を作成した。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -4717,6 +4717,8 @@
 第10期計画_将来推計_第2段階_サービス見込量.xlsx（8シート）
 第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx（8シート）
 第10期計画_実施済み3調査の受領点検と集計.xlsx（16シート）
+第10期計画_アンケート調査の集計分析報告書.xlsx（14シート）
+第10期計画_実施済み調査_結果報告書.docx（8章41表）
 第10期計画_要介護認定データの確認.xlsx（7シート）
 第10期計画_サービス受給者数データの確認.xlsx（7シート）
 figures/*.png（34点）</t>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表）を作成した。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表39図）を作成した。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表）を作成した。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表39図）を作成した。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -4718,7 +4718,7 @@
 第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx（8シート）
 第10期計画_実施済み3調査の受領点検と集計.xlsx（16シート）
 第10期計画_アンケート調査の集計分析報告書.xlsx（14シート）
-第10期計画_実施済み調査_結果報告書.docx（8章41表）
+第10期計画_実施済み調査_結果報告書.docx（8章41表39図）
 第10期計画_要介護認定データの確認.xlsx（7シート）
 第10期計画_サービス受給者数データの確認.xlsx（7シート）
 figures/*.png（34点）</t>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表39図）を作成した。点検事項32件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表39図）を作成した。点検事項33件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -5521,7 +5521,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項32件のうち重大5件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
+          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項33件のうち重大5件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -4770,7 +4770,7 @@
 第10期計画素案_第9稿→第10稿_修正指示書.xlsx（66件）
 第10期計画_業務工程管理表.xlsx（本表）
 第10期計画_キックオフ会議資料_第4稿.docx（13章18表）
-第10期計画_キックオフ会議ヒアリングシート.docx（14項目）
+第10期計画_キックオフ会議ヒアリングシート.docx（16項目）
 第10期計画_キックオフ資料の点検結果.xlsx（6シート）
 第10期計画_必要事項の一覧.xlsx（8シート）
 第10期計画_計画素案の別管理表.xlsx（6シート）

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表39図）を作成した。点検事項33件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表39図）を作成した。点検事項34件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -5521,7 +5521,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項33件のうち重大5件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
+          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項34件のうち重大5件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表39図）を作成した。点検事項34件のうち重大5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章48表39図）を作成した。点検事項35件のうち重大6件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1912,7 +1912,7 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>キックオフ会議で、①事業所実態調査の取扱い、②人口推計の基礎及び認定率のシナリオ、③3調査の点検事項の重大5件の取扱い、④委員会日程についてご意向を確認する</t>
+          <t>キックオフ会議で、①事業所実態調査の取扱い、②人口推計の基礎及び認定率のシナリオ、③3調査の点検事項の重大6件の取扱い、④委員会日程についてご意向を確認する</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章41表39図）を作成した。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章48表39図）を作成した。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1955,7 +1955,7 @@
       <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>計画本文への反映は点検事項の重大5件の取扱いによる。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
+          <t>計画本文への反映は点検事項の重大6件の取扱いによる。仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の実績確定時期の確認を要する</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大5件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
+          <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -4718,7 +4718,7 @@
 第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx（8シート）
 第10期計画_実施済み3調査の受領点検と集計.xlsx（16シート）
 第10期計画_アンケート調査の集計分析報告書.xlsx（14シート）
-第10期計画_実施済み調査_結果報告書.docx（8章41表39図）
+第10期計画_実施済み調査_結果報告書.docx（8章48表39図）
 第10期計画_要介護認定データの確認.xlsx（7シート）
 第10期計画_サービス受給者数データの確認.xlsx（7シート）
 figures/*.png（34点）</t>
@@ -5521,7 +5521,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項34件のうち重大5件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
+          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項35件のうち重大6件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月4日に102ファイルを受領。残るのは点検事項29件の解消。</t>
+          <t>令和8年8月4日に102ファイルを受領。残るのは点検事項35件の解消。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -6229,17 +6229,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地）</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。</t>
+          <t>①区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。②区域内の地域密着型サービスは広域連合が指定権者であり、グループホームくるみの郷は介護サービス情報公表システムに掲載がないため定員を公表資料で確認できない。同事業所の定員及び休止の状況。③事業所票に所在町の記入欄がないため、事業所の所在町。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>区域外利用の内訳</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>依頼No.6の残る部分。自給率では所在地が分からない</t>
+          <t>依頼No.6の残る部分。自給率では所在地が分からない。②は点検事項No.35に対応する</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地）、No.19 居住系・施設サービスの種別別受給者数と総合事</t>
+          <t>No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地、区域内、No.19 居住系・施設サービスの種別別受給者数と総合事</t>
         </is>
       </c>
       <c r="D28" s="22" t="n"/>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1389,7 +1389,8 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>素案第10稿（542段落97表34図）
+          <t>骨子案（11節22表）
+素案第11稿（620段落108表34図）
 修正指示書（66件）</t>
         </is>
       </c>
@@ -1399,7 +1400,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -1408,7 +1409,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>素案は第11稿まで作成済み。骨子案は素案に統合している。第6章の推計値が未確定のため素案は暫定。概要版は未着手。3町の第10期計画に共通指標を掲載する合意が未了（確認No.17）</t>
+          <t>骨子案を作成した（令和8年8月）。素案は第11稿まで作成済み。第6章の推計値が未確定のため素案は暫定。概要版は未着手。3町の第10期計画に共通指標を掲載する合意が未了（確認No.17）</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1985,7 +1986,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>地域課題の整理は先行実施済み（妥当性検証報告書 主要所見20件）。骨子案は計画素案（第11稿）に統合して先行作成済み。将来推計は第1段階（人口と認定者数）・第2段階（サービス見込量）を先行して試算済み。第3段階（給付費・保険料）が未着手</t>
+          <t>地域課題の整理は先行実施済み（妥当性検証報告書 主要所見20件）。骨子案を作成した（第10期介護保険事業計画_骨子案.docx・11節22表）。将来推計は第1段階（人口と認定者数）・第2段階（サービス見込量）を先行して試算済み。第3段階（給付費・保険料）が未着手</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1998,7 +1999,7 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>骨子案を素案に統合してよいか、又は骨子案を別に作成するかの確認を要する</t>
+          <t>骨子案 第10節の決定・確認を要する事項12件についてご意向を確認する</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2662,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。</t>
+          <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>素案 第3章第5節
+          <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
@@ -3268,17 +3269,18 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>骨子案の取扱い</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>仕様書は骨子案・計画素案・計画最終案・概要版原稿の作成を求めている。現在、骨子案の内容は計画素案（第11稿）に統合して先行作成しているが、骨子案を別に作成する必要があるかの確認。</t>
+          <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>骨子案</t>
+          <t>骨子案
+素案の次稿</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -4818,7 +4820,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>計画素案（第11稿）に統合して先行作成</t>
+          <t>第10期介護保険事業計画_骨子案.docx（11節22表）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -4826,13 +4828,13 @@
           <t>Word及びPDF</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -4841,7 +4843,7 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>骨子案を計画素案とは別に作成する必要があるかの確認。仕様書５は令和8年10月に骨子案作成、11月に骨子の整理としている。</t>
+          <t>第10節の決定・確認を要する事項12件についてご意向を確認したうえで、令和8年11月に構成3町の意見を反映して確定する。</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -5734,7 +5736,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>第9期のプロセス評価（事業が計画どおり実施されたか）に必要。現時点で最大の空白。</t>
+          <t>第9期のプロセス評価（事業が計画どおり実施されたか）に必要。現時点で最大の空白。5区分14項目に展開し、記入様式を別冊「資料提供依頼_第9期の施策事業実績」（7シート）として作成した。既存資料（事務事業評価表、実施計画、介護保険事業状況報告、決算書）の写しのご提供でも足りる。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -5764,7 +5766,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.1と対応。仕様書４（2）が完了しない</t>
+          <t>確認事項No.1と対応。仕様書４（2）が完了しない。代替できない項目が3件ある（同別冊06シート）</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6166,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.8・9と対応。重大3件の取扱いが決まると着手できる</t>
+          <t>確認事項No.8・9と対応。重大6件の取扱いが決まると着手できる</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1143,6 +1143,7 @@
 ⑩人口推計の基礎の検証（見える化A系列 2000〜2050年）
 ⑪将来推計 第1段階（人口と認定者数・3シナリオ）
 ⑫将来推計 第2段階（サービス見込量・感度分析）
+⑬需要3シナリオ（低位・標準・高位）の感度表
 ⑧レビュー指摘への対応（記述の修正16件・訂正1件）</t>
         </is>
       </c>
@@ -1327,7 +1328,8 @@
 ④認定率・サービス利用率の施策反映
 ⑤事業所が存在しないサービスの見込量の直接入力
 ⑥給付費・保険料の算定
-⑦シナリオ比較（基本・需要上振れ・供給制約・基金活用）</t>
+⑦需要3シナリオ（低位・標準・高位）の感度表
+⑧シナリオ比較（基本・需要上振れ・供給制約・基金活用）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1353,7 +1355,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>令和8年8月4日に見える化B3系列（要介護度別認定者数）及びD系列（受給者数・利用率・1人当たり利用日数）を受領し、第2段階の算定チェーン（認定者数×利用率×1人当たり利用日数）が閉じた。同チェーンにより令和7年度の実績を1％未満の差で再現できることを検証した（サービス受給者数データの確認 05シート）。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて第1段階（人口と認定者数）を試算し、将来推計（8シート）として取りまとめた（基礎の採用はキックオフ会議でご意向を確認する。確認No.14）。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、利用率と1人当たり利用日数・回数を令和7年度の値で固定する案を基本とし、趨勢を見込む場合を感度分析として併記する形で試算し、将来推計 第2段階（8シート）として取りまとめた（置き方はヒアリングシート項目6でご意向を確認する）。残るのは、居住系・施設の種別別受給者数、総合事業の実績、及び第3段階（給付費・保険料）である</t>
+          <t>令和8年8月4日に見える化B3系列（要介護度別認定者数）及びD系列（受給者数・利用率・1人当たり利用日数）を受領し、第2段階の算定チェーン（認定者数×利用率×1人当たり利用日数）が閉じた。同チェーンにより令和7年度の実績を1％未満の差で再現できることを検証した（サービス受給者数データの確認 05シート）。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて第1段階（人口と認定者数）を試算し、将来推計（8シート）として取りまとめた（基礎の採用はキックオフ会議でご意向を確認する。確認No.14）。階級別人口は令和7年度の実績人口に社人研推計の伸び率を乗じて求め、基準年度の認定者数が実績1,984人と一致することを確認した。令和11年度の認定者数は認定率のシナリオにより2,004〜2,112人となる。第2段階（サービス見込量）は、利用率と1人当たり利用日数・回数を令和7年度の値で固定する案を基本とし、趨勢を見込む場合を感度分析として併記する形で試算し、将来推計 第2段階（8シート）として取りまとめた（置き方はヒアリングシート項目6でご意向を確認する）。この基本ケースを標準とする需要3シナリオ（低位・標準・高位）を感度表（8シート）として取りまとめた。令和11年度の幅は在宅＋0.0〜＋13.5％、居住系▲9.9〜＋5.4％、施設▲13.5〜＋5.4％、訪問介護▲3.4〜＋36.0％である。高位でも施設・居住系は区域内定員に収まる。採用値は標準とすることを受託者案とする。残るのは、居住系・施設の種別別受給者数、総合事業の実績、及び第3段階（給付費・保険料）である</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1723,7 +1723,7 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>事業所実態調査・在宅介護実態調査が仕様書の対象外であり、H07・H08・H12・H16のデータ源が確保できない。取扱いの決定を要する（確認No.4）</t>
+          <t>事業所実態調査は実施済みだが、受領した回答に受入困難・BCP等の設問がなく、H12・H16の基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。代理指標への振替の決定を要する（確認No.4）</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1915,7 +1915,7 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>キックオフ会議で、①事業所実態調査の取扱い、②人口推計の基礎及び認定率のシナリオ、③3調査の点検事項の重大6件の取扱い、④委員会日程についてご意向を確認する</t>
+          <t>キックオフ会議で、①代表KPI4項目の代理指標、②人口推計の基礎及び認定率のシナリオ、③3調査の点検事項の重大6件の取扱い、④委員会日程についてご意向を確認する</t>
         </is>
       </c>
     </row>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>事業所実態調査・在宅介護実態調査の取扱い</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査に事業所実態調査・在宅介護実態調査が含まれておらず、「新たなアンケート調査の企画、設計、配布、回収、入力及び督促は行わない」とされている。一方、代表KPIのH07・H08・H12・H16はこれらをデータ源としている。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。H12・H16は事業所側の情報を要するため算定できない。①発注者が実施する、②代理指標へ振り替える、③指標から外す、のいずれかの決定を要する。</t>
+          <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項35件のうち重大6件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH07・H08・H12・H16は事業所実態調査・在宅介護実態調査をデータ源としているが、これらは仕様書４（3）の対象4調査に含まれていない（確認事項No.4）。</t>
+          <t>注1）4調査はいずれも発注者において実施済みであり、本業務では新たな調査の企画、設計、配布、回収、入力及び督促は行わない。契約締結後に発注者から貸与される資料に基づき、集計・クロス集計・分析・課題整理・計画への反映を行う。注2）健康とくらしの調査（令和7年度）は個票データを受領済であり、単純集計・クロス集計・分析を完了している（調査クロス集計・分析 13シート）。他の3調査は令和8年8月4日に第10期分を受領し、点検と集計を行った。点検事項35件のうち重大6件の取扱いが決まるまでは、計画素案の該当箇所を令和5年調査又は見える化システムの数値により暫定的に記述し、確定を要する箇所を［要確認］としている。注3）代表KPIのうちH12・H16は事業所実態調査をデータ源としているが、受領した事業所票に受入困難・BCPの設問がなく、基準値を算定できない。H07・H08の在宅介護実態調査は実施されていない（確認事項No.4）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章48表39図）を作成した。点検事項35件のうち重大6件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章50表39図）を作成した。点検事項35件のうち重大6件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章48表39図）を作成した。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章50表39図）を作成した。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -4722,7 +4722,7 @@
 第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx（8シート）
 第10期計画_実施済み3調査の受領点検と集計.xlsx（16シート）
 第10期計画_アンケート調査の集計分析報告書.xlsx（14シート）
-第10期計画_実施済み調査_結果報告書.docx（8章48表39図）
+第10期計画_実施済み調査_結果報告書.docx（8章50表39図）
 第10期計画_要介護認定データの確認.xlsx（7シート）
 第10期計画_サービス受給者数データの確認.xlsx（7シート）
 figures/*.png（34点）</t>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章50表39図）を作成した。点検事項35件のうち重大6件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
+          <t>健康とくらしの調査は個票データ4,729票によりクロス集計・分析を完了（作業項目①⑥）。第9期の課題20件及び第10期の施策体系に対する妥当性レビューを行い、不足と判定した4領域（介護・介助が必要な層、認知症、施設志向と在宅資源、地域重点度と社会参加の障壁）の分析を追加した（全24シート）。レビューにより、本調査の対象者が一般高齢者及び総合事業対象者であり要支援者・要介護者を含まないことが判明したため、H06・H11の位置づけを代替から補完に改めた（確認No.28）。令和8年8月4日に②③④の第10期分（23の法人・事業者、102ファイル）を受領し、点検と集計を行った（実施済み3調査の受領点検と集計 11シート）。同資料10シートで見える化のK系列・M2系列と突合し、グループホーム・特定施設・住宅型有料・サ高住の介護職員129人が見える化では把握できないことを確認した。令和8年8月5日、4調査を横断したクロス集計は行わず完了とするご意向をいただいた。利用者票の所在地区の記入形式が9種類に分かれ個票を地区に割り付けられないためである。これに代えて、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章51表39図）を作成した。点検事項35件のうち重大6件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答）は、計画本文へ反映する数値の確定に必要であり、ヒアリングシート項目13・14でご意向を確認する（確認No.8）。同日に北海道の施設・住まいの名簿5種を受領し、居所変更実態調査及び見える化K系列と突合した（住まいと施設の公表名簿との突合 7シート）。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設・定員223人であること、特別養護老人ホームの定員が160人＋地域密着型62人であることを確認し、将来推計 第2段階06シートを訂正した。同日受領した北海道の介護保険事業所一覧（47区分）により、区域内の指定事業所124件の「通常の事業実施地域」を整理し（確認No.15の解消）、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した。あわせて同規模保険者40及び参加74市町村との比較分析を実施し、仕様書４（4）の類似保険者比較のうち住民の状態・社会参加の領域を充足した（確認No.3）</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章50表39図）を作成した。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、アンケート調査の集計分析報告書（14シート）として取りまとめ、発注者から提示のあった様式に合わせて実施済み調査 結果報告書（Word・8章51表39図）を作成した。4調査横断のクロス集計は発注者のご意向により行わない。介護給付実績分析・現状分析は見える化データにより先行実施済み（妥当性検証報告書・図表集）。人口推計は実績確定後</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -4722,7 +4722,7 @@
 第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx（8シート）
 第10期計画_実施済み3調査の受領点検と集計.xlsx（16シート）
 第10期計画_アンケート調査の集計分析報告書.xlsx（14シート）
-第10期計画_実施済み調査_結果報告書.docx（8章50表39図）
+第10期計画_実施済み調査_結果報告書.docx（8章51表39図）
 第10期計画_要介護認定データの確認.xlsx（7シート）
 第10期計画_サービス受給者数データの確認.xlsx（7シート）
 figures/*.png（34点）</t>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -939,7 +939,7 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>【本表の位置づけ】計画素案（第11稿）の本文には、確認事項や作業上の留意点を注記として書き込まない方針とする。本文の注記は、計画の読み手（住民・委員・関係機関）が計画を理解するために必要なものに限り、受託者と発注者の間の作業管理に関する事項は本表で管理する。確定していない数値は、本文では［要協議］［要確認］［要内訳］として空欄扱いのまま残し、その解消に必要な作業と確認事項は本表03シートで管理する。</t>
+          <t>【本表の位置づけ】計画素案の本文には、確認事項や作業上の留意点を注記として書き込まない方針とする。本文の注記は、計画の読み手（住民・委員・関係機関）が計画を理解するために必要なものに限り、受託者と発注者の間の作業管理に関する事項は本表で管理する。確定していない数値は、本文では［要協議］［要確認］［要内訳］として空欄扱いのまま残し、その解消に必要な作業と確認事項は本表03シートで管理する。</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
     <row r="23" ht="117" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案（第11稿）、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価のレッドチームレビュー（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）、将来推計 第2段階（8シート）、実施済み3調査の受領点検と集計（16シート）、要介護認定データの確認（7シート）、サービス受給者数データの確認（7シート）を作成した。人口推計の基礎は、社人研推計をそのまま用いることを受託者の案とし、これを作業上の前提として仮に置いて試算している（キックオフ会議でご意向を確認する）。レッドチームレビューの指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
+          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価の自己点検記録（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）、将来推計 第2段階（8シート）、実施済み3調査の受領点検と集計（16シート）、要介護認定データの確認（7シート）、サービス受給者数データの確認（7シート）を作成した。人口推計の基礎は、社人研推計をそのまま用いることを受託者の案とし、これを作業上の前提として仮に置いて試算している（キックオフ会議でご意向を確認する）。自己点検記録の指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
         <is>
           <t>妥当性検証報告書 07・17シート
 追加調査報告書 01・05シート
-素案第10稿 第1章第9節・資料6</t>
+計画素案 第1章第9節・資料6</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -1137,7 +1137,7 @@
 ④給付実績の分析（受給率・利用率・サービス別給付動向）
 ⑤地域支援事業の実績整理
 ⑥令和6〜8年度の事業実績による達成度の再判定
-⑦評価そのもののレッドチームレビュー（指摘29件）
+⑦評価そのものの自己点検記録（指摘29件）
 ⑧全成果物の主張の棚卸し（54主張・根拠水準5階層）
 ⑨地域差の分析（自給率・地域差指数・保険料の管内比較）
 ⑩人口推計の基礎の検証（見える化A系列 2000〜2050年）
@@ -1150,9 +1150,9 @@
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>妥当性検証報告書 01・02・12・23シート
-素案第10稿 第3章
+計画素案 第3章
 施策体系新旧対照表
-第9期評価のレッドチームレビュー（8シート）</t>
+第9期評価の自己点検記録（8シート）</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>レッドチームレビューの指摘29件のうち、記述の修正により対応できる22件への対応を進めた（記述の修正・表現の限定・注記の追加）。うち2件（No.5・No.1）は指摘が的中し、評価の記述を訂正した。No.5は「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見を「数値目標を設定しているのは東川町のみ」に訂正。No.1は見える化B4・B5・B6系列の受領により年齢調整分析を実施し、従来の説明「軽度は改善・中重度は悪化」が逆であることが判明したため撤回した（認定率の年齢調整分析 7シート）。残る2件（人口推計の検証・保険者の自己評価）は資料の受領を要する。レッドチームレビューの結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
+          <t>自己点検記録の指摘29件のうち、記述の修正により対応できる22件への対応を進めた（記述の修正・表現の限定・注記の追加）。うち2件（No.5・No.1）は指摘のとおりであることが確認され、評価の記述を訂正した。No.5は「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見を「数値目標を設定しているのは東川町のみ」に訂正。No.1は見える化B4・B5・B6系列の受領により年齢調整分析を実施し、従来の説明「軽度は改善・中重度は悪化」が逆であることが判明したため撤回した（認定率の年齢調整分析 7シート）。残る2件（人口推計の検証・保険者の自己評価）は資料の受領を要する。自己点検記録の結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1211,7 +1211,7 @@
           <t>調査クロス集計・分析（24シート）
 図表集 08〜13シート
 妥当性検証報告書 11シート
-素案第10稿 第2章第4〜6節
+計画素案 第2章第4〜6節
 実施済み3調査の受領点検と集計（11シート）</t>
         </is>
       </c>
@@ -1273,7 +1273,7 @@
           <t>妥当性検証報告書 03〜06・13・14・21・22シート
 図表集 01〜31シート
 調査クロス集計・分析 01・02・19〜21シート
-素案第10稿 第2章
+計画素案 第2章
 実施済み3調査の受領点検と集計 05・10シート</t>
         </is>
       </c>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>素案第10稿 第6章
+          <t>計画素案 第6章
 追加調査報告書 06シート
 保険料と施策評価の他団体比較（9シート）
 推計資料（見える化の総括表）</t>
@@ -1392,7 +1392,7 @@
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>骨子案（11節22表）
-素案第11稿（620段落108表34図）
+計画素案（620段落108表34図）
 修正指示書（66件）</t>
         </is>
       </c>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>骨子案を作成した（令和8年8月）。素案は第11稿まで作成済み。第6章の推計値が未確定のため素案は暫定。概要版は未着手。3町の第10期計画に共通指標を掲載する合意が未了（確認No.17）</t>
+          <t>骨子案を作成した（令和8年8月）。素案は令和8年8月時点の版まで作成済み。第6章の推計値が未確定のため素案は暫定。概要版は未着手。3町の第10期計画に共通指標を掲載する合意が未了（確認No.17）</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>貸与資料の受領と整理は先行実施済み。第9期計画の評価・検証は妥当性検証報告書（24シート）として先行して取りまとめ済み。令和8年8月4日に3調査の第10期分102ファイルを受領し、点検・集計・見える化との突合を完了した。キックオフ会議資料は第4稿。キックオフ会議の日程が未確定</t>
+          <t>貸与資料の受領と整理は先行実施済み。第9期計画の評価・検証は妥当性検証報告書（24シート）として先行して取りまとめ済み。令和8年8月4日に3調査の第10期分102ファイルを受領し、点検・集計・見える化との突合を完了した。キックオフ会議資料は作成中。キックオフ会議の日程が未確定</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>素案は第11稿まで作成済み（暫定）。見込量・保険料は将来推計の完了後に確定する</t>
+          <t>素案は令和8年8月時点の版まで作成済み（暫定）。見込量・保険料は将来推計の完了後に確定する</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>第9期は3町の高齢者福祉計画に数値目標が1件も設定されておらず、広域連合の代表KPIの検証への参画を明記していたのは東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
+          <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>見える化システムの値は6,077円であるが、計画素案の第9稿までは5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
+          <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（レッドチームレビュー No.1）。</t>
+          <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（レッドチームレビュー No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
+          <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -4612,8 +4612,8 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第11稿.docx
-（577段落・98表・34図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx
+（667段落・114表・34図）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -4709,7 +4709,7 @@
           <t>第10期計画_調査クロス集計・分析.xlsx（24シート）
 第10期計画_保険料と施策評価の他団体比較.xlsx（9シート）
 第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx（10シート）
-第10期計画_第9期評価のレッドチームレビュー.xlsx（9シート）
+第10期計画_第9期評価の自己点検記録.xlsx（9シート）
 第10期計画_認定率の年齢調整分析.xlsx（7シート）
 第10期計画_図表集_白黒.xlsx（33シート133点）
 第10期計画_妥当性検証報告書.xlsx（24シート）
@@ -4771,9 +4771,9 @@
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>第10期計画_確認依頼書.docx（第9版）
-第10期計画素案_第9稿→第10稿_修正指示書.xlsx（66件）
+第10期計画素案_修正指示書.xlsx（66件）
 第10期計画_業務工程管理表.xlsx（本表）
-第10期計画_キックオフ会議資料_第4稿.docx（13章18表）
+第10期計画_キックオフ会議資料.docx（13章18表）
 第10期計画_キックオフ会議ヒアリングシート.docx（16項目）
 第10期計画_キックオフ資料の点検結果.xlsx（6シート）
 第10期計画_必要事項の一覧.xlsx（8シート）
@@ -4801,7 +4801,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>①キックオフ会議資料は第4稿まで作成済み。会議日程が未確定。②運営協議会等への資料原案は開催日程と審議事項の確定を要する。③パブリックコメント資料は実施期間の確定を要する。</t>
+          <t>①キックオフ会議資料は作成済み。会議日程が未確定。②運営協議会等への資料原案は開催日程と審議事項の確定を要する。③パブリックコメント資料は実施期間の確定を要する。</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第11稿.docx</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>令和7年11月17日〜12月8日実施分の個票データ4,729票を受領済（65歳以上7,121人対象・回収4,798票・回収率67.4％）。20指標の年齢階級別・町別集計に加え、小学校区12地区別の集計、年齢調整による地域比較、社会参加・世帯構成・経済状況・移動制約・在宅生活の課題との関連分析を実施し、調査クロス集計・分析（13シート）として取りまとめた。H04＝19.1％、H05の基準値を確定。大雪独自設問によりH06・H07・H08・H11の代替データ源を特定した（確認No.4）。計画素案への反映は次稿で行う。</t>
+          <t>令和7年11月17日〜12月8日実施分の個票データ4,729票を受領済（65歳以上7,121人対象・回収4,798票・回収率67.4％）。20指標の年齢階級別・町別集計に加え、小学校区12地区別の集計、年齢調整による地域比較、社会参加・世帯構成・経済状況・移動制約・在宅生活の課題との関連分析を実施し、調査クロス集計・分析（13シート）として取りまとめた。H04＝19.1％、H05の基準値を確定。大雪独自設問によりH06・H07・H08・H11の代替データ源を特定した（確認No.4）。計画素案への反映は次の改訂で行う。</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料第3稿の自己点検で、12件中5件がこの類であった。</t>
+          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料の自己点検で、12件中5件がこの類であった。</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -664,7 +664,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。作成日：令和8年8月4日。</t>
+          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。状況基準日：令和8年8月25日。</t>
         </is>
       </c>
     </row>
@@ -950,10 +950,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="117" customHeight="1">
+    <row r="23" ht="104" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、第9期評価の自己点検記録（9シート・指摘29件）、主張の根拠水準の棚卸しと再レビュー（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）、将来推計 第2段階（8シート）、実施済み3調査の受領点検と集計（16シート）、要介護認定データの確認（7シート）、サービス受給者数データの確認（7シート）を作成した。人口推計の基礎は、社人研推計をそのまま用いることを受託者の案とし、これを作業上の前提として仮に置いて試算している（キックオフ会議でご意向を確認する）。自己点検記録の指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
+          <t>【現時点の全体状況（令和8年7月29日）】契約上の業務期間は令和8年8月着手であるが、発注者から第9期計画、3町の高齢者福祉計画、業務仕様書、地域包括ケア「見える化」システムのデータ、令和7年度 健康とくらしの調査の成果物の貸与を受け、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理を先行して実施している。成果物として、妥当性検証報告書（24シート）、追加調査報告書（8シート）、図表集（33シート133点）、修正指示書（66件）、計画素案、施策体系新旧対照表（5シート）、確認依頼書を作成済みである。また、健康とくらしの調査の個票データによる調査クロス集計・分析（24シート）、認定率の年齢調整分析（7シート）、保険料と施策評価の他団体比較（9シート）、保険料の所得段階と低所得者軽減の検証（10シート）、受託者の自己点検（9シート・指摘29件）、受託者の自己点検（8シート・主張54件）、地域差の分析（15シート）、計画素案の別管理表（6シート）、必要事項の一覧（8シート）、人口推計の基礎の検証（9シート）、将来推計 第1段階（8シート）、将来推計 第2段階（8シート）、実施済み3調査の受領点検と集計（16シート）、要介護認定データの確認（7シート）、サービス受給者数データの確認（7シート）を作成した。人口推計の基礎は、社人研推計をそのまま用いることを受託者の案とし、これを作業上の前提として仮に置いて試算している（キックオフ会議でご意向を確認する）。自己点検記録の指摘のうち2件（3町の数値目標、認定率の年齢調整）は検証の結果が当初の説明と逆転したため、評価の記述を訂正している。</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
 ⑪将来推計 第1段階（人口と認定者数・3シナリオ）
 ⑫将来推計 第2段階（サービス見込量・感度分析）
 ⑬需要3シナリオ（低位・標準・高位）の感度表
-⑧レビュー指摘への対応（記述の修正16件・訂正1件）</t>
+⑧点検指摘への対応（記述の修正16件・訂正1件）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1152,7 +1152,7 @@
           <t>妥当性検証報告書 01・02・12・23シート
 計画素案 第3章
 施策体系新旧対照表
-第9期評価の自己点検記録（8シート）</t>
+受託者の自己点検（8シート）</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>自己点検記録の指摘29件のうち、記述の修正により対応できる22件への対応を進めた（記述の修正・表現の限定・注記の追加）。うち2件（No.5・No.1）は指摘のとおりであることが確認され、評価の記述を訂正した。No.5は「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見を「数値目標を設定しているのは東川町のみ」に訂正。No.1は見える化B4・B5・B6系列の受領により年齢調整分析を実施し、従来の説明「軽度は改善・中重度は悪化」が逆であることが判明したため撤回した（認定率の年齢調整分析 7シート）。残る2件（人口推計の検証・保険者の自己評価）は資料の受領を要する。自己点検記録の結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
+          <t>受託者の自己点検による指摘29件のうち、記述の修正により対応できる22件への対応を進めた（記述の修正・表現の限定・注記の追加）。うち2件（No.5・No.1）は指摘のとおりであることが確認され、評価の記述を訂正した。No.5は「3町の高齢者福祉計画に数値目標がない」という所見を「事業の数値目標を設定しているのは東川町のみ」に訂正。No.1は見える化B4・B5・B6系列の受領により年齢調整分析を実施し、従来の説明「軽度は改善・中重度は悪化」が逆であることが判明したため撤回した（認定率の年齢調整分析 7シート）。残る2件（人口推計の検証・保険者の自己評価）は資料の受領を要する。自己点検の結果、現時点の評価は「計画記載事項の検証」と「外部評価の分析」にとどまり、事業が計画どおり実施されたかというプロセス評価が空白であることを確認したため、進捗を0.80から0.65に改めた。令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算が未受領（確認No.5）。受領後に施策単位の達成度を判定する。あわせて年齢階級別認定率（確認No.37）及び交付金評価の最新調査（確認No.38）を要する</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>注1）「対応する業務内容」は仕様書４（1）〜（12）の番号。01シートと対応する。注2）「提出期日」は発注者が指定する期日を記入する欄。仕様書５は各工程終了後の成果物提出と発注者確認を次工程の条件としているため、期日を月ごとに定めていただく必要がある。注3）令和8年7月29日時点で、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理、（6）計画書の作成の一部を先行実施している。先行実施分は8月・9月・10月の工程に前倒しで反映される。注4）仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の給付実績・事業実績の確定時期によっては後ろ倒しとなる可能性がある。キックオフ会議で工程の調整を協議したい。</t>
+          <t>注1）「対応する業務内容」は仕様書４（1）〜（12）の番号。01シートと対応する。注2）「提出期日」は発注者が指定する期日を記入する欄。仕様書５は各工程終了後の成果物提出と発注者確認を次工程の条件としているため、期日を月ごとに定めていただく必要がある。注3）令和8年8月25日時点で、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理、（6）計画書の作成の一部を先行実施している。先行実施分は8月・9月・10月の工程に前倒しで反映される。注4）仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の給付実績・事業実績の確定時期によっては後ろ倒しとなる可能性がある。キックオフ会議で工程の調整を協議したい。</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
           <t>第10期計画_調査クロス集計・分析.xlsx（24シート）
 第10期計画_保険料と施策評価の他団体比較.xlsx（9シート）
 第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx（10シート）
-第10期計画_第9期評価の自己点検記録.xlsx（9シート）
+第10期計画_受託者の自己点検.xlsx（9シート）
 第10期計画_認定率の年齢調整分析.xlsx（7シート）
 第10期計画_図表集_白黒.xlsx（33シート133点）
 第10期計画_妥当性検証報告書.xlsx（24シート）
@@ -4719,7 +4719,7 @@
 第10期計画_人口推計の基礎の検証.xlsx（9シート）
 第10期計画_将来推計_人口と認定者数.xlsx（8シート）
 第10期計画_将来推計_第2段階_サービス見込量.xlsx（8シート）
-第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx（8シート）
+第10期計画_受託者の自己点検.xlsx（8シート）
 第10期計画_実施済み3調査の受領点検と集計.xlsx（16シート）
 第10期計画_アンケート調査の集計分析報告書.xlsx（14シート）
 第10期計画_実施済み調査_結果報告書.docx（8章51表39図）
@@ -4775,10 +4775,9 @@
 第10期計画_業務工程管理表.xlsx（本表）
 第10期計画_キックオフ会議資料.docx（13章18表）
 第10期計画_キックオフ会議ヒアリングシート.docx（16項目）
-第10期計画_キックオフ資料の点検結果.xlsx（6シート）
 第10期計画_必要事項の一覧.xlsx（8シート）
 第10期計画_計画素案の別管理表.xlsx（6シート）
-第10期計画_成果品一覧.xlsx（4シート）</t>
+第10期計画_送付資料一覧.xlsx（3シート）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -5666,7 +5665,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>成果物の主張を確定するために提供を要する資料を一覧化する。03シートの確認事項が発注者・3町・北海道の「決定」を求めるものであるのに対し、本シートは「資料の提供」を求めるものである。根拠及び各資料が確定する主張は、「主張の根拠水準の棚卸しと再レビュー」06シートに対応する。</t>
+          <t>成果物の主張を確定するために提供を要する資料を一覧化する。03シートの確認事項が発注者・3町・北海道の「決定」を求めるものであるのに対し、本シートは「資料の提供」を求めるものである。根拠及び各資料が確定する主張は、「受託者の自己点検」06シートに対応する。</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6567,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>キックオフ資料の点検結果05シートに手順を記録</t>
+          <t>受託者の自己点検に手順を記録</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6836,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査の第10期分）は、いずれも業務内容そのものが進まない資料である。No.13がなければ仕様書４（2）のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の資料は、いずれも成果物の主張の根拠を推論・仮説から算定又は確認に引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する手段である。注3）本シートは令和8年7月29日の主張の棚卸し（全成果物46主張のMECEな分類）に基づく。各資料が確定する主張の詳細は、「主張の根拠水準の棚卸しと再レビュー」01・06シートに示している。</t>
+          <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査の第10期分）は、いずれも業務内容そのものが進まない資料である。No.13がなければ仕様書４（2）のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の資料は、いずれも成果物の主張の根拠を推論・仮説から算定又は確認に引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する手段である。注3）本シートは令和8年7月29日の主張の棚卸し（全成果物46主張のMECEな分類）に基づく。各資料が確定する主張の詳細は、「受託者の自己点検」01・06シートに示している。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -5640,7 +5640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5658,7 +5658,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料提供依頼一覧（20件）</t>
+          <t>資料提供依頼一覧（21件）</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>第7期（平成30〜令和2年度）の保険料条例</t>
+          <t>介護保険事業状況報告（月報・年報）の保険者控え（令和2年度〜令和7年度）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>基準額が6,077円か5,900円かを確定する。</t>
+          <t>第3段階（給付費・保険料）の算定に用いる給付費の月次・年度の実績。あわせて第9期の給付費の計画乖離（代表KPI H15）の把握に用いる。見える化には年報ベースの値が収録されているが、月次の推移と直近年度の速報値は保険者控えによる。</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>第7期の保険料基準額</t>
+          <t>第3段階の給付費の算定、H15の基準値</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -6355,49 +6355,49 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>見える化C1により6,077円を確認（R8.7.30）。依頼は解消</t>
+          <t>キックオフ会議のご指示により「令和8年実績」を年報・月報の実績に改める整理としたことに対応する</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第7期（平成30〜令和2年度）の保険料条例</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
+          <t>基準額が6,077円か5,900円かを確定する。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>第7期の保険料基準額</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -6412,42 +6412,42 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.20と対応</t>
+          <t>見える化C1により6,077円を確認（R8.7.30）。依頼は解消</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -6467,42 +6467,42 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.7と対応</t>
+          <t>確認事項No.20と対応</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
+          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -6512,47 +6512,47 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>受託者側で確認する</t>
+          <t>確認事項No.7と対応</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>見える化システムD49の指標定義</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料の自己点検で、12件中5件がこの類であった。</t>
+          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>地域差指数の分解の可否</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>見える化システム・厚生労働省</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -6562,97 +6562,97 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>受託者の自己点検に手順を記録</t>
+          <t>受託者側で確認する</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>―</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料の自己点検で、12件中5件がこの類であった。</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>会議資料・委員会資料の記述の正確性</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>受託者側で出力を試行する</t>
+          <t>受託者の自己点検に手順を記録</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域【令和8年8月4日受領済】</t>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に収録されており、区域内124件を抽出して整理した。</t>
+          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定</t>
+          <t>中重度・軽度の認定率の推移</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北海道・広域連合</t>
+          <t>見える化システム</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -6662,123 +6662,151 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.15と対応。住まいと施設の公表名簿との突合 08シート</t>
+          <t>受託者側で出力を試行する</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域【令和8年8月4日受領済】</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に収録されており、区域内124件を抽出して整理した。</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>訪問・通所困難地域の判定</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>北海道・広域連合</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.15と対応。住まいと施設の公表名簿との突合 08シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。公表され次第。</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>公表待ち</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
+      <c r="B28" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="22" t="n"/>
-      <c r="H27" s="22" t="n"/>
-      <c r="I27" s="22" t="n"/>
-      <c r="J27" s="23" t="n"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地、区域内、No.19 居住系・施設サービスの種別別受給者数と総合事</t>
         </is>
       </c>
       <c r="D28" s="22" t="n"/>
@@ -6790,17 +6818,17 @@
       <c r="J28" s="23" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B29" s="21" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.20 （受託者の作業）会議資料・委員会資料の作成時、No.15 第9期の自己評価と北海道への報告の実績</t>
+          <t>No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地、区域内、No.21 介護保険事業状況報告（月報・年報）の保険者控、No.19 居住系・施設サービスの種別別受給者数と総合事</t>
         </is>
       </c>
       <c r="D29" s="22" t="n"/>
@@ -6812,17 +6840,17 @@
       <c r="J29" s="23" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="B30" s="21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.2 訪問系・通所系事業所の運営規程における通常の、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.20 （受託者の作業）会議資料・委員会資料の作成時、No.15 第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D30" s="22" t="n"/>
@@ -6833,8 +6861,30 @@
       <c r="I30" s="22" t="n"/>
       <c r="J30" s="23" t="n"/>
     </row>
-    <row r="32" ht="39" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.2 訪問系・通所系事業所の運営規程における通常の、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="23" t="n"/>
+    </row>
+    <row r="33" ht="39" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査の第10期分）は、いずれも業務内容そのものが進まない資料である。No.13がなければ仕様書４（2）のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の資料は、いずれも成果物の主張の根拠を推論・仮説から算定又は確認に引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する手段である。注3）本シートは令和8年7月29日の主張の棚卸し（全成果物46主張のMECEな分類）に基づく。各資料が確定する主張の詳細は、「受託者の自己点検」01・06シートに示している。</t>
         </is>
@@ -6843,14 +6893,14 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A32:J32"/>
     <mergeCell ref="C29:J29"/>
     <mergeCell ref="C30:J30"/>
     <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C27:J27"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="C31:J31"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I24">
+  <conditionalFormatting sqref="I5:I25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -6868,7 +6918,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2375,7 +2375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2458,1901 +2458,2029 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月25日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>計画骨子案
+施策体系新旧対照表
+計画素案 第4章・第5章</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9.2</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>同打合せで期限を令和8年9月2日（水）と設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>従業員数の重複計上の整理
+計画素案 第2章第3節・第6章第2節</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度の実績の推定方法</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第6章
+将来推計 第1〜3段階</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>了承済</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>R8.8.25</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>令和8年8月25日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr"/>
-    </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="J9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr"/>
-    </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="J10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr"/>
-    </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="J12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr"/>
-    </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr"/>
-    </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+      <c r="J15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="J16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr"/>
-    </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+      <c r="J17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>北海道・圏域との調整の場</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第4節</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="J45" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B45" s="4">
-        <f>COUNTIF(H5:H42,"完了")</f>
-        <v/>
-      </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B46" s="4">
-        <f>COUNTIF(H5:H42,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="B47" s="4">
-        <f>COUNTIF(H5:H42,"確認待ち")</f>
-        <v/>
-      </c>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="B48" s="4">
-        <f>COUNTIF(H5:H42,"未着手")</f>
-        <v/>
-      </c>
-      <c r="C48" s="5" t="inlineStr"/>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
       <c r="B49" s="4">
-        <f>COUNTIF(H5:H42,"対象外")</f>
+        <f>COUNTIF(H5:H46,"完了")</f>
         <v/>
       </c>
       <c r="C49" s="5" t="inlineStr"/>
@@ -4364,34 +4492,52 @@
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
     </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="B50" s="4">
+        <f>COUNTIF(H5:H46,"実施中")</f>
+        <v/>
+      </c>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="B51" s="4">
+        <f>COUNTIF(H5:H46,"確認待ち")</f>
+        <v/>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B52" s="4">
-        <f>COUNTIF(G5:G42,"発注者")</f>
+        <f>COUNTIF(H5:H46,"未着手")</f>
         <v/>
       </c>
       <c r="C52" s="5" t="inlineStr"/>
@@ -4404,13 +4550,13 @@
       <c r="J52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
         </is>
       </c>
       <c r="B53" s="4">
-        <f>COUNTIF(G5:G42,"発注者・3町")</f>
+        <f>COUNTIF(H5:H46,"対象外")</f>
         <v/>
       </c>
       <c r="C53" s="5" t="inlineStr"/>
@@ -4422,52 +4568,34 @@
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="B54" s="4">
-        <f>COUNTIF(G5:G42,"発注者・北海道")</f>
-        <v/>
-      </c>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町・北海道</t>
-        </is>
-      </c>
-      <c r="B55" s="4">
-        <f>COUNTIF(G5:G42,"発注者・3町・北海道")</f>
-        <v/>
-      </c>
-      <c r="C55" s="5" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B56" s="4">
-        <f>COUNTIF(G5:G42,"北海道")</f>
+        <f>COUNTIF(G5:G46,"発注者")</f>
         <v/>
       </c>
       <c r="C56" s="5" t="inlineStr"/>
@@ -4479,8 +4607,84 @@
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
     </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="B57" s="4">
+        <f>COUNTIF(G5:G46,"発注者・3町")</f>
+        <v/>
+      </c>
+      <c r="C57" s="5" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="B58" s="4">
+        <f>COUNTIF(G5:G46,"発注者・北海道")</f>
+        <v/>
+      </c>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="B59" s="4">
+        <f>COUNTIF(G5:G46,"発注者・3町・北海道")</f>
+        <v/>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B60" s="4">
+        <f>COUNTIF(G5:G46,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr"/>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -4488,11 +4692,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A58:J58"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A62:J62"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H42">
+  <conditionalFormatting sqref="H5:H46">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4510,7 +4714,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5640,7 +5844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5658,7 +5862,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料提供依頼一覧（21件）</t>
+          <t>資料提供依頼一覧（23件）</t>
         </is>
       </c>
     </row>
@@ -6332,12 +6536,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（月報・年報）の保険者控え（令和2年度〜令和7年度）</t>
+          <t>介護保険事業状況報告　年報（令和6年度・令和7年度）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>第3段階（給付費・保険料）の算定に用いる給付費の月次・年度の実績。あわせて第9期の給付費の計画乖離（代表KPI H15）の把握に用いる。見える化には年報ベースの値が収録されているが、月次の推移と直近年度の速報値は保険者控えによる。</t>
+          <t>第9期の令和6・7年度の確定値。見える化は年度途中で締めた値（令和6年度分は令和6年2月データ締め等）を収録しており、4月から3月までの通年の実績が確認できない。第3段階（給付費・保険料）の算定と、第9期の給付費の計画乖離（代表KPI H15）の把握に用いる。</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -6352,7 +6556,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -6362,18 +6566,18 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>提供予定（即時）</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>キックオフ会議のご指示により「令和8年実績」を年報・月報の実績に改める整理としたことに対応する</t>
+          <t>令和8年8月25日の進捗確認の打合せで合意。様式のままのExcelが望ましいがPDFでも可</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
@@ -6382,17 +6586,17 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>第7期（平成30〜令和2年度）の保険料条例</t>
+          <t>介護保険事業状況報告　月報（令和8年4月〜7月分）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>基準額が6,077円か5,900円かを確定する。</t>
+          <t>令和8年度は年報が出ないため、月報により各月の進捗を確認する。令和8年度の実績は本業務の期間中に確定しないため、月報により推移を把握したうえで見える化ベースの試算により推定する。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>第7期の保険料基準額</t>
+          <t>令和8年度の推定、第9期の中間評価の更新</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -6402,97 +6606,97 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>提供予定（即時）</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>見える化C1により6,077円を確認（R8.7.30）。依頼は解消</t>
+          <t>同打合せで、締まっているのは令和8年7月分までであることを確認した</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>給付実績データ（サービス別の利用者数・利用日数等）（令和5年度〜令和7年度）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
+          <t>サービス見込量の推定の基礎。月当たりの平均利用者数、利用者1人当たりの利用日数・回数。見える化のD系列では年度途中で締めた値となるサービスがあるため、保険者の給付実績により通年の値を確認する。</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>第2段階の見込量の精緻化、第3段階の給付費の算定</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.8.31</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>作成中</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.20と対応</t>
+          <t>同打合せで、3年前に提出された様式のExcelにより令和8年8月31日までにご提供いただくこととなった</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>第7期（平成30〜令和2年度）の保険料条例</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
+          <t>基準額が6,077円か5,900円かを確定する。</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>第7期の保険料基準額</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -6512,47 +6716,47 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.7と対応</t>
+          <t>見える化C1により6,077円を確認（R8.7.30）。依頼は解消</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -6562,47 +6766,47 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>受託者側で確認する</t>
+          <t>確認事項No.20と対応</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料の自己点検で、12件中5件がこの類であった。</t>
+          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -6612,52 +6816,52 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>受託者の自己点検に手順を記録</t>
+          <t>確認事項No.7と対応</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>見える化システムD49の指標定義</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>地域差指数の分解の可否</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>見える化システム・厚生労働省</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -6667,190 +6871,246 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>受託者側で出力を試行する</t>
+          <t>受託者側で確認する</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>―</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域【令和8年8月4日受領済】</t>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に収録されており、区域内124件を抽出して整理した。</t>
+          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料の自己点検で、12件中5件がこの類であった。</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定</t>
+          <t>会議資料・委員会資料の記述の正確性</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北海道・広域連合</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.15と対応。住まいと施設の公表名簿との突合 08シート</t>
+          <t>受託者の自己点検に手順を記録</t>
         </is>
       </c>
     </row>
     <row r="25" ht="56" customHeight="1">
       <c r="A25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>受託者側で出力を試行する</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域【令和8年8月4日受領済】</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に収録されており、区域内124件を抽出して整理した。</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>訪問・通所困難地域の判定</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>北海道・広域連合</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.15と対応。住まいと施設の公表名簿との突合 08シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。公表され次第。</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>公表待ち</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n">
+      <c r="B30" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>No.13 令和6〜8年度の施策・事業実績、事業量、対象</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="22" t="n"/>
-      <c r="I28" s="22" t="n"/>
-      <c r="J28" s="23" t="n"/>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地、区域内、No.21 介護保険事業状況報告（月報・年報）の保険者控、No.19 居住系・施設サービスの種別別受給者数と総合事</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="n"/>
-      <c r="E29" s="22" t="n"/>
-      <c r="F29" s="22" t="n"/>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="22" t="n"/>
-      <c r="I29" s="22" t="n"/>
-      <c r="J29" s="23" t="n"/>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.20 （受託者の作業）会議資料・委員会資料の作成時、No.15 第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D30" s="22" t="n"/>
@@ -6862,17 +7122,17 @@
       <c r="J30" s="23" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B31" s="21" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.2 訪問系・通所系事業所の運営規程における通常の、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.3 令和6年・令和7年の町別住民基本台帳人口（年、No.5 保険者機能強化推進交付金等の評価調書（令和4、No.6 国民健康保険団体連合会の給付実績情報と指定事、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス構成、No.9 決算書及び介護給付費準備基金の積立・取崩実績、No.11 第10期の政令改正の内容（所得段階・乗率・負、No.14 在宅生活改善調査・居所変更実態調査・介護人材、No.17 町別・サービス区分別の給付費（令和4〜7年度、No.18 指定事業所台帳（区域外事業所の所在地、区域内、No.21 介護保険事業状況報告　年報（令和6年度・令和、No.22 介護保険事業状況報告　月報（令和8年4月〜7、No.23 給付実績データ（サービス別の利用者数・利用日、No.19 居住系・施設サービスの種別別受給者数と総合事</t>
         </is>
       </c>
       <c r="D31" s="22" t="n"/>
@@ -6883,8 +7143,52 @@
       <c r="I31" s="22" t="n"/>
       <c r="J31" s="23" t="n"/>
     </row>
-    <row r="33" ht="39" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>No.10 第7期（平成30〜令和2年度）の保険料条例、No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.20 （受託者の作業）会議資料・委員会資料の作成時、No.15 第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="23" t="n"/>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>No.1 見える化B5a・B6a・B6bの令和8年3月、No.2 訪問系・通所系事業所の運営規程における通常の、No.4 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="23" t="n"/>
+    </row>
+    <row r="35" ht="39" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査の第10期分）は、いずれも業務内容そのものが進まない資料である。No.13がなければ仕様書４（2）のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の資料は、いずれも成果物の主張の根拠を推論・仮説から算定又は確認に引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する手段である。注3）本シートは令和8年7月29日の主張の棚卸し（全成果物46主張のMECEな分類）に基づく。各資料が確定する主張の詳細は、「受託者の自己点検」01・06シートに示している。</t>
         </is>
@@ -6893,14 +7197,14 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C29:J29"/>
     <mergeCell ref="C30:J30"/>
-    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="C32:J32"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C31:J31"/>
-    <mergeCell ref="A33:J33"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I25">
+  <conditionalFormatting sqref="I5:I27">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -6918,7 +7222,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1780,6 +1780,24 @@
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"代替により解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"一部解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+      <formula>"提供予定（即時）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+      <formula>"作成中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+      <formula>"了承済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+      <formula>"対応中"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F5:F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2359,6 +2377,24 @@
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"代替により解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"一部解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+      <formula>"提供予定（即時）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+      <formula>"作成中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+      <formula>"了承済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+      <formula>"対応中"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F5:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2375,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2458,518 +2494,523 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>認定に要する日数の扱い</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>中間報告 第3節
+計画素案 第2章・第5章</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>令和8年8月28日受領の集計帳票により判明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.8.25</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
       <c r="A9" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr"/>
-    </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="88" customHeight="1">
       <c r="A11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+      <c r="J12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr"/>
-    </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -2989,1310 +3030,1310 @@
     </row>
     <row r="16" ht="88" customHeight="1">
       <c r="A16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="J17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="88" customHeight="1">
       <c r="A29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J41" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
@@ -4309,197 +4350,224 @@
     </row>
     <row r="44" ht="88" customHeight="1">
       <c r="A44" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J46" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr"/>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B49" s="4">
-        <f>COUNTIF(H5:H46,"完了")</f>
-        <v/>
-      </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B50" s="4">
-        <f>COUNTIF(H5:H46,"実施中")</f>
+        <f>COUNTIF(H5:H47,"完了")</f>
         <v/>
       </c>
       <c r="C50" s="5" t="inlineStr"/>
@@ -4512,13 +4580,13 @@
       <c r="J50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B51" s="4">
-        <f>COUNTIF(H5:H46,"確認待ち")</f>
+        <f>COUNTIF(H5:H47,"実施中")</f>
         <v/>
       </c>
       <c r="C51" s="5" t="inlineStr"/>
@@ -4531,13 +4599,13 @@
       <c r="J51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B52" s="4">
-        <f>COUNTIF(H5:H46,"未着手")</f>
+        <f>COUNTIF(H5:H47,"確認待ち")</f>
         <v/>
       </c>
       <c r="C52" s="5" t="inlineStr"/>
@@ -4550,13 +4618,13 @@
       <c r="J52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B53" s="4">
-        <f>COUNTIF(H5:H46,"対象外")</f>
+        <f>COUNTIF(H5:H47,"未着手")</f>
         <v/>
       </c>
       <c r="C53" s="5" t="inlineStr"/>
@@ -4568,53 +4636,53 @@
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
     </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B54" s="4">
+        <f>COUNTIF(H5:H47,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B56" s="4">
-        <f>COUNTIF(G5:G46,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C56" s="5" t="inlineStr"/>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B57" s="4">
-        <f>COUNTIF(G5:G46,"発注者・3町")</f>
+        <f>COUNTIF(G5:G47,"発注者")</f>
         <v/>
       </c>
       <c r="C57" s="5" t="inlineStr"/>
@@ -4629,11 +4697,11 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B58" s="4">
-        <f>COUNTIF(G5:G46,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G47,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C58" s="5" t="inlineStr"/>
@@ -4648,11 +4716,11 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B59" s="4">
-        <f>COUNTIF(G5:G46,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G47,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C59" s="5" t="inlineStr"/>
@@ -4667,11 +4735,11 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B60" s="4">
-        <f>COUNTIF(G5:G46,"北海道")</f>
+        <f>COUNTIF(G5:G47,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C60" s="5" t="inlineStr"/>
@@ -4683,8 +4751,27 @@
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B61" s="4">
+        <f>COUNTIF(G5:G47,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr"/>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -4693,10 +4780,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="A63:J63"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H46">
+  <conditionalFormatting sqref="H5:H47">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4712,9 +4799,27 @@
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"代替により解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"一部解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+      <formula>"提供予定（即時）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+      <formula>"作成中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+      <formula>"了承済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+      <formula>"対応中"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5282,6 +5387,24 @@
     </cfRule>
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"代替により解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"一部解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+      <formula>"提供予定（即時）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+      <formula>"作成中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+      <formula>"了承済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+      <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -5754,66 +5877,138 @@
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"代替により解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"一部解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+      <formula>"提供予定（即時）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+      <formula>"作成中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+      <formula>"了承済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+      <formula>"対応中"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F8">
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="1">
       <formula>"実施中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
+      <formula>"代替により解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
+      <formula>"一部解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="1">
+      <formula>"提供予定（即時）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="1">
+      <formula>"作成中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
+      <formula>"了承済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="1">
+      <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G8">
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="24" operator="equal" dxfId="1">
       <formula>"実施中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="26" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="0">
+      <formula>"代替により解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="1">
+      <formula>"一部解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="equal" dxfId="1">
+      <formula>"提供予定（即時）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="1">
+      <formula>"作成中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
+      <formula>"了承済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="1">
+      <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H8">
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="34" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="35" operator="equal" dxfId="1">
       <formula>"実施中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="38" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="39" operator="equal" dxfId="0">
+      <formula>"代替により解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="40" operator="equal" dxfId="1">
+      <formula>"一部解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="41" operator="equal" dxfId="1">
+      <formula>"提供予定（即時）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="equal" dxfId="1">
+      <formula>"作成中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="43" operator="equal" dxfId="0">
+      <formula>"了承済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="44" operator="equal" dxfId="1">
+      <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D8">
-    <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="45" operator="equal" dxfId="0">
       <formula>"受領済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="22" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="46" operator="equal" dxfId="2">
       <formula>"一部受領"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="23" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="47" operator="equal" dxfId="3">
       <formula>"未受領"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6066,12 +6261,12 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.6・38と対応</t>
+          <t>令和8年8月28日に「保険者機能強化推進交付金等（市町村）に係る全国集計結果」令和6〜8年度を受領した。3町の項目別得点が判明したため、評価調書そのものがなくても分析できる。ただし0点の項目が未実施か要件未充足かの別は依然として不明である</t>
         </is>
       </c>
     </row>
@@ -7220,6 +7415,24 @@
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"代替により解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"一部解消"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+      <formula>"提供予定（即時）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+      <formula>"作成中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+      <formula>"了承済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+      <formula>"対応中"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="I5:I27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2411,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2494,2137 +2494,2233 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度の給付費の集計が一致しない</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>給付実績データの受領点検
+将来推計 第2・3段階</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>給付実績データに含まれる個人情報の取扱い</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>給付実績データの受領点検
+将来推計 第2・3段階</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>受託者は集計シートのみを用い、個票は成果品に収録しない。ご指示がない場合は業務終了後に消去し記録を残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>代表KPI H15の分母の定義</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第4章 資料1
+中間報告 第3節</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.8.25</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>対応中</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr"/>
-    </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="J15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr"/>
-    </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+      <c r="J16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="J17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>北海道・圏域との調整の場</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第4節</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="J44" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B50" s="4">
-        <f>COUNTIF(H5:H47,"完了")</f>
-        <v/>
-      </c>
-      <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B51" s="4">
-        <f>COUNTIF(H5:H47,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="B52" s="4">
-        <f>COUNTIF(H5:H47,"確認待ち")</f>
-        <v/>
-      </c>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
       <c r="B53" s="4">
-        <f>COUNTIF(H5:H47,"未着手")</f>
+        <f>COUNTIF(H5:H50,"完了")</f>
         <v/>
       </c>
       <c r="C53" s="5" t="inlineStr"/>
@@ -4637,13 +4733,13 @@
       <c r="J53" s="5" t="inlineStr"/>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B54" s="4">
-        <f>COUNTIF(H5:H47,"対象外")</f>
+        <f>COUNTIF(H5:H50,"実施中")</f>
         <v/>
       </c>
       <c r="C54" s="5" t="inlineStr"/>
@@ -4655,34 +4751,52 @@
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
     </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr"/>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="B55" s="4">
+        <f>COUNTIF(H5:H50,"確認待ち")</f>
+        <v/>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B56" s="4">
+        <f>COUNTIF(H5:H50,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
         </is>
       </c>
       <c r="B57" s="4">
-        <f>COUNTIF(G5:G47,"発注者")</f>
+        <f>COUNTIF(H5:H50,"対象外")</f>
         <v/>
       </c>
       <c r="C57" s="5" t="inlineStr"/>
@@ -4694,52 +4808,34 @@
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="B58" s="4">
-        <f>COUNTIF(G5:G47,"発注者・3町")</f>
-        <v/>
-      </c>
-      <c r="C58" s="5" t="inlineStr"/>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="B59" s="4">
-        <f>COUNTIF(G5:G47,"発注者・北海道")</f>
-        <v/>
-      </c>
-      <c r="C59" s="5" t="inlineStr"/>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B60" s="4">
-        <f>COUNTIF(G5:G47,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G50,"発注者")</f>
         <v/>
       </c>
       <c r="C60" s="5" t="inlineStr"/>
@@ -4754,11 +4850,11 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B61" s="4">
-        <f>COUNTIF(G5:G47,"北海道")</f>
+        <f>COUNTIF(G5:G50,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C61" s="5" t="inlineStr"/>
@@ -4770,8 +4866,65 @@
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
     </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="B62" s="4">
+        <f>COUNTIF(G5:G50,"発注者・北海道")</f>
+        <v/>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="B63" s="4">
+        <f>COUNTIF(G5:G50,"発注者・3町・北海道")</f>
+        <v/>
+      </c>
+      <c r="C63" s="5" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B64" s="4">
+        <f>COUNTIF(G5:G50,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -4780,10 +4933,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A66:J66"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H47">
+  <conditionalFormatting sqref="H5:H50">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4819,7 +4972,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6861,12 +7014,12 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>作成中</t>
+          <t>解消</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>同打合せで、3年前に提出された様式のExcelにより令和8年8月31日までにご提供いただくこととなった</t>
+          <t>令和8年8月28日に12ファイルを受領した（大雪地区広域連合及び構成3町の令和6〜8年度）。受領ファイルの第1シートには被保険者の氏名・生年月日等の個票が含まれるため、集計シートのみを用いる。個人情報の取扱いについて確認事項No.44を起こした</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1774,28 +1774,31 @@
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"了承済（保管せず廃棄）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"代替により解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
       <formula>"一部解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
       <formula>"提供予定（即時）"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
       <formula>"作成中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"了承済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
       <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2371,28 +2374,31 @@
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"了承済（保管せず廃棄）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"代替により解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
       <formula>"一部解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
       <formula>"提供予定（即時）"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
       <formula>"作成中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"了承済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
       <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2411,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2494,722 +2500,727 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>計画作成支援ツールの実績値シートの確認</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>給付実績データの受領点検 04シート
+将来推計 第3段階</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>第3段階（給付費・保険料）の算定に用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>受託者は集計シートのみを用い、個票は成果品に収録しない。ご指示がない場合は業務終了後に消去し記録を残す</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>了承済（保管せず廃棄）</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>R8.8.28</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.8.25</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1">
       <c r="A13" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
-    </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="88" customHeight="1">
       <c r="A15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
+      <c r="J16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="J17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -3229,1310 +3240,1310 @@
     </row>
     <row r="20" ht="88" customHeight="1">
       <c r="A20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="88" customHeight="1">
       <c r="A33" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J45" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
@@ -4549,197 +4560,224 @@
     </row>
     <row r="48" ht="88" customHeight="1">
       <c r="A48" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="J50" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr"/>
-      <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="3" t="inlineStr"/>
-      <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B53" s="4">
-        <f>COUNTIF(H5:H50,"完了")</f>
-        <v/>
-      </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr"/>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B54" s="4">
-        <f>COUNTIF(H5:H50,"実施中")</f>
+        <f>COUNTIF(H5:H51,"完了")</f>
         <v/>
       </c>
       <c r="C54" s="5" t="inlineStr"/>
@@ -4752,13 +4790,13 @@
       <c r="J54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B55" s="4">
-        <f>COUNTIF(H5:H50,"確認待ち")</f>
+        <f>COUNTIF(H5:H51,"実施中")</f>
         <v/>
       </c>
       <c r="C55" s="5" t="inlineStr"/>
@@ -4771,13 +4809,13 @@
       <c r="J55" s="5" t="inlineStr"/>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B56" s="4">
-        <f>COUNTIF(H5:H50,"未着手")</f>
+        <f>COUNTIF(H5:H51,"確認待ち")</f>
         <v/>
       </c>
       <c r="C56" s="5" t="inlineStr"/>
@@ -4790,13 +4828,13 @@
       <c r="J56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B57" s="4">
-        <f>COUNTIF(H5:H50,"対象外")</f>
+        <f>COUNTIF(H5:H51,"未着手")</f>
         <v/>
       </c>
       <c r="C57" s="5" t="inlineStr"/>
@@ -4808,53 +4846,53 @@
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
     </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B58" s="4">
+        <f>COUNTIF(H5:H51,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr"/>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="3" t="inlineStr"/>
-      <c r="J59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B60" s="4">
-        <f>COUNTIF(G5:G50,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B61" s="4">
-        <f>COUNTIF(G5:G50,"発注者・3町")</f>
+        <f>COUNTIF(G5:G51,"発注者")</f>
         <v/>
       </c>
       <c r="C61" s="5" t="inlineStr"/>
@@ -4869,11 +4907,11 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B62" s="4">
-        <f>COUNTIF(G5:G50,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G51,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C62" s="5" t="inlineStr"/>
@@ -4888,11 +4926,11 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B63" s="4">
-        <f>COUNTIF(G5:G50,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G51,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C63" s="5" t="inlineStr"/>
@@ -4907,11 +4945,11 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B64" s="4">
-        <f>COUNTIF(G5:G50,"北海道")</f>
+        <f>COUNTIF(G5:G51,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C64" s="5" t="inlineStr"/>
@@ -4923,8 +4961,27 @@
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
     </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="16" t="inlineStr">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B65" s="4">
+        <f>COUNTIF(G5:G51,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="5" t="inlineStr"/>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -4933,10 +4990,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A67:J67"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H50">
+  <conditionalFormatting sqref="H5:H51">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4946,33 +5003,36 @@
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"了承済（保管せず廃棄）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"代替により解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
       <formula>"一部解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
       <formula>"提供予定（即時）"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
       <formula>"作成中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"了承済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
       <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5535,28 +5595,31 @@
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"了承済（保管せず廃棄）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"代替により解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
       <formula>"一部解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
       <formula>"提供予定（即時）"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
       <formula>"作成中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"了承済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
       <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6024,144 +6087,156 @@
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"了承済（保管せず廃棄）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"代替により解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
       <formula>"一部解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
       <formula>"提供予定（即時）"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
       <formula>"作成中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"了承済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
       <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F8">
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="1">
       <formula>"実施中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
+      <formula>"了承済（保管せず廃棄）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"代替により解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="1">
       <formula>"一部解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="1">
       <formula>"提供予定（即時）"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="1">
       <formula>"作成中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
       <formula>"了承済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="22" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="24" operator="equal" dxfId="1">
       <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G8">
-    <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="24" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="26" operator="equal" dxfId="1">
       <formula>"実施中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="25" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="26" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="0">
+      <formula>"了承済（保管せず廃棄）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="27" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="30" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="28" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="0">
       <formula>"代替により解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="29" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="1">
       <formula>"一部解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="30" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="1">
       <formula>"提供予定（即時）"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="31" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="34" operator="equal" dxfId="1">
       <formula>"作成中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="35" operator="equal" dxfId="0">
       <formula>"了承済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="33" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="1">
       <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H8">
-    <cfRule type="cellIs" priority="34" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="35" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="38" operator="equal" dxfId="1">
       <formula>"実施中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="36" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="39" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="37" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="40" operator="equal" dxfId="0">
+      <formula>"了承済（保管せず廃棄）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="41" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="38" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="42" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="39" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="43" operator="equal" dxfId="0">
       <formula>"代替により解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="40" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="44" operator="equal" dxfId="1">
       <formula>"一部解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="41" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="45" operator="equal" dxfId="1">
       <formula>"提供予定（即時）"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="42" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="46" operator="equal" dxfId="1">
       <formula>"作成中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="43" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="47" operator="equal" dxfId="0">
       <formula>"了承済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="44" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="48" operator="equal" dxfId="1">
       <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D8">
-    <cfRule type="cellIs" priority="45" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="49" operator="equal" dxfId="0">
       <formula>"受領済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="46" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="50" operator="equal" dxfId="2">
       <formula>"一部受領"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="47" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="51" operator="equal" dxfId="3">
       <formula>"未受領"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7562,28 +7637,31 @@
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"確認待ち"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"了承済（保管せず廃棄）"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"未着手"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
       <formula>"対象外"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"代替により解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
       <formula>"一部解消"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
       <formula>"提供予定（即時）"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
       <formula>"作成中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"了承済"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
       <formula>"対応中"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,773 +2500,779 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>総合事業実施状況調査の受領点検
+素案 第3章第1節・第2節
+H05の基準値</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>第9期の通いの場と地域支援事業の評価に用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.8.25</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1">
       <c r="A14" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="88" customHeight="1">
       <c r="A16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="J17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -3286,1310 +3292,1310 @@
     </row>
     <row r="21" ht="88" customHeight="1">
       <c r="A21" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr"/>
     </row>
     <row r="34" ht="88" customHeight="1">
       <c r="A34" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J46" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -4606,197 +4612,224 @@
     </row>
     <row r="49" ht="88" customHeight="1">
       <c r="A49" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr"/>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B54" s="4">
-        <f>COUNTIF(H5:H51,"完了")</f>
-        <v/>
-      </c>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B55" s="4">
-        <f>COUNTIF(H5:H51,"実施中")</f>
+        <f>COUNTIF(H5:H52,"完了")</f>
         <v/>
       </c>
       <c r="C55" s="5" t="inlineStr"/>
@@ -4809,13 +4842,13 @@
       <c r="J55" s="5" t="inlineStr"/>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B56" s="4">
-        <f>COUNTIF(H5:H51,"確認待ち")</f>
+        <f>COUNTIF(H5:H52,"実施中")</f>
         <v/>
       </c>
       <c r="C56" s="5" t="inlineStr"/>
@@ -4828,13 +4861,13 @@
       <c r="J56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B57" s="4">
-        <f>COUNTIF(H5:H51,"未着手")</f>
+        <f>COUNTIF(H5:H52,"確認待ち")</f>
         <v/>
       </c>
       <c r="C57" s="5" t="inlineStr"/>
@@ -4847,13 +4880,13 @@
       <c r="J57" s="5" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B58" s="4">
-        <f>COUNTIF(H5:H51,"対象外")</f>
+        <f>COUNTIF(H5:H52,"未着手")</f>
         <v/>
       </c>
       <c r="C58" s="5" t="inlineStr"/>
@@ -4865,53 +4898,53 @@
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
     </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B59" s="4">
+        <f>COUNTIF(H5:H52,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr"/>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr"/>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B61" s="4">
-        <f>COUNTIF(G5:G51,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C61" s="5" t="inlineStr"/>
-      <c r="D61" s="5" t="inlineStr"/>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="5" t="inlineStr"/>
-      <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B62" s="4">
-        <f>COUNTIF(G5:G51,"発注者・3町")</f>
+        <f>COUNTIF(G5:G52,"発注者")</f>
         <v/>
       </c>
       <c r="C62" s="5" t="inlineStr"/>
@@ -4926,11 +4959,11 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B63" s="4">
-        <f>COUNTIF(G5:G51,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G52,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C63" s="5" t="inlineStr"/>
@@ -4945,11 +4978,11 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B64" s="4">
-        <f>COUNTIF(G5:G51,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G52,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C64" s="5" t="inlineStr"/>
@@ -4964,11 +4997,11 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B65" s="4">
-        <f>COUNTIF(G5:G51,"北海道")</f>
+        <f>COUNTIF(G5:G52,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C65" s="5" t="inlineStr"/>
@@ -4980,8 +5013,27 @@
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr"/>
     </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B66" s="4">
+        <f>COUNTIF(G5:G52,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C66" s="5" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr"/>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -4990,10 +5042,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A68:J68"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H51">
+  <conditionalFormatting sqref="H5:H52">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5032,7 +5084,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,825 +2500,831 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>中間報告会議の議事録の記載の確認</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月26日付の議事録を校正した（13件）。本文を変えずにご確認をお願いする事項が2件ある。①開催日について、議事録は令和8年8月26日（水）、受託者の記録は令和8年8月25日としている。令和8年8月26日は水曜日、8月25日は火曜日であり、曜日は議事録の記載と一致する。どちらが正しいか。②年報・月報について「令和8年8月27日 受領」とあるが、受託者が令和8年8月28日に受領した9件に年報・月報は含まれていない。資料No.21・22は受託者の記録では未受領である。別便でのご送付があったか。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>中間報告会議議事録
+業務工程管理表
+必要事項の一覧</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>ご回答により議事録・工程管理表・必要事項の一覧を更新する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.8.25</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>令和8年8月25日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
       <c r="A15" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="88" customHeight="1">
       <c r="A17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -3338,1310 +3344,1310 @@
     </row>
     <row r="22" ht="88" customHeight="1">
       <c r="A22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr"/>
     </row>
     <row r="35" ht="88" customHeight="1">
       <c r="A35" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -4658,197 +4664,224 @@
     </row>
     <row r="50" ht="88" customHeight="1">
       <c r="A50" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr">
+      <c r="J52" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr"/>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="J53" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr"/>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B55" s="4">
-        <f>COUNTIF(H5:H52,"完了")</f>
-        <v/>
-      </c>
-      <c r="C55" s="5" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B56" s="4">
-        <f>COUNTIF(H5:H52,"実施中")</f>
+        <f>COUNTIF(H5:H53,"完了")</f>
         <v/>
       </c>
       <c r="C56" s="5" t="inlineStr"/>
@@ -4861,13 +4894,13 @@
       <c r="J56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B57" s="4">
-        <f>COUNTIF(H5:H52,"確認待ち")</f>
+        <f>COUNTIF(H5:H53,"実施中")</f>
         <v/>
       </c>
       <c r="C57" s="5" t="inlineStr"/>
@@ -4880,13 +4913,13 @@
       <c r="J57" s="5" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B58" s="4">
-        <f>COUNTIF(H5:H52,"未着手")</f>
+        <f>COUNTIF(H5:H53,"確認待ち")</f>
         <v/>
       </c>
       <c r="C58" s="5" t="inlineStr"/>
@@ -4899,13 +4932,13 @@
       <c r="J58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B59" s="4">
-        <f>COUNTIF(H5:H52,"対象外")</f>
+        <f>COUNTIF(H5:H53,"未着手")</f>
         <v/>
       </c>
       <c r="C59" s="5" t="inlineStr"/>
@@ -4917,53 +4950,53 @@
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
     </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B60" s="4">
+        <f>COUNTIF(H5:H53,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr"/>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B62" s="4">
-        <f>COUNTIF(G5:G52,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="5" t="inlineStr"/>
-      <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B63" s="4">
-        <f>COUNTIF(G5:G52,"発注者・3町")</f>
+        <f>COUNTIF(G5:G53,"発注者")</f>
         <v/>
       </c>
       <c r="C63" s="5" t="inlineStr"/>
@@ -4978,11 +5011,11 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B64" s="4">
-        <f>COUNTIF(G5:G52,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G53,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C64" s="5" t="inlineStr"/>
@@ -4997,11 +5030,11 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B65" s="4">
-        <f>COUNTIF(G5:G52,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G53,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C65" s="5" t="inlineStr"/>
@@ -5016,11 +5049,11 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B66" s="4">
-        <f>COUNTIF(G5:G52,"北海道")</f>
+        <f>COUNTIF(G5:G53,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C66" s="5" t="inlineStr"/>
@@ -5032,8 +5065,27 @@
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
     </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B67" s="4">
+        <f>COUNTIF(G5:G53,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr"/>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5041,11 +5093,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A69:J69"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A68:J68"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H52">
+  <conditionalFormatting sqref="H5:H53">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5084,7 +5136,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2905,7 +2905,7 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>同打合せで期限を令和8年9月2日（水）と設定</t>
+          <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -664,7 +664,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。状況基準日：令和8年8月25日。</t>
+          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。状況基準日：令和8年8月26日。</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>注1）「対応する業務内容」は仕様書４（1）〜（12）の番号。01シートと対応する。注2）「提出期日」は発注者が指定する期日を記入する欄。仕様書５は各工程終了後の成果物提出と発注者確認を次工程の条件としているため、期日を月ごとに定めていただく必要がある。注3）令和8年8月25日時点で、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理、（6）計画書の作成の一部を先行実施している。先行実施分は8月・9月・10月の工程に前倒しで反映される。注4）仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の給付実績・事業実績の確定時期によっては後ろ倒しとなる可能性がある。キックオフ会議で工程の調整を協議したい。</t>
+          <t>注1）「対応する業務内容」は仕様書４（1）〜（12）の番号。01シートと対応する。注2）「提出期日」は発注者が指定する期日を記入する欄。仕様書５は各工程終了後の成果物提出と発注者確認を次工程の条件としているため、期日を月ごとに定めていただく必要がある。注3）令和8年8月26日時点で、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理、（6）計画書の作成の一部を先行実施している。先行実施分は8月・9月・10月の工程に前倒しで反映される。注4）仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の給付実績・事業実績の確定時期によっては後ろ倒しとなる可能性がある。キックオフ会議で工程の調整を協議したい。</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>中間報告会議の議事録の記載の確認</t>
+          <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月26日付の議事録を校正した（13件）。本文を変えずにご確認をお願いする事項が2件ある。①開催日について、議事録は令和8年8月26日（水）、受託者の記録は令和8年8月25日としている。令和8年8月26日は水曜日、8月25日は火曜日であり、曜日は議事録の記載と一致する。どちらが正しいか。②年報・月報について「令和8年8月27日 受領」とあるが、受託者が令和8年8月28日に受領した9件に年報・月報は含まれていない。資料No.21・22は受託者の記録では未受領である。別便でのご送付があったか。</t>
+          <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2534,19 +2534,19 @@
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>了承済</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8.28</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>ご回答により議事録・工程管理表・必要事項の一覧を更新する</t>
+          <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月25日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
+          <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>R8.8.25</t>
+          <t>R8.8.26</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>令和8年8月25日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
+          <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月25日の進捗確認の打合せで合意。様式のままのExcelが望ましいがPDFでも可</t>
+          <t>令和8年8月26日の進捗確認の打合せで合意。様式のままのExcelが望ましいがPDFでも可</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,877 +2500,883 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>年報・月報の受領に伴う確認</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>年報月報の受領点検
+将来推計 第3段階
+素案 第6章第3節・第6節</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>①は第10期の保険料算定を止めている。最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
       <c r="A16" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr"/>
     </row>
     <row r="18" ht="88" customHeight="1">
       <c r="A18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -3390,1310 +3396,1310 @@
     </row>
     <row r="23" ht="88" customHeight="1">
       <c r="A23" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr"/>
     </row>
     <row r="36" ht="88" customHeight="1">
       <c r="A36" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr">
+      <c r="J48" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -4710,197 +4716,224 @@
     </row>
     <row r="51" ht="88" customHeight="1">
       <c r="A51" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J53" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="88" customHeight="1">
-      <c r="A53" s="4" t="n">
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="J54" s="11" t="inlineStr"/>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B56" s="4">
-        <f>COUNTIF(H5:H53,"完了")</f>
-        <v/>
-      </c>
-      <c r="C56" s="5" t="inlineStr"/>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B57" s="4">
-        <f>COUNTIF(H5:H53,"実施中")</f>
+        <f>COUNTIF(H5:H54,"完了")</f>
         <v/>
       </c>
       <c r="C57" s="5" t="inlineStr"/>
@@ -4913,13 +4946,13 @@
       <c r="J57" s="5" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B58" s="4">
-        <f>COUNTIF(H5:H53,"確認待ち")</f>
+        <f>COUNTIF(H5:H54,"実施中")</f>
         <v/>
       </c>
       <c r="C58" s="5" t="inlineStr"/>
@@ -4932,13 +4965,13 @@
       <c r="J58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B59" s="4">
-        <f>COUNTIF(H5:H53,"未着手")</f>
+        <f>COUNTIF(H5:H54,"確認待ち")</f>
         <v/>
       </c>
       <c r="C59" s="5" t="inlineStr"/>
@@ -4951,13 +4984,13 @@
       <c r="J59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B60" s="4">
-        <f>COUNTIF(H5:H53,"対象外")</f>
+        <f>COUNTIF(H5:H54,"未着手")</f>
         <v/>
       </c>
       <c r="C60" s="5" t="inlineStr"/>
@@ -4969,53 +5002,53 @@
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B61" s="4">
+        <f>COUNTIF(H5:H54,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr"/>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr"/>
-      <c r="D62" s="3" t="inlineStr"/>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr"/>
-      <c r="H62" s="3" t="inlineStr"/>
-      <c r="I62" s="3" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B63" s="4">
-        <f>COUNTIF(G5:G53,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C63" s="5" t="inlineStr"/>
-      <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="5" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B64" s="4">
-        <f>COUNTIF(G5:G53,"発注者・3町")</f>
+        <f>COUNTIF(G5:G54,"発注者")</f>
         <v/>
       </c>
       <c r="C64" s="5" t="inlineStr"/>
@@ -5030,11 +5063,11 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B65" s="4">
-        <f>COUNTIF(G5:G53,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G54,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C65" s="5" t="inlineStr"/>
@@ -5049,11 +5082,11 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B66" s="4">
-        <f>COUNTIF(G5:G53,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G54,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C66" s="5" t="inlineStr"/>
@@ -5068,11 +5101,11 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B67" s="4">
-        <f>COUNTIF(G5:G53,"北海道")</f>
+        <f>COUNTIF(G5:G54,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C67" s="5" t="inlineStr"/>
@@ -5084,8 +5117,27 @@
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr"/>
     </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B68" s="4">
+        <f>COUNTIF(G5:G54,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C68" s="5" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr"/>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5093,11 +5145,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A69:J69"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A70:J70"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H53">
+  <conditionalFormatting sqref="H5:H54">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5136,7 +5188,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,929 +2500,933 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>月報の値の接続のずれ（ご報告）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>年報月報の受領点検 04シート</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>計画本文への影響はない。記録として残すもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>①は第10期の保険料算定を止めている。最優先</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
       <c r="A17" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="88" customHeight="1">
       <c r="A19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -3442,1310 +3446,1310 @@
     </row>
     <row r="24" ht="88" customHeight="1">
       <c r="A24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr"/>
     </row>
     <row r="37" ht="88" customHeight="1">
       <c r="A37" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -4762,197 +4766,224 @@
     </row>
     <row r="52" ht="88" customHeight="1">
       <c r="A52" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="88" customHeight="1">
-      <c r="A53" s="4" t="n">
+      <c r="J53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="J54" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="88" customHeight="1">
-      <c r="A54" s="4" t="n">
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr"/>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="J55" s="11" t="inlineStr"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr"/>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B57" s="4">
-        <f>COUNTIF(H5:H54,"完了")</f>
-        <v/>
-      </c>
-      <c r="C57" s="5" t="inlineStr"/>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B58" s="4">
-        <f>COUNTIF(H5:H54,"実施中")</f>
+        <f>COUNTIF(H5:H55,"完了")</f>
         <v/>
       </c>
       <c r="C58" s="5" t="inlineStr"/>
@@ -4965,13 +4996,13 @@
       <c r="J58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B59" s="4">
-        <f>COUNTIF(H5:H54,"確認待ち")</f>
+        <f>COUNTIF(H5:H55,"実施中")</f>
         <v/>
       </c>
       <c r="C59" s="5" t="inlineStr"/>
@@ -4984,13 +5015,13 @@
       <c r="J59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B60" s="4">
-        <f>COUNTIF(H5:H54,"未着手")</f>
+        <f>COUNTIF(H5:H55,"確認待ち")</f>
         <v/>
       </c>
       <c r="C60" s="5" t="inlineStr"/>
@@ -5003,13 +5034,13 @@
       <c r="J60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B61" s="4">
-        <f>COUNTIF(H5:H54,"対象外")</f>
+        <f>COUNTIF(H5:H55,"未着手")</f>
         <v/>
       </c>
       <c r="C61" s="5" t="inlineStr"/>
@@ -5021,53 +5052,53 @@
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
     </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B62" s="4">
+        <f>COUNTIF(H5:H55,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr"/>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr"/>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B64" s="4">
-        <f>COUNTIF(G5:G54,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C64" s="5" t="inlineStr"/>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
+      <c r="C64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B65" s="4">
-        <f>COUNTIF(G5:G54,"発注者・3町")</f>
+        <f>COUNTIF(G5:G55,"発注者")</f>
         <v/>
       </c>
       <c r="C65" s="5" t="inlineStr"/>
@@ -5082,11 +5113,11 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B66" s="4">
-        <f>COUNTIF(G5:G54,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G55,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C66" s="5" t="inlineStr"/>
@@ -5101,11 +5132,11 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B67" s="4">
-        <f>COUNTIF(G5:G54,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G55,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C67" s="5" t="inlineStr"/>
@@ -5120,11 +5151,11 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B68" s="4">
-        <f>COUNTIF(G5:G54,"北海道")</f>
+        <f>COUNTIF(G5:G55,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C68" s="5" t="inlineStr"/>
@@ -5136,8 +5167,27 @@
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr"/>
     </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B69" s="4">
+        <f>COUNTIF(G5:G55,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr"/>
+      <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr"/>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5146,10 +5196,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A71:J71"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H54">
+  <conditionalFormatting sqref="H5:H55">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5188,7 +5238,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,11 +2500,11 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>(2)</t>
+          <t>(5)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -2514,17 +2514,18 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
+          <t>令和8年8月28日に令和6年度決算書（介護保険特別会計）を受領し、年報の様式4と対照した結果、歳入10項目・歳出12項目のすべてで金額が一致した。次の3点のご確認をお願いする。①基金の名称について、決算書は「介護保険事業財政調整基金」、年報は「介護給付費準備基金」である。残高は一致するため実質的に同一のものと解しているが、計画本文にどちらを用いるか。条例上の名称をご教示いただきたい。②決算書の地域支援事業費に「一般介護予防事業費」の項がなく、年報の様式4でも同項は0円である。総合事業の実施状況に関する調査では介護予防普及啓発事業を3町とも実施しているため、どの科目で執行されているか。③保険料の不納欠損額が決算書646,812円・年報645,312円、収入未済額が決算書1,361,675円・年報1,363,175円で、区分が1,500円分だけ異なる。調定額・収納額は一致する。計画本文に用いる値をどちらとするか。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 04シート</t>
+          <t>令和6年度決算書の受領点検 03シート
+素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -2544,935 +2545,939 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>計画本文への影響はない。記録として残すもの</t>
+          <t>いずれも金額の総額に影響しない。名称と科目の確認である</t>
         </is>
       </c>
     </row>
     <row r="6" ht="88" customHeight="1">
       <c r="A6" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>月報の値の接続のずれ（ご報告）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>年報月報の受領点検 04シート</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>計画本文への影響はない。記録として残すもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>①は第10期の保険料算定を止めている。最優先</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1">
       <c r="A18" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="88" customHeight="1">
       <c r="A20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -3492,1310 +3497,1310 @@
     </row>
     <row r="25" ht="88" customHeight="1">
       <c r="A25" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr"/>
     </row>
     <row r="38" ht="88" customHeight="1">
       <c r="A38" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="J50" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -4812,197 +4817,224 @@
     </row>
     <row r="53" ht="88" customHeight="1">
       <c r="A53" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54" ht="88" customHeight="1">
-      <c r="A54" s="4" t="n">
+      <c r="J54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="J55" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="88" customHeight="1">
-      <c r="A55" s="4" t="n">
+    <row r="56" ht="88" customHeight="1">
+      <c r="A56" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr"/>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="J56" s="11" t="inlineStr"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B58" s="4">
-        <f>COUNTIF(H5:H55,"完了")</f>
-        <v/>
-      </c>
-      <c r="C58" s="5" t="inlineStr"/>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B59" s="4">
-        <f>COUNTIF(H5:H55,"実施中")</f>
+        <f>COUNTIF(H5:H56,"完了")</f>
         <v/>
       </c>
       <c r="C59" s="5" t="inlineStr"/>
@@ -5015,13 +5047,13 @@
       <c r="J59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B60" s="4">
-        <f>COUNTIF(H5:H55,"確認待ち")</f>
+        <f>COUNTIF(H5:H56,"実施中")</f>
         <v/>
       </c>
       <c r="C60" s="5" t="inlineStr"/>
@@ -5034,13 +5066,13 @@
       <c r="J60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B61" s="4">
-        <f>COUNTIF(H5:H55,"未着手")</f>
+        <f>COUNTIF(H5:H56,"確認待ち")</f>
         <v/>
       </c>
       <c r="C61" s="5" t="inlineStr"/>
@@ -5053,13 +5085,13 @@
       <c r="J61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B62" s="4">
-        <f>COUNTIF(H5:H55,"対象外")</f>
+        <f>COUNTIF(H5:H56,"未着手")</f>
         <v/>
       </c>
       <c r="C62" s="5" t="inlineStr"/>
@@ -5071,53 +5103,53 @@
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
     </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B63" s="4">
+        <f>COUNTIF(H5:H56,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C63" s="5" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr"/>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr"/>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B65" s="4">
-        <f>COUNTIF(G5:G55,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C65" s="5" t="inlineStr"/>
-      <c r="D65" s="5" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="5" t="inlineStr"/>
-      <c r="G65" s="5" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B66" s="4">
-        <f>COUNTIF(G5:G55,"発注者・3町")</f>
+        <f>COUNTIF(G5:G56,"発注者")</f>
         <v/>
       </c>
       <c r="C66" s="5" t="inlineStr"/>
@@ -5132,11 +5164,11 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B67" s="4">
-        <f>COUNTIF(G5:G55,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G56,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C67" s="5" t="inlineStr"/>
@@ -5151,11 +5183,11 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B68" s="4">
-        <f>COUNTIF(G5:G55,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G56,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C68" s="5" t="inlineStr"/>
@@ -5170,11 +5202,11 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B69" s="4">
-        <f>COUNTIF(G5:G55,"北海道")</f>
+        <f>COUNTIF(G5:G56,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C69" s="5" t="inlineStr"/>
@@ -5186,8 +5218,27 @@
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr"/>
     </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="16" t="inlineStr">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B70" s="4">
+        <f>COUNTIF(G5:G56,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C70" s="5" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="5" t="inlineStr"/>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5195,11 +5246,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A72:J72"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A71:J71"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H55">
+  <conditionalFormatting sqref="H5:H56">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5238,7 +5289,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,1030 +2500,1036 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月28日に受領した基金条例の第5条第3項は、剰余金の積立てを「当該計画期間における介護保険事業計画で算定する介護保険料必要収納額の100分の10に相当する額まで」としている。第9期の保険料収納必要額2,051,968,467円（3か年計）の100分の10は205,196,846円であり、令和6年度末の基金残高231,689,018円はこれを26,492,172円上回る。①令和6年度に実質収支142,873,961円が生じながら積立てが運用益232,197円のみであったのは、上限に達しているためという理解で相違ないか。②「100分の10に相当する額まで」は、各年度の積立額の上限ではなく基金残高の上限を定めたものという解釈で相違ないか。③条例にいう「介護保険事業計画で算定する介護保険料必要収納額」は第9期計画の3か年計2,051,968,467円を指すか。④第10期の保険料算定において基金をどこまで取り崩す方針とするか。受託者の案は、条例上の上限に収まる水準まで取り崩して保険料の上昇を抑制することである。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>基金条例の確認 02シート
+素案 第6章第6節
+将来推計 第3段階</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>第10期の保険料の水準に影響する。条例の受領により判明した</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>令和8年8月28日に令和6年度決算書（介護保険特別会計）を受領し、年報の様式4と対照した結果、歳入10項目・歳出12項目のすべてで金額が一致した。次の3点のご確認をお願いする。①基金の名称について、決算書は「介護保険事業財政調整基金」、年報は「介護給付費準備基金」である。残高は一致するため実質的に同一のものと解しているが、計画本文にどちらを用いるか。条例上の名称をご教示いただきたい。②決算書の地域支援事業費に「一般介護予防事業費」の項がなく、年報の様式4でも同項は0円である。総合事業の実施状況に関する調査では介護予防普及啓発事業を3町とも実施しているため、どの科目で執行されているか。③保険料の不納欠損額が決算書646,812円・年報645,312円、収入未済額が決算書1,361,675円・年報1,363,175円で、区分が1,500円分だけ異なる。調定額・収納額は一致する。計画本文に用いる値をどちらとするか。</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月28日に令和6年度決算書（介護保険特別会計）を受領し、年報の様式4と対照した結果、歳入10項目・歳出12項目のすべてで金額が一致した。次の3点のご確認をお願いする。①【解決済】基金の名称は、令和8年8月28日に受領した大雪地区広域連合基金条例の別表により「介護保険事業財政調整基金」と確定した。年報の「介護給付費準備基金」は国の様式上の呼称である。計画本文には条例上の名称を用いる。②決算書の地域支援事業費に「一般介護予防事業費」の項がなく、年報の様式4でも同項は0円である。総合事業の実施状況に関する調査では介護予防普及啓発事業を3町とも実施しているため、どの科目で執行されているか。③保険料の不納欠損額が決算書646,812円・年報645,312円、収入未済額が決算書1,361,675円・年報1,363,175円で、区分が1,500円分だけ異なる。調定額・収納額は一致する。計画本文に用いる値をどちらとするか。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領点検 03シート
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>いずれも金額の総額に影響しない。名称と科目の確認である</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>年報月報の受領点検 04シート</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>計画本文への影響はない。記録として残すもの</t>
         </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
       <c r="A7" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>月報の値の接続のずれ（ご報告）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>年報月報の受領点検 04シート</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>計画本文への影響はない。記録として残すもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>①は第10期の保険料算定を止めている。最優先</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
       <c r="A19" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="88" customHeight="1">
       <c r="A21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -3543,1310 +3549,1310 @@
     </row>
     <row r="26" ht="88" customHeight="1">
       <c r="A26" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr"/>
     </row>
     <row r="39" ht="88" customHeight="1">
       <c r="A39" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="88" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -4863,197 +4869,224 @@
     </row>
     <row r="54" ht="88" customHeight="1">
       <c r="A54" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="88" customHeight="1">
-      <c r="A55" s="4" t="n">
+      <c r="J55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56" ht="88" customHeight="1">
+      <c r="A56" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr">
+      <c r="J56" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="88" customHeight="1">
-      <c r="A56" s="4" t="n">
+    <row r="57" ht="88" customHeight="1">
+      <c r="A57" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="J57" s="11" t="inlineStr"/>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr"/>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B59" s="4">
-        <f>COUNTIF(H5:H56,"完了")</f>
-        <v/>
-      </c>
-      <c r="C59" s="5" t="inlineStr"/>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B60" s="4">
-        <f>COUNTIF(H5:H56,"実施中")</f>
+        <f>COUNTIF(H5:H57,"完了")</f>
         <v/>
       </c>
       <c r="C60" s="5" t="inlineStr"/>
@@ -5066,13 +5099,13 @@
       <c r="J60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B61" s="4">
-        <f>COUNTIF(H5:H56,"確認待ち")</f>
+        <f>COUNTIF(H5:H57,"実施中")</f>
         <v/>
       </c>
       <c r="C61" s="5" t="inlineStr"/>
@@ -5085,13 +5118,13 @@
       <c r="J61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B62" s="4">
-        <f>COUNTIF(H5:H56,"未着手")</f>
+        <f>COUNTIF(H5:H57,"確認待ち")</f>
         <v/>
       </c>
       <c r="C62" s="5" t="inlineStr"/>
@@ -5104,13 +5137,13 @@
       <c r="J62" s="5" t="inlineStr"/>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B63" s="4">
-        <f>COUNTIF(H5:H56,"対象外")</f>
+        <f>COUNTIF(H5:H57,"未着手")</f>
         <v/>
       </c>
       <c r="C63" s="5" t="inlineStr"/>
@@ -5122,53 +5155,53 @@
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
     </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B64" s="4">
+        <f>COUNTIF(H5:H57,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B66" s="4">
-        <f>COUNTIF(G5:G56,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C66" s="5" t="inlineStr"/>
-      <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="5" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
+      <c r="C66" s="3" t="inlineStr"/>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B67" s="4">
-        <f>COUNTIF(G5:G56,"発注者・3町")</f>
+        <f>COUNTIF(G5:G57,"発注者")</f>
         <v/>
       </c>
       <c r="C67" s="5" t="inlineStr"/>
@@ -5183,11 +5216,11 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B68" s="4">
-        <f>COUNTIF(G5:G56,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G57,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C68" s="5" t="inlineStr"/>
@@ -5202,11 +5235,11 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B69" s="4">
-        <f>COUNTIF(G5:G56,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G57,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C69" s="5" t="inlineStr"/>
@@ -5221,11 +5254,11 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B70" s="4">
-        <f>COUNTIF(G5:G56,"北海道")</f>
+        <f>COUNTIF(G5:G57,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C70" s="5" t="inlineStr"/>
@@ -5237,8 +5270,27 @@
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="5" t="inlineStr"/>
     </row>
-    <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="16" t="inlineStr">
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B71" s="4">
+        <f>COUNTIF(G5:G57,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C71" s="5" t="inlineStr"/>
+      <c r="D71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr"/>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="5" t="inlineStr"/>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5246,11 +5298,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A72:J72"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A73:J73"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H56">
+  <conditionalFormatting sqref="H5:H57">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5289,7 +5341,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -664,7 +664,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。状況基準日：令和8年8月26日。</t>
+          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。状況基準日：令和8年8月28日。</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>注1）「対応する業務内容」は仕様書４（1）〜（12）の番号。01シートと対応する。注2）「提出期日」は発注者が指定する期日を記入する欄。仕様書５は各工程終了後の成果物提出と発注者確認を次工程の条件としているため、期日を月ごとに定めていただく必要がある。注3）令和8年8月26日時点で、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理、（6）計画書の作成の一部を先行実施している。先行実施分は8月・9月・10月の工程に前倒しで反映される。注4）仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の給付実績・事業実績の確定時期によっては後ろ倒しとなる可能性がある。キックオフ会議で工程の調整を協議したい。</t>
+          <t>注1）「対応する業務内容」は仕様書４（1）〜（12）の番号。01シートと対応する。注2）「提出期日」は発注者が指定する期日を記入する欄。仕様書５は各工程終了後の成果物提出と発注者確認を次工程の条件としているため、期日を月ごとに定めていただく必要がある。注3）令和8年8月28日時点で、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理、（6）計画書の作成の一部を先行実施している。先行実施分は8月・9月・10月の工程に前倒しで反映される。注4）仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の給付実績・事業実績の確定時期によっては後ろ倒しとなる可能性がある。キックオフ会議で工程の調整を協議したい。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,2631 +2500,2695 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日に受領した編集後の議事録の文書プロパティに、作成者として個人名が再度入っていた。令和8年8月28日の校正で法人名に是正した箇所である。Word で保存すると作成者が自動で入るためと思われる。構成3町へ展開される文書であり、送付前の是正を要する。Word の「ファイル」→「情報」→「問題のチェック」→「ドキュメント検査」で個人情報を削除してから保存する運用をご提案する。受託者側では生成時に自動で整備している。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>中間報告会議議事録
+業務工程管理表</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>本文には現れないため、通読では気づかない</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>議事録の表記に関するご提案3件</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>編集後の議事録について、次の3件をご提案する。いずれも発注者が意図して編集された箇所に関わるため、受託者の判断では変えず、本文は受領版のままとしている。①「必要書類の確認」で2つの合意事項が1文になり文の途中で主語が変わるため、2文に分ける。②「業務進捗」の並列の読点を「及び」に改める。③「実態が確認された」を「実態があることを確認」に改め、他の記述の簡潔体に揃える。このままで差し支えないとのご判断であれば、受領版の表記のままで確定する。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>中間報告会議議事録
+業務工程管理表</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>文意は変わらない。読みやすさと文体の統一に関するもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に受領した基金条例の第5条第3項は、剰余金の積立てを「当該計画期間における介護保険事業計画で算定する介護保険料必要収納額の100分の10に相当する額まで」としている。第9期の保険料収納必要額2,051,968,467円（3か年計）の100分の10は205,196,846円であり、令和6年度末の基金残高231,689,018円はこれを26,492,172円上回る。①令和6年度に実質収支142,873,961円が生じながら積立てが運用益232,197円のみであったのは、上限に達しているためという理解で相違ないか。②「100分の10に相当する額まで」は、各年度の積立額の上限ではなく基金残高の上限を定めたものという解釈で相違ないか。③条例にいう「介護保険事業計画で算定する介護保険料必要収納額」は第9期計画の3か年計2,051,968,467円を指すか。④第10期の保険料算定において基金をどこまで取り崩す方針とするか。受託者の案は、条例上の上限に収まる水準まで取り崩して保険料の上昇を抑制することである。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>基金条例の確認 02シート
 素案 第6章第6節
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>第10期の保険料の水準に影響する。条例の受領により判明した</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に令和6年度決算書（介護保険特別会計）を受領し、年報の様式4と対照した結果、歳入10項目・歳出12項目のすべてで金額が一致した。次の3点のご確認をお願いする。①【解決済】基金の名称は、令和8年8月28日に受領した大雪地区広域連合基金条例の別表により「介護保険事業財政調整基金」と確定した。年報の「介護給付費準備基金」は国の様式上の呼称である。計画本文には条例上の名称を用いる。②決算書の地域支援事業費に「一般介護予防事業費」の項がなく、年報の様式4でも同項は0円である。総合事業の実施状況に関する調査では介護予防普及啓発事業を3町とも実施しているため、どの科目で執行されているか。③保険料の不納欠損額が決算書646,812円・年報645,312円、収入未済額が決算書1,361,675円・年報1,363,175円で、区分が1,500円分だけ異なる。調定額・収納額は一致する。計画本文に用いる値をどちらとするか。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領点検 03シート
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>いずれも金額の総額に影響しない。名称と科目の確認である</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>計画本文への影響はない。記録として残すもの</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>①は第10期の保険料算定を止めている。最優先</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>対応中</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>北海道・圏域との調整の場</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第4節</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr">
+      <c r="J53" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="88" customHeight="1">
-      <c r="A53" s="4" t="n">
+      <c r="J54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54" ht="88" customHeight="1">
-      <c r="A54" s="4" t="n">
+      <c r="J55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56" ht="88" customHeight="1">
+      <c r="A56" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="88" customHeight="1">
-      <c r="A55" s="4" t="n">
+      <c r="J56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57" ht="88" customHeight="1">
+      <c r="A57" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56" ht="88" customHeight="1">
-      <c r="A56" s="4" t="n">
+      <c r="J57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58" ht="88" customHeight="1">
+      <c r="A58" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="J58" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="88" customHeight="1">
-      <c r="A57" s="4" t="n">
+    <row r="59" ht="88" customHeight="1">
+      <c r="A59" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr"/>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="J59" s="11" t="inlineStr"/>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="3" t="inlineStr"/>
-      <c r="J59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B60" s="4">
-        <f>COUNTIF(H5:H57,"完了")</f>
-        <v/>
-      </c>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B61" s="4">
-        <f>COUNTIF(H5:H57,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C61" s="5" t="inlineStr"/>
-      <c r="D61" s="5" t="inlineStr"/>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="5" t="inlineStr"/>
-      <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
       <c r="B62" s="4">
-        <f>COUNTIF(H5:H57,"確認待ち")</f>
+        <f>COUNTIF(H5:H59,"完了")</f>
         <v/>
       </c>
       <c r="C62" s="5" t="inlineStr"/>
@@ -5137,13 +5201,13 @@
       <c r="J62" s="5" t="inlineStr"/>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B63" s="4">
-        <f>COUNTIF(H5:H57,"未着手")</f>
+        <f>COUNTIF(H5:H59,"実施中")</f>
         <v/>
       </c>
       <c r="C63" s="5" t="inlineStr"/>
@@ -5156,13 +5220,13 @@
       <c r="J63" s="5" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B64" s="4">
-        <f>COUNTIF(H5:H57,"対象外")</f>
+        <f>COUNTIF(H5:H59,"確認待ち")</f>
         <v/>
       </c>
       <c r="C64" s="5" t="inlineStr"/>
@@ -5174,72 +5238,72 @@
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
     </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B65" s="4">
+        <f>COUNTIF(H5:H59,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B66" s="4">
+        <f>COUNTIF(H5:H59,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C66" s="5" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr"/>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr"/>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B67" s="4">
-        <f>COUNTIF(G5:G57,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C67" s="5" t="inlineStr"/>
-      <c r="D67" s="5" t="inlineStr"/>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="5" t="inlineStr"/>
-      <c r="G67" s="5" t="inlineStr"/>
-      <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="B68" s="4">
-        <f>COUNTIF(G5:G57,"発注者・3町")</f>
-        <v/>
-      </c>
-      <c r="C68" s="5" t="inlineStr"/>
-      <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="5" t="inlineStr"/>
-      <c r="G68" s="5" t="inlineStr"/>
-      <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="5" t="inlineStr"/>
-      <c r="J68" s="5" t="inlineStr"/>
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B69" s="4">
-        <f>COUNTIF(G5:G57,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G59,"発注者")</f>
         <v/>
       </c>
       <c r="C69" s="5" t="inlineStr"/>
@@ -5254,11 +5318,11 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B70" s="4">
-        <f>COUNTIF(G5:G57,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G59,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C70" s="5" t="inlineStr"/>
@@ -5273,11 +5337,11 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B71" s="4">
-        <f>COUNTIF(G5:G57,"北海道")</f>
+        <f>COUNTIF(G5:G59,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C71" s="5" t="inlineStr"/>
@@ -5289,8 +5353,46 @@
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="5" t="inlineStr"/>
     </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="16" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="B72" s="4">
+        <f>COUNTIF(G5:G59,"発注者・3町・北海道")</f>
+        <v/>
+      </c>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B73" s="4">
+        <f>COUNTIF(G5:G59,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C73" s="5" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr"/>
+      <c r="I73" s="5" t="inlineStr"/>
+      <c r="J73" s="5" t="inlineStr"/>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5299,10 +5401,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A75:J75"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H57">
+  <conditionalFormatting sqref="H5:H59">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5341,7 +5443,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,2752 +2500,2847 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>見える化システムの総括表により、第8期は3か年とも計画（延べ72人）に対し実績0人、第9期も令和6年度は計画60人に対し実績0人、令和7年度は実績7人であることが確定した。第7期には実績があった（平成30年度4人・令和元年度18人・令和2年度28人）ため、その後に供給が失われたとみられる。①この間の事業所の状況（撤退・休止の別と時期）。②第10期に引き続き計画に位置づけるか、位置づける場合の整備の見通し。③位置づけない場合、24時間対応の必要量をどのサービスで満たすとするか。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>見える化総括表の受領点検 02シート
+計画素案 第4章</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>2期続けて計画に位置づけながら実績が伴っていない。代表KPI H12（必要サービス未充足率）の設定にも関わる</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>計画値を0としたサービスに実績がある2件</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>見える化システムの総括表により、次の2件が確定した。①認知症対応型通所介護は第9期の計画値が0であるが、令和6・7年度とも延べ12人・約124万円の実績がある。第8期は令和5年度に計画12人・実績12人であった。②介護療養型医療施設は令和6年度に延べ1人・325,178円の実績がある（同施設は令和5年度末で廃止）。①について、第10期の計画値の置き方（0のままとするか実績相当を計上するか）をご相談したい。②は経過的なものとして第10期には計上しない扱いでよいか。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>見える化総括表の受領点検 02シート
+計画素案 第4章</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>計画値が0だと対計画比が算出されず、評価の対象から漏れる。第10期で同じ状態を繰り返さないための確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日に受領したPDF6件（074021_2021.pdf〜074021_2026.pdf）は、表紙及び各帳票に「北塩原村」と印字されており、大雪地区広域連合の資料ではない。帳票の構成は令和8年8月28日に受領した大雪地区広域連合の集計帳票と同じである。①出力の際の団体の指定をご確認いただきたい。②受託者は他団体の資料として用いず、作業終了後に消去する。③大雪地区広域連合の同帳票は令和6〜8年度分を受領済みである。令和3〜5年度分をご提供いただければ、第8期の認定事務の推移まで遡って確認できる。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>見える化総括表の受領点検 00シート</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>他団体の資料を成果品に用いない。第8期の認定所要日数の推移は第9期の評価の材料になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>令和8年8月31日に受領した編集後の議事録の文書プロパティに、作成者として個人名が再度入っていた。令和8年8月28日の校正で法人名に是正した箇所である。Word で保存すると作成者が自動で入るためと思われる。構成3町へ展開される文書であり、送付前の是正を要する。Word の「ファイル」→「情報」→「問題のチェック」→「ドキュメント検査」で個人情報を削除してから保存する運用をご提案する。受託者側では生成時に自動で整備している。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>本文には現れないため、通読では気づかない</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>編集後の議事録について、次の3件をご提案する。いずれも発注者が意図して編集された箇所に関わるため、受託者の判断では変えず、本文は受領版のままとしている。①「必要書類の確認」で2つの合意事項が1文になり文の途中で主語が変わるため、2文に分ける。②「業務進捗」の並列の読点を「及び」に改める。③「実態が確認された」を「実態があることを確認」に改め、他の記述の簡潔体に揃える。このままで差し支えないとのご判断であれば、受領版の表記のままで確定する。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>文意は変わらない。読みやすさと文体の統一に関するもの</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に受領した基金条例の第5条第3項は、剰余金の積立てを「当該計画期間における介護保険事業計画で算定する介護保険料必要収納額の100分の10に相当する額まで」としている。第9期の保険料収納必要額2,051,968,467円（3か年計）の100分の10は205,196,846円であり、令和6年度末の基金残高231,689,018円はこれを26,492,172円上回る。①令和6年度に実質収支142,873,961円が生じながら積立てが運用益232,197円のみであったのは、上限に達しているためという理解で相違ないか。②「100分の10に相当する額まで」は、各年度の積立額の上限ではなく基金残高の上限を定めたものという解釈で相違ないか。③条例にいう「介護保険事業計画で算定する介護保険料必要収納額」は第9期計画の3か年計2,051,968,467円を指すか。④第10期の保険料算定において基金をどこまで取り崩す方針とするか。受託者の案は、条例上の上限に収まる水準まで取り崩して保険料の上昇を抑制することである。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>基金条例の確認 02シート
 素案 第6章第6節
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>第10期の保険料の水準に影響する。条例の受領により判明した</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に令和6年度決算書（介護保険特別会計）を受領し、年報の様式4と対照した結果、歳入10項目・歳出12項目のすべてで金額が一致した。次の3点のご確認をお願いする。①【解決済】基金の名称は、令和8年8月28日に受領した大雪地区広域連合基金条例の別表により「介護保険事業財政調整基金」と確定した。年報の「介護給付費準備基金」は国の様式上の呼称である。計画本文には条例上の名称を用いる。②決算書の地域支援事業費に「一般介護予防事業費」の項がなく、年報の様式4でも同項は0円である。総合事業の実施状況に関する調査では介護予防普及啓発事業を3町とも実施しているため、どの科目で執行されているか。③保険料の不納欠損額が決算書646,812円・年報645,312円、収入未済額が決算書1,361,675円・年報1,363,175円で、区分が1,500円分だけ異なる。調定額・収納額は一致する。計画本文に用いる値をどちらとするか。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領点検 03シート
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>いずれも金額の総額に影響しない。名称と科目の確認である</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>計画本文への影響はない。記録として残すもの</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>①は第10期の保険料算定を止めている。最優先</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>対応中</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="J26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>北海道・圏域との調整の場</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第4節</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+      <c r="J53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
+      <c r="J54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="88" customHeight="1">
-      <c r="A53" s="4" t="n">
+      <c r="J55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56" ht="88" customHeight="1">
+      <c r="A56" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="J56" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="88" customHeight="1">
-      <c r="A54" s="4" t="n">
+    <row r="57" ht="88" customHeight="1">
+      <c r="A57" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="88" customHeight="1">
-      <c r="A55" s="4" t="n">
+      <c r="J57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58" ht="88" customHeight="1">
+      <c r="A58" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56" ht="88" customHeight="1">
-      <c r="A56" s="4" t="n">
+      <c r="J58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59" ht="88" customHeight="1">
+      <c r="A59" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57" ht="88" customHeight="1">
-      <c r="A57" s="4" t="n">
+      <c r="J59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60" ht="88" customHeight="1">
+      <c r="A60" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58" ht="88" customHeight="1">
-      <c r="A58" s="4" t="n">
+      <c r="J60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61" ht="88" customHeight="1">
+      <c r="A61" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="J61" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="88" customHeight="1">
-      <c r="A59" s="4" t="n">
+    <row r="62" ht="88" customHeight="1">
+      <c r="A62" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J59" s="11" t="inlineStr"/>
-    </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="J62" s="11" t="inlineStr"/>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B62" s="4">
-        <f>COUNTIF(H5:H59,"完了")</f>
-        <v/>
-      </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="5" t="inlineStr"/>
-      <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B63" s="4">
-        <f>COUNTIF(H5:H59,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C63" s="5" t="inlineStr"/>
-      <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="5" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="B64" s="4">
-        <f>COUNTIF(H5:H59,"確認待ち")</f>
-        <v/>
-      </c>
-      <c r="C64" s="5" t="inlineStr"/>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
       <c r="B65" s="4">
-        <f>COUNTIF(H5:H59,"未着手")</f>
+        <f>COUNTIF(H5:H62,"完了")</f>
         <v/>
       </c>
       <c r="C65" s="5" t="inlineStr"/>
@@ -5258,13 +5353,13 @@
       <c r="J65" s="5" t="inlineStr"/>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B66" s="4">
-        <f>COUNTIF(H5:H59,"対象外")</f>
+        <f>COUNTIF(H5:H62,"実施中")</f>
         <v/>
       </c>
       <c r="C66" s="5" t="inlineStr"/>
@@ -5276,34 +5371,52 @@
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
     </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr"/>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="3" t="inlineStr"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="B67" s="4">
+        <f>COUNTIF(H5:H62,"確認待ち")</f>
+        <v/>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B68" s="4">
+        <f>COUNTIF(H5:H62,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C68" s="5" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
         </is>
       </c>
       <c r="B69" s="4">
-        <f>COUNTIF(G5:G59,"発注者")</f>
+        <f>COUNTIF(H5:H62,"対象外")</f>
         <v/>
       </c>
       <c r="C69" s="5" t="inlineStr"/>
@@ -5315,52 +5428,34 @@
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr"/>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="B70" s="4">
-        <f>COUNTIF(G5:G59,"発注者・3町")</f>
-        <v/>
-      </c>
-      <c r="C70" s="5" t="inlineStr"/>
-      <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="5" t="inlineStr"/>
-      <c r="G70" s="5" t="inlineStr"/>
-      <c r="H70" s="5" t="inlineStr"/>
-      <c r="I70" s="5" t="inlineStr"/>
-      <c r="J70" s="5" t="inlineStr"/>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="B71" s="4">
-        <f>COUNTIF(G5:G59,"発注者・北海道")</f>
-        <v/>
-      </c>
-      <c r="C71" s="5" t="inlineStr"/>
-      <c r="D71" s="5" t="inlineStr"/>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="5" t="inlineStr"/>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="5" t="inlineStr"/>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B72" s="4">
-        <f>COUNTIF(G5:G59,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G62,"発注者")</f>
         <v/>
       </c>
       <c r="C72" s="5" t="inlineStr"/>
@@ -5375,11 +5470,11 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B73" s="4">
-        <f>COUNTIF(G5:G59,"北海道")</f>
+        <f>COUNTIF(G5:G62,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C73" s="5" t="inlineStr"/>
@@ -5391,8 +5486,65 @@
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr"/>
     </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="16" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="B74" s="4">
+        <f>COUNTIF(G5:G62,"発注者・北海道")</f>
+        <v/>
+      </c>
+      <c r="C74" s="5" t="inlineStr"/>
+      <c r="D74" s="5" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr"/>
+      <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="B75" s="4">
+        <f>COUNTIF(G5:G62,"発注者・3町・北海道")</f>
+        <v/>
+      </c>
+      <c r="C75" s="5" t="inlineStr"/>
+      <c r="D75" s="5" t="inlineStr"/>
+      <c r="E75" s="5" t="inlineStr"/>
+      <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B76" s="4">
+        <f>COUNTIF(G5:G62,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C76" s="5" t="inlineStr"/>
+      <c r="D76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr"/>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr"/>
+      <c r="I76" s="5" t="inlineStr"/>
+      <c r="J76" s="5" t="inlineStr"/>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5401,10 +5553,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A78:J78"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H59">
+  <conditionalFormatting sqref="H5:H62">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5443,7 +5595,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -664,7 +664,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。状況基準日：令和8年8月28日。</t>
+          <t>業務仕様書「４．業務内容」（1）〜（12）及び「５．業務スケジュール（予定）」に沿って、業務内容別・月別の進捗を管理する。状況基準日：令和8年8月31日。</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>注1）「対応する業務内容」は仕様書４（1）〜（12）の番号。01シートと対応する。注2）「提出期日」は発注者が指定する期日を記入する欄。仕様書５は各工程終了後の成果物提出と発注者確認を次工程の条件としているため、期日を月ごとに定めていただく必要がある。注3）令和8年8月28日時点で、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理、（6）計画書の作成の一部を先行実施している。先行実施分は8月・9月・10月の工程に前倒しで反映される。注4）仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の給付実績・事業実績の確定時期によっては後ろ倒しとなる可能性がある。キックオフ会議で工程の調整を協議したい。</t>
+          <t>注1）「対応する業務内容」は仕様書４（1）〜（12）の番号。01シートと対応する。注2）「提出期日」は発注者が指定する期日を記入する欄。仕様書５は各工程終了後の成果物提出と発注者確認を次工程の条件としているため、期日を月ごとに定めていただく必要がある。注3）令和8年8月31日時点で、（1）制度改正等の整理、（2）第9期計画の評価・検証、（4）現状分析及び地域課題の整理、（6）計画書の作成の一部を先行実施している。先行実施分は8月・9月・10月の工程に前倒しで反映される。注4）仕様書は9月に人口推計・現状分析を求めているが、令和6〜8年度の給付実績・事業実績の確定時期によっては後ろ倒しとなる可能性がある。キックオフ会議で工程の調整を協議したい。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,2885 +2500,2948 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>第10期の保険料算定の前提（受託者案）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月28日及び31日の受領資料により、将来推計 第3段階（給付費と保険料）の暫定算定を行った。第9期の算定を再現すると公表値6,428円と一致する。この式に第10期の前提を入れた基本ケースは月額6,684円で、第9期の条例基準額6,400円を284円上回る。次の4件について受託者案のご確認をお願いしたい。①給付費の採用値を見える化の自然体推計（9,267百万円）とすること。第9期の実績年率で置くと月額は6,229円となり455円下がる。②予定保険料収納率を99.0％のままとするか、現年度分の実績（99.8％台）に即した水準に改めるか。③調整交付金の見込交付割合を第9期計画と同水準（7.375％）とすること。交付実績は第7期90％・第8期88％で計画を下回っている。④第1号被保険者負担割合は政令待ちのため第9期と同じ23％で置くこと。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第3段階 05・06シート
+計画素案 第6章第6節</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>第10期の保険料水準の決定に直結する。水準そのものより「どの前提でその水準になるか」を示すことが要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>調整交付金の算定基礎の確認</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の調整交付金相当額492,515,476円を5％で割り戻すと9,850,309,520円となり、標準給付費見込額9,519,211,524円との差331,097,996円（年110,365,999円）が介護予防・日常生活支援総合事業費に当たると考えられる。同じ基礎に対する調整交付金見込額の割合は7.3755％で、第9期計画の見込交付割合（令和6年度7.51％・令和7年度7.43％・令和8年度7.19％）の平均と一致する。①調整交付金の算定基礎に包括的支援事業費及び任意事業費を含めない扱いで相違ないか。②第9期計画の総合事業費の年額110,365,999円で相違ないか（令和6年度決算は101,274,621円）。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第3段階 00・03シート</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>この扱いにより第9期の算定を再現でき、公表値6,428円と一致した。第10期の算定でも同じ扱いによる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>見える化システムの総括表により、第8期は3か年とも計画（延べ72人）に対し実績0人、第9期も令和6年度は計画60人に対し実績0人、令和7年度は実績7人であることが確定した。第7期には実績があった（平成30年度4人・令和元年度18人・令和2年度28人）ため、その後に供給が失われたとみられる。①この間の事業所の状況（撤退・休止の別と時期）。②第10期に引き続き計画に位置づけるか、位置づける場合の整備の見通し。③位置づけない場合、24時間対応の必要量をどのサービスで満たすとするか。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>見える化総括表の受領点検 02シート
 計画素案 第4章</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>2期続けて計画に位置づけながら実績が伴っていない。代表KPI H12（必要サービス未充足率）の設定にも関わる</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>見える化システムの総括表により、次の2件が確定した。①認知症対応型通所介護は第9期の計画値が0であるが、令和6・7年度とも延べ12人・約124万円の実績がある。第8期は令和5年度に計画12人・実績12人であった。②介護療養型医療施設は令和6年度に延べ1人・325,178円の実績がある（同施設は令和5年度末で廃止）。①について、第10期の計画値の置き方（0のままとするか実績相当を計上するか）をご相談したい。②は経過的なものとして第10期には計上しない扱いでよいか。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>見える化総括表の受領点検 02シート
 計画素案 第4章</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>計画値が0だと対計画比が算出されず、評価の対象から漏れる。第10期で同じ状態を繰り返さないための確認</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>令和8年8月31日に受領したPDF6件（074021_2021.pdf〜074021_2026.pdf）は、表紙及び各帳票に「北塩原村」と印字されており、大雪地区広域連合の資料ではない。帳票の構成は令和8年8月28日に受領した大雪地区広域連合の集計帳票と同じである。①出力の際の団体の指定をご確認いただきたい。②受託者は他団体の資料として用いず、作業終了後に消去する。③大雪地区広域連合の同帳票は令和6〜8年度分を受領済みである。令和3〜5年度分をご提供いただければ、第8期の認定事務の推移まで遡って確認できる。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>見える化総括表の受領点検 00シート</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>他団体の資料を成果品に用いない。第8期の認定所要日数の推移は第9期の評価の材料になる</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>令和8年8月31日に受領した編集後の議事録の文書プロパティに、作成者として個人名が再度入っていた。令和8年8月28日の校正で法人名に是正した箇所である。Word で保存すると作成者が自動で入るためと思われる。構成3町へ展開される文書であり、送付前の是正を要する。Word の「ファイル」→「情報」→「問題のチェック」→「ドキュメント検査」で個人情報を削除してから保存する運用をご提案する。受託者側では生成時に自動で整備している。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>本文には現れないため、通読では気づかない</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>編集後の議事録について、次の3件をご提案する。いずれも発注者が意図して編集された箇所に関わるため、受託者の判断では変えず、本文は受領版のままとしている。①「必要書類の確認」で2つの合意事項が1文になり文の途中で主語が変わるため、2文に分ける。②「業務進捗」の並列の読点を「及び」に改める。③「実態が確認された」を「実態があることを確認」に改め、他の記述の簡潔体に揃える。このままで差し支えないとのご判断であれば、受領版の表記のままで確定する。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>文意は変わらない。読みやすさと文体の統一に関するもの</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に受領した基金条例の第5条第3項は、剰余金の積立てを「当該計画期間における介護保険事業計画で算定する介護保険料必要収納額の100分の10に相当する額まで」としている。第9期の保険料収納必要額2,051,968,467円（3か年計）の100分の10は205,196,846円であり、令和6年度末の基金残高231,689,018円はこれを26,492,172円上回る。①令和6年度に実質収支142,873,961円が生じながら積立てが運用益232,197円のみであったのは、上限に達しているためという理解で相違ないか。②「100分の10に相当する額まで」は、各年度の積立額の上限ではなく基金残高の上限を定めたものという解釈で相違ないか。③条例にいう「介護保険事業計画で算定する介護保険料必要収納額」は第9期計画の3か年計2,051,968,467円を指すか。④第10期の保険料算定において基金をどこまで取り崩す方針とするか。受託者の案は、条例上の上限に収まる水準まで取り崩して保険料の上昇を抑制することである。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>基金条例の確認 02シート
 素案 第6章第6節
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>第10期の保険料の水準に影響する。条例の受領により判明した</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に令和6年度決算書（介護保険特別会計）を受領し、年報の様式4と対照した結果、歳入10項目・歳出12項目のすべてで金額が一致した。次の3点のご確認をお願いする。①【解決済】基金の名称は、令和8年8月28日に受領した大雪地区広域連合基金条例の別表により「介護保険事業財政調整基金」と確定した。年報の「介護給付費準備基金」は国の様式上の呼称である。計画本文には条例上の名称を用いる。②決算書の地域支援事業費に「一般介護予防事業費」の項がなく、年報の様式4でも同項は0円である。総合事業の実施状況に関する調査では介護予防普及啓発事業を3町とも実施しているため、どの科目で執行されているか。③保険料の不納欠損額が決算書646,812円・年報645,312円、収入未済額が決算書1,361,675円・年報1,363,175円で、区分が1,500円分だけ異なる。調定額・収納額は一致する。計画本文に用いる値をどちらとするか。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領点検 03シート
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>いずれも金額の総額に影響しない。名称と科目の確認である</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>計画本文への影響はない。記録として残すもの</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>①は第10期の保険料算定を止めている。最優先</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>キックオフ会議資料</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>対応中</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>北海道・圏域との調整の場</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第4節</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
+      <c r="J53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="88" customHeight="1">
-      <c r="A53" s="4" t="n">
+      <c r="J54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54" ht="88" customHeight="1">
-      <c r="A54" s="4" t="n">
+      <c r="J55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56" ht="88" customHeight="1">
+      <c r="A56" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="88" customHeight="1">
-      <c r="A55" s="4" t="n">
+      <c r="J56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57" ht="88" customHeight="1">
+      <c r="A57" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56" ht="88" customHeight="1">
-      <c r="A56" s="4" t="n">
+      <c r="J57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58" ht="88" customHeight="1">
+      <c r="A58" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="J58" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="88" customHeight="1">
-      <c r="A57" s="4" t="n">
+    <row r="59" ht="88" customHeight="1">
+      <c r="A59" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58" ht="88" customHeight="1">
-      <c r="A58" s="4" t="n">
+      <c r="J59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60" ht="88" customHeight="1">
+      <c r="A60" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J58" s="11" t="inlineStr"/>
-    </row>
-    <row r="59" ht="88" customHeight="1">
-      <c r="A59" s="4" t="n">
+      <c r="J60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61" ht="88" customHeight="1">
+      <c r="A61" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60" ht="88" customHeight="1">
-      <c r="A60" s="4" t="n">
+      <c r="J61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62" ht="88" customHeight="1">
+      <c r="A62" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61" ht="88" customHeight="1">
-      <c r="A61" s="4" t="n">
+      <c r="J62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63" ht="88" customHeight="1">
+      <c r="A63" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J61" s="11" t="inlineStr">
+      <c r="J63" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="88" customHeight="1">
-      <c r="A62" s="4" t="n">
+    <row r="64" ht="88" customHeight="1">
+      <c r="A64" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J62" s="11" t="inlineStr"/>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="J64" s="11" t="inlineStr"/>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr"/>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr"/>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B65" s="4">
-        <f>COUNTIF(H5:H62,"完了")</f>
-        <v/>
-      </c>
-      <c r="C65" s="5" t="inlineStr"/>
-      <c r="D65" s="5" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="5" t="inlineStr"/>
-      <c r="G65" s="5" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B66" s="4">
-        <f>COUNTIF(H5:H62,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C66" s="5" t="inlineStr"/>
-      <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="5" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
       <c r="B67" s="4">
-        <f>COUNTIF(H5:H62,"確認待ち")</f>
+        <f>COUNTIF(H5:H64,"完了")</f>
         <v/>
       </c>
       <c r="C67" s="5" t="inlineStr"/>
@@ -5391,13 +5454,13 @@
       <c r="J67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B68" s="4">
-        <f>COUNTIF(H5:H62,"未着手")</f>
+        <f>COUNTIF(H5:H64,"実施中")</f>
         <v/>
       </c>
       <c r="C68" s="5" t="inlineStr"/>
@@ -5410,13 +5473,13 @@
       <c r="J68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B69" s="4">
-        <f>COUNTIF(H5:H62,"対象外")</f>
+        <f>COUNTIF(H5:H64,"確認待ち")</f>
         <v/>
       </c>
       <c r="C69" s="5" t="inlineStr"/>
@@ -5428,72 +5491,72 @@
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr"/>
     </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B70" s="4">
+        <f>COUNTIF(H5:H64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C70" s="5" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B71" s="4">
+        <f>COUNTIF(H5:H64,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C71" s="5" t="inlineStr"/>
+      <c r="D71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr"/>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="5" t="inlineStr"/>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B72" s="4">
-        <f>COUNTIF(G5:G62,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C72" s="5" t="inlineStr"/>
-      <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr"/>
-      <c r="F72" s="5" t="inlineStr"/>
-      <c r="G72" s="5" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr"/>
-      <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="B73" s="4">
-        <f>COUNTIF(G5:G62,"発注者・3町")</f>
-        <v/>
-      </c>
-      <c r="C73" s="5" t="inlineStr"/>
-      <c r="D73" s="5" t="inlineStr"/>
-      <c r="E73" s="5" t="inlineStr"/>
-      <c r="F73" s="5" t="inlineStr"/>
-      <c r="G73" s="5" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="5" t="inlineStr"/>
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr"/>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B74" s="4">
-        <f>COUNTIF(G5:G62,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G64,"発注者")</f>
         <v/>
       </c>
       <c r="C74" s="5" t="inlineStr"/>
@@ -5508,11 +5571,11 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B75" s="4">
-        <f>COUNTIF(G5:G62,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G64,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C75" s="5" t="inlineStr"/>
@@ -5527,11 +5590,11 @@
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B76" s="4">
-        <f>COUNTIF(G5:G62,"北海道")</f>
+        <f>COUNTIF(G5:G64,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C76" s="5" t="inlineStr"/>
@@ -5543,8 +5606,46 @@
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr"/>
     </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="B77" s="4">
+        <f>COUNTIF(G5:G64,"発注者・3町・北海道")</f>
+        <v/>
+      </c>
+      <c r="C77" s="5" t="inlineStr"/>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B78" s="4">
+        <f>COUNTIF(G5:G64,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr"/>
+      <c r="I78" s="5" t="inlineStr"/>
+      <c r="J78" s="5" t="inlineStr"/>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5553,10 +5654,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A80:J80"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H62">
+  <conditionalFormatting sqref="H5:H64">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5595,7 +5696,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,1437 +2500,1441 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>交付金の評価項目と19施策の割当て</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>資料提供依頼No.13（施策・事業実績）の受領前に判定できる範囲を示すため、保険者機能強化推進交付金等の大項目別得点53項目を19施策に割り当て、暫定の判定を行った。結果は、取組あり・改善4施策、横ばい7施策、低下4施策、交付金では判定できない4施策（1-4虐待防止、2-4住まいと生活支援、4-2事業者の適正・円滑な運営、5-1災害・感染症対策）である。①割当ては受託者によるものであり、ご確認をお願いしたい。②1つの交付金項目が複数の施策に対応する場合がある（介護人材の確保・定着の取組状況は4-1と4-4の双方）。この扱いで相違ないか。③交付金に該当項目がない4施策は、実績がなければ判定できないことをご承知おきいただきたい。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>第9期施策別評価表 06シート</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>交付金は取組の有無と要件の充足を測るものであり、事業量・対象実人数・決算額を測るものではない。プロセス評価の代替にはならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日及び31日の受領資料により、将来推計 第3段階（給付費と保険料）の暫定算定を行った。第9期の算定を再現すると公表値6,428円と一致する。この式に第10期の前提を入れた基本ケースは月額6,684円で、第9期の条例基準額6,400円を284円上回る。次の4件について受託者案のご確認をお願いしたい。①給付費の採用値を見える化の自然体推計（9,267百万円）とすること。第9期の実績年率で置くと月額は6,229円となり455円下がる。②予定保険料収納率を99.0％のままとするか、現年度分の実績（99.8％台）に即した水準に改めるか。③調整交付金の見込交付割合を第9期計画と同水準（7.375％）とすること。交付実績は第7期90％・第8期88％で計画を下回っている。④第1号被保険者負担割合は政令待ちのため第9期と同じ23％で置くこと。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>将来推計 第3段階 05・06シート
 計画素案 第6章第6節</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>第10期の保険料水準の決定に直結する。水準そのものより「どの前提でその水準になるか」を示すことが要る</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>調整交付金の算定基礎の確認</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の調整交付金相当額492,515,476円を5％で割り戻すと9,850,309,520円となり、標準給付費見込額9,519,211,524円との差331,097,996円（年110,365,999円）が介護予防・日常生活支援総合事業費に当たると考えられる。同じ基礎に対する調整交付金見込額の割合は7.3755％で、第9期計画の見込交付割合（令和6年度7.51％・令和7年度7.43％・令和8年度7.19％）の平均と一致する。①調整交付金の算定基礎に包括的支援事業費及び任意事業費を含めない扱いで相違ないか。②第9期計画の総合事業費の年額110,365,999円で相違ないか（令和6年度決算は101,274,621円）。</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>将来推計 第3段階 00・03シート</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>この扱いにより第9期の算定を再現でき、公表値6,428円と一致した。第10期の算定でも同じ扱いによる</t>
         </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
       <c r="A7" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>調整交付金の算定基礎の確認</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の調整交付金相当額492,515,476円を5％で割り戻すと9,850,309,520円となり、標準給付費見込額9,519,211,524円との差331,097,996円（年110,365,999円）が介護予防・日常生活支援総合事業費に当たると考えられる。同じ基礎に対する調整交付金見込額の割合は7.3755％で、第9期計画の見込交付割合（令和6年度7.51％・令和7年度7.43％・令和8年度7.19％）の平均と一致する。①調整交付金の算定基礎に包括的支援事業費及び任意事業費を含めない扱いで相違ないか。②第9期計画の総合事業費の年額110,365,999円で相違ないか（令和6年度決算は101,274,621円）。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第3段階 00・03シート</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>この扱いにより第9期の算定を再現でき、公表値6,428円と一致した。第10期の算定でも同じ扱いによる</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>見える化システムの総括表により、第8期は3か年とも計画（延べ72人）に対し実績0人、第9期も令和6年度は計画60人に対し実績0人、令和7年度は実績7人であることが確定した。第7期には実績があった（平成30年度4人・令和元年度18人・令和2年度28人）ため、その後に供給が失われたとみられる。①この間の事業所の状況（撤退・休止の別と時期）。②第10期に引き続き計画に位置づけるか、位置づける場合の整備の見通し。③位置づけない場合、24時間対応の必要量をどのサービスで満たすとするか。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>見える化総括表の受領点検 02シート
 計画素案 第4章</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>2期続けて計画に位置づけながら実績が伴っていない。代表KPI H12（必要サービス未充足率）の設定にも関わる</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>見える化システムの総括表により、次の2件が確定した。①認知症対応型通所介護は第9期の計画値が0であるが、令和6・7年度とも延べ12人・約124万円の実績がある。第8期は令和5年度に計画12人・実績12人であった。②介護療養型医療施設は令和6年度に延べ1人・325,178円の実績がある（同施設は令和5年度末で廃止）。①について、第10期の計画値の置き方（0のままとするか実績相当を計上するか）をご相談したい。②は経過的なものとして第10期には計上しない扱いでよいか。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>見える化総括表の受領点検 02シート
 計画素案 第4章</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>計画値が0だと対計画比が算出されず、評価の対象から漏れる。第10期で同じ状態を繰り返さないための確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>令和8年8月31日に受領したPDF6件（074021_2021.pdf〜074021_2026.pdf）は、表紙及び各帳票に「北塩原村」と印字されており、大雪地区広域連合の資料ではない。帳票の構成は令和8年8月28日に受領した大雪地区広域連合の集計帳票と同じである。①出力の際の団体の指定をご確認いただきたい。②受託者は他団体の資料として用いず、作業終了後に消去する。③大雪地区広域連合の同帳票は令和6〜8年度分を受領済みである。令和3〜5年度分をご提供いただければ、第8期の認定事務の推移まで遡って確認できる。</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>見える化総括表の受領点検 00シート</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>他団体の資料を成果品に用いない。第8期の認定所要日数の推移は第9期の評価の材料になる</t>
         </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
       <c r="A10" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日に受領したPDF6件（074021_2021.pdf〜074021_2026.pdf）は、表紙及び各帳票に「北塩原村」と印字されており、大雪地区広域連合の資料ではない。帳票の構成は令和8年8月28日に受領した大雪地区広域連合の集計帳票と同じである。①出力の際の団体の指定をご確認いただきたい。②受託者は他団体の資料として用いず、作業終了後に消去する。③大雪地区広域連合の同帳票は令和6〜8年度分を受領済みである。令和3〜5年度分をご提供いただければ、第8期の認定事務の推移まで遡って確認できる。</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>見える化総括表の受領点検 00シート</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>他団体の資料を成果品に用いない。第8期の認定所要日数の推移は第9期の評価の材料になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>令和8年8月31日に受領した編集後の議事録の文書プロパティに、作成者として個人名が再度入っていた。令和8年8月28日の校正で法人名に是正した箇所である。Word で保存すると作成者が自動で入るためと思われる。構成3町へ展開される文書であり、送付前の是正を要する。Word の「ファイル」→「情報」→「問題のチェック」→「ドキュメント検査」で個人情報を削除してから保存する運用をご提案する。受託者側では生成時に自動で整備している。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>本文には現れないため、通読では気づかない</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>編集後の議事録について、次の3件をご提案する。いずれも発注者が意図して編集された箇所に関わるため、受託者の判断では変えず、本文は受領版のままとしている。①「必要書類の確認」で2つの合意事項が1文になり文の途中で主語が変わるため、2文に分ける。②「業務進捗」の並列の読点を「及び」に改める。③「実態が確認された」を「実態があることを確認」に改め、他の記述の簡潔体に揃える。このままで差し支えないとのご判断であれば、受領版の表記のままで確定する。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>文意は変わらない。読みやすさと文体の統一に関するもの</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に受領した基金条例の第5条第3項は、剰余金の積立てを「当該計画期間における介護保険事業計画で算定する介護保険料必要収納額の100分の10に相当する額まで」としている。第9期の保険料収納必要額2,051,968,467円（3か年計）の100分の10は205,196,846円であり、令和6年度末の基金残高231,689,018円はこれを26,492,172円上回る。①令和6年度に実質収支142,873,961円が生じながら積立てが運用益232,197円のみであったのは、上限に達しているためという理解で相違ないか。②「100分の10に相当する額まで」は、各年度の積立額の上限ではなく基金残高の上限を定めたものという解釈で相違ないか。③条例にいう「介護保険事業計画で算定する介護保険料必要収納額」は第9期計画の3か年計2,051,968,467円を指すか。④第10期の保険料算定において基金をどこまで取り崩す方針とするか。受託者の案は、条例上の上限に収まる水準まで取り崩して保険料の上昇を抑制することである。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>基金条例の確認 02シート
 素案 第6章第6節
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>第10期の保険料の水準に影響する。条例の受領により判明した</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に令和6年度決算書（介護保険特別会計）を受領し、年報の様式4と対照した結果、歳入10項目・歳出12項目のすべてで金額が一致した。次の3点のご確認をお願いする。①【解決済】基金の名称は、令和8年8月28日に受領した大雪地区広域連合基金条例の別表により「介護保険事業財政調整基金」と確定した。年報の「介護給付費準備基金」は国の様式上の呼称である。計画本文には条例上の名称を用いる。②決算書の地域支援事業費に「一般介護予防事業費」の項がなく、年報の様式4でも同項は0円である。総合事業の実施状況に関する調査では介護予防普及啓発事業を3町とも実施しているため、どの科目で執行されているか。③保険料の不納欠損額が決算書646,812円・年報645,312円、収入未済額が決算書1,361,675円・年報1,363,175円で、区分が1,500円分だけ異なる。調定額・収納額は一致する。計画本文に用いる値をどちらとするか。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領点検 03シート
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>いずれも金額の総額に影響しない。名称と科目の確認である</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>年報月報の受領点検 04シート</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>計画本文への影響はない。記録として残すもの</t>
         </is>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1">
       <c r="A15" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>月報の値の接続のずれ（ご報告）</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>年報月報の受領点検 04シート</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>計画本文への影響はない。記録として残すもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>①は第10期の保険料算定を止めている。最優先</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="27" ht="88" customHeight="1">
       <c r="A27" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="88" customHeight="1">
       <c r="A29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -3950,1310 +3954,1310 @@
     </row>
     <row r="34" ht="88" customHeight="1">
       <c r="A34" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr"/>
     </row>
     <row r="47" ht="88" customHeight="1">
       <c r="A47" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="88" customHeight="1">
-      <c r="A53" s="4" t="n">
+      <c r="J53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54" ht="88" customHeight="1">
-      <c r="A54" s="4" t="n">
+      <c r="J54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="88" customHeight="1">
-      <c r="A55" s="4" t="n">
+      <c r="J55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56" ht="88" customHeight="1">
+      <c r="A56" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56" ht="88" customHeight="1">
-      <c r="A56" s="4" t="n">
+      <c r="J56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57" ht="88" customHeight="1">
+      <c r="A57" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57" ht="88" customHeight="1">
-      <c r="A57" s="4" t="n">
+      <c r="J57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58" ht="88" customHeight="1">
+      <c r="A58" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58" ht="88" customHeight="1">
-      <c r="A58" s="4" t="n">
+      <c r="J58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59" ht="88" customHeight="1">
+      <c r="A59" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="J59" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="88" customHeight="1">
-      <c r="A59" s="4" t="n">
+    <row r="60" ht="88" customHeight="1">
+      <c r="A60" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60" ht="88" customHeight="1">
-      <c r="A60" s="4" t="n">
+      <c r="J60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61" ht="88" customHeight="1">
+      <c r="A61" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61" ht="88" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
@@ -5270,197 +5274,224 @@
     </row>
     <row r="62" ht="88" customHeight="1">
       <c r="A62" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63" ht="88" customHeight="1">
+      <c r="A63" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63" ht="88" customHeight="1">
-      <c r="A63" s="4" t="n">
+      <c r="J63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64" ht="88" customHeight="1">
+      <c r="A64" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J63" s="11" t="inlineStr">
+      <c r="J64" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="88" customHeight="1">
-      <c r="A64" s="4" t="n">
+    <row r="65" ht="88" customHeight="1">
+      <c r="A65" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J64" s="11" t="inlineStr"/>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="J65" s="11" t="inlineStr"/>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr"/>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B67" s="4">
-        <f>COUNTIF(H5:H64,"完了")</f>
-        <v/>
-      </c>
-      <c r="C67" s="5" t="inlineStr"/>
-      <c r="D67" s="5" t="inlineStr"/>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="5" t="inlineStr"/>
-      <c r="G67" s="5" t="inlineStr"/>
-      <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B68" s="4">
-        <f>COUNTIF(H5:H64,"実施中")</f>
+        <f>COUNTIF(H5:H65,"完了")</f>
         <v/>
       </c>
       <c r="C68" s="5" t="inlineStr"/>
@@ -5473,13 +5504,13 @@
       <c r="J68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B69" s="4">
-        <f>COUNTIF(H5:H64,"確認待ち")</f>
+        <f>COUNTIF(H5:H65,"実施中")</f>
         <v/>
       </c>
       <c r="C69" s="5" t="inlineStr"/>
@@ -5492,13 +5523,13 @@
       <c r="J69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B70" s="4">
-        <f>COUNTIF(H5:H64,"未着手")</f>
+        <f>COUNTIF(H5:H65,"確認待ち")</f>
         <v/>
       </c>
       <c r="C70" s="5" t="inlineStr"/>
@@ -5511,13 +5542,13 @@
       <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B71" s="4">
-        <f>COUNTIF(H5:H64,"対象外")</f>
+        <f>COUNTIF(H5:H65,"未着手")</f>
         <v/>
       </c>
       <c r="C71" s="5" t="inlineStr"/>
@@ -5529,53 +5560,53 @@
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="5" t="inlineStr"/>
     </row>
-    <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B72" s="4">
+        <f>COUNTIF(H5:H65,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="5" t="inlineStr"/>
+    </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="3" t="inlineStr"/>
-      <c r="F73" s="3" t="inlineStr"/>
-      <c r="G73" s="3" t="inlineStr"/>
-      <c r="H73" s="3" t="inlineStr"/>
-      <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B74" s="4">
-        <f>COUNTIF(G5:G64,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C74" s="5" t="inlineStr"/>
-      <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="5" t="inlineStr"/>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr"/>
-      <c r="I74" s="5" t="inlineStr"/>
-      <c r="J74" s="5" t="inlineStr"/>
+      <c r="C74" s="3" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B75" s="4">
-        <f>COUNTIF(G5:G64,"発注者・3町")</f>
+        <f>COUNTIF(G5:G65,"発注者")</f>
         <v/>
       </c>
       <c r="C75" s="5" t="inlineStr"/>
@@ -5590,11 +5621,11 @@
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B76" s="4">
-        <f>COUNTIF(G5:G64,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G65,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C76" s="5" t="inlineStr"/>
@@ -5609,11 +5640,11 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B77" s="4">
-        <f>COUNTIF(G5:G64,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G65,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C77" s="5" t="inlineStr"/>
@@ -5628,11 +5659,11 @@
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B78" s="4">
-        <f>COUNTIF(G5:G64,"北海道")</f>
+        <f>COUNTIF(G5:G65,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C78" s="5" t="inlineStr"/>
@@ -5644,8 +5675,27 @@
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="5" t="inlineStr"/>
     </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="16" t="inlineStr">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B79" s="4">
+        <f>COUNTIF(G5:G65,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C79" s="5" t="inlineStr"/>
+      <c r="D79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr"/>
+      <c r="I79" s="5" t="inlineStr"/>
+      <c r="J79" s="5" t="inlineStr"/>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5654,10 +5704,10 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A81:J81"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H64">
+  <conditionalFormatting sqref="H5:H65">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5696,7 +5746,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,11 +2500,11 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>(2)</t>
+          <t>(4)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -2514,17 +2514,18 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>社人研推計の町別・男女5歳階級別表の入手</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（施策・事業実績）の受領前に判定できる範囲を示すため、保険者機能強化推進交付金等の大項目別得点53項目を19施策に割り当て、暫定の判定を行った。結果は、取組あり・改善4施策、横ばい7施策、低下4施策、交付金では判定できない4施策（1-4虐待防止、2-4住まいと生活支援、4-2事業者の適正・円滑な運営、5-1災害・感染症対策）である。①割当ては受託者によるものであり、ご確認をお願いしたい。②1つの交付金項目が複数の施策に対応する場合がある（介護人材の確保・定着の取組状況は4-1と4-4の双方）。この扱いで相違ないか。③交付金に該当項目がない4施策は、実績がなければ判定できないことをご承知おきいただきたい。</t>
+          <t>計画素案 第2章第1節の町別75歳以上人口は、令和2年国勢調査の町別75歳以上を起点に3町計の後期高齢者比の推移で按分した推計値であり、公表値ではない（本文に［要確認］を付している）。国立社会保障・人口問題研究所「日本の地域別将来推計人口」（令和5年推計）の市区町村別・男女5歳階級別表を入手できれば、按分をやめて公表値に置き換えられる。受託者の作業環境は外部サイトへ接続できないため、①発注者において当該表をダウンロードしご提供いただけないか。②又は見える化システムから町別のA系列を出力いただけないか。いずれも難しい場合は、按分による推計値である旨を本文の注記として残す。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>第9期施策別評価表 06シート</t>
+          <t>計画素案 第2章第1節
+人口推計の補正 05シート</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -2544,1443 +2545,1447 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>交付金は取組の有無と要件の充足を測るものであり、事業量・対象実人数・決算額を測るものではない。プロセス評価の代替にはならない</t>
+          <t>町別の補正の向きが3町で異なるため、按分のままでは町別の議論に用いにくい。3町計の推計には影響しない</t>
         </is>
       </c>
     </row>
     <row r="6" ht="88" customHeight="1">
       <c r="A6" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>交付金の評価項目と19施策の割当て</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>資料提供依頼No.13（施策・事業実績）の受領前に判定できる範囲を示すため、保険者機能強化推進交付金等の大項目別得点53項目を19施策に割り当て、暫定の判定を行った。結果は、取組あり・改善4施策、横ばい7施策、低下4施策、交付金では判定できない4施策（1-4虐待防止、2-4住まいと生活支援、4-2事業者の適正・円滑な運営、5-1災害・感染症対策）である。①割当ては受託者によるものであり、ご確認をお願いしたい。②1つの交付金項目が複数の施策に対応する場合がある（介護人材の確保・定着の取組状況は4-1と4-4の双方）。この扱いで相違ないか。③交付金に該当項目がない4施策は、実績がなければ判定できないことをご承知おきいただきたい。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>第9期施策別評価表 06シート</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>交付金は取組の有無と要件の充足を測るものであり、事業量・対象実人数・決算額を測るものではない。プロセス評価の代替にはならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日及び31日の受領資料により、将来推計 第3段階（給付費と保険料）の暫定算定を行った。第9期の算定を再現すると公表値6,428円と一致する。この式に第10期の前提を入れた基本ケースは月額6,684円で、第9期の条例基準額6,400円を284円上回る。次の4件について受託者案のご確認をお願いしたい。①給付費の採用値を見える化の自然体推計（9,267百万円）とすること。第9期の実績年率で置くと月額は6,229円となり455円下がる。②予定保険料収納率を99.0％のままとするか、現年度分の実績（99.8％台）に即した水準に改めるか。③調整交付金の見込交付割合を第9期計画と同水準（7.375％）とすること。交付実績は第7期90％・第8期88％で計画を下回っている。④第1号被保険者負担割合は政令待ちのため第9期と同じ23％で置くこと。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>将来推計 第3段階 05・06シート
 計画素案 第6章第6節</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>第10期の保険料水準の決定に直結する。水準そのものより「どの前提でその水準になるか」を示すことが要る</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>調整交付金の算定基礎の確認</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の調整交付金相当額492,515,476円を5％で割り戻すと9,850,309,520円となり、標準給付費見込額9,519,211,524円との差331,097,996円（年110,365,999円）が介護予防・日常生活支援総合事業費に当たると考えられる。同じ基礎に対する調整交付金見込額の割合は7.3755％で、第9期計画の見込交付割合（令和6年度7.51％・令和7年度7.43％・令和8年度7.19％）の平均と一致する。①調整交付金の算定基礎に包括的支援事業費及び任意事業費を含めない扱いで相違ないか。②第9期計画の総合事業費の年額110,365,999円で相違ないか（令和6年度決算は101,274,621円）。</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>将来推計 第3段階 00・03シート</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>この扱いにより第9期の算定を再現でき、公表値6,428円と一致した。第10期の算定でも同じ扱いによる</t>
         </is>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1">
       <c r="A8" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>調整交付金の算定基礎の確認</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の調整交付金相当額492,515,476円を5％で割り戻すと9,850,309,520円となり、標準給付費見込額9,519,211,524円との差331,097,996円（年110,365,999円）が介護予防・日常生活支援総合事業費に当たると考えられる。同じ基礎に対する調整交付金見込額の割合は7.3755％で、第9期計画の見込交付割合（令和6年度7.51％・令和7年度7.43％・令和8年度7.19％）の平均と一致する。①調整交付金の算定基礎に包括的支援事業費及び任意事業費を含めない扱いで相違ないか。②第9期計画の総合事業費の年額110,365,999円で相違ないか（令和6年度決算は101,274,621円）。</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第3段階 00・03シート</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>この扱いにより第9期の算定を再現でき、公表値6,428円と一致した。第10期の算定でも同じ扱いによる</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>見える化システムの総括表により、第8期は3か年とも計画（延べ72人）に対し実績0人、第9期も令和6年度は計画60人に対し実績0人、令和7年度は実績7人であることが確定した。第7期には実績があった（平成30年度4人・令和元年度18人・令和2年度28人）ため、その後に供給が失われたとみられる。①この間の事業所の状況（撤退・休止の別と時期）。②第10期に引き続き計画に位置づけるか、位置づける場合の整備の見通し。③位置づけない場合、24時間対応の必要量をどのサービスで満たすとするか。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>見える化総括表の受領点検 02シート
 計画素案 第4章</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>2期続けて計画に位置づけながら実績が伴っていない。代表KPI H12（必要サービス未充足率）の設定にも関わる</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>見える化システムの総括表により、次の2件が確定した。①認知症対応型通所介護は第9期の計画値が0であるが、令和6・7年度とも延べ12人・約124万円の実績がある。第8期は令和5年度に計画12人・実績12人であった。②介護療養型医療施設は令和6年度に延べ1人・325,178円の実績がある（同施設は令和5年度末で廃止）。①について、第10期の計画値の置き方（0のままとするか実績相当を計上するか）をご相談したい。②は経過的なものとして第10期には計上しない扱いでよいか。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>見える化総括表の受領点検 02シート
 計画素案 第4章</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>計画値が0だと対計画比が算出されず、評価の対象から漏れる。第10期で同じ状態を繰り返さないための確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>令和8年8月31日に受領したPDF6件（074021_2021.pdf〜074021_2026.pdf）は、表紙及び各帳票に「北塩原村」と印字されており、大雪地区広域連合の資料ではない。帳票の構成は令和8年8月28日に受領した大雪地区広域連合の集計帳票と同じである。①出力の際の団体の指定をご確認いただきたい。②受託者は他団体の資料として用いず、作業終了後に消去する。③大雪地区広域連合の同帳票は令和6〜8年度分を受領済みである。令和3〜5年度分をご提供いただければ、第8期の認定事務の推移まで遡って確認できる。</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>見える化総括表の受領点検 00シート</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>他団体の資料を成果品に用いない。第8期の認定所要日数の推移は第9期の評価の材料になる</t>
         </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
       <c r="A11" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日に受領したPDF6件（074021_2021.pdf〜074021_2026.pdf）は、表紙及び各帳票に「北塩原村」と印字されており、大雪地区広域連合の資料ではない。帳票の構成は令和8年8月28日に受領した大雪地区広域連合の集計帳票と同じである。①出力の際の団体の指定をご確認いただきたい。②受託者は他団体の資料として用いず、作業終了後に消去する。③大雪地区広域連合の同帳票は令和6〜8年度分を受領済みである。令和3〜5年度分をご提供いただければ、第8期の認定事務の推移まで遡って確認できる。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>見える化総括表の受領点検 00シート</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>他団体の資料を成果品に用いない。第8期の認定所要日数の推移は第9期の評価の材料になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>令和8年8月31日に受領した編集後の議事録の文書プロパティに、作成者として個人名が再度入っていた。令和8年8月28日の校正で法人名に是正した箇所である。Word で保存すると作成者が自動で入るためと思われる。構成3町へ展開される文書であり、送付前の是正を要する。Word の「ファイル」→「情報」→「問題のチェック」→「ドキュメント検査」で個人情報を削除してから保存する運用をご提案する。受託者側では生成時に自動で整備している。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>本文には現れないため、通読では気づかない</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>編集後の議事録について、次の3件をご提案する。いずれも発注者が意図して編集された箇所に関わるため、受託者の判断では変えず、本文は受領版のままとしている。①「必要書類の確認」で2つの合意事項が1文になり文の途中で主語が変わるため、2文に分ける。②「業務進捗」の並列の読点を「及び」に改める。③「実態が確認された」を「実態があることを確認」に改め、他の記述の簡潔体に揃える。このままで差し支えないとのご判断であれば、受領版の表記のままで確定する。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>文意は変わらない。読みやすさと文体の統一に関するもの</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に受領した基金条例の第5条第3項は、剰余金の積立てを「当該計画期間における介護保険事業計画で算定する介護保険料必要収納額の100分の10に相当する額まで」としている。第9期の保険料収納必要額2,051,968,467円（3か年計）の100分の10は205,196,846円であり、令和6年度末の基金残高231,689,018円はこれを26,492,172円上回る。①令和6年度に実質収支142,873,961円が生じながら積立てが運用益232,197円のみであったのは、上限に達しているためという理解で相違ないか。②「100分の10に相当する額まで」は、各年度の積立額の上限ではなく基金残高の上限を定めたものという解釈で相違ないか。③条例にいう「介護保険事業計画で算定する介護保険料必要収納額」は第9期計画の3か年計2,051,968,467円を指すか。④第10期の保険料算定において基金をどこまで取り崩す方針とするか。受託者の案は、条例上の上限に収まる水準まで取り崩して保険料の上昇を抑制することである。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>基金条例の確認 02シート
 素案 第6章第6節
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>第10期の保険料の水準に影響する。条例の受領により判明した</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に令和6年度決算書（介護保険特別会計）を受領し、年報の様式4と対照した結果、歳入10項目・歳出12項目のすべてで金額が一致した。次の3点のご確認をお願いする。①【解決済】基金の名称は、令和8年8月28日に受領した大雪地区広域連合基金条例の別表により「介護保険事業財政調整基金」と確定した。年報の「介護給付費準備基金」は国の様式上の呼称である。計画本文には条例上の名称を用いる。②決算書の地域支援事業費に「一般介護予防事業費」の項がなく、年報の様式4でも同項は0円である。総合事業の実施状況に関する調査では介護予防普及啓発事業を3町とも実施しているため、どの科目で執行されているか。③保険料の不納欠損額が決算書646,812円・年報645,312円、収入未済額が決算書1,361,675円・年報1,363,175円で、区分が1,500円分だけ異なる。調定額・収納額は一致する。計画本文に用いる値をどちらとするか。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領点検 03シート
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>いずれも金額の総額に影響しない。名称と科目の確認である</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>年報月報の受領点検 04シート</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>計画本文への影響はない。記録として残すもの</t>
         </is>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
       <c r="A16" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>月報の値の接続のずれ（ご報告）</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>年報月報の受領点検 04シート</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>計画本文への影響はない。記録として残すもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>①は第10期の保険料算定を止めている。最優先</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="28" ht="88" customHeight="1">
       <c r="A28" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
-      <c r="A29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr"/>
     </row>
     <row r="30" ht="88" customHeight="1">
       <c r="A30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -4000,1310 +4005,1310 @@
     </row>
     <row r="35" ht="88" customHeight="1">
       <c r="A35" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="88" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr"/>
     </row>
     <row r="48" ht="88" customHeight="1">
       <c r="A48" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="88" customHeight="1">
-      <c r="A49" s="4" t="n">
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="88" customHeight="1">
-      <c r="A53" s="4" t="n">
+      <c r="J53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54" ht="88" customHeight="1">
-      <c r="A54" s="4" t="n">
+      <c r="J54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="88" customHeight="1">
-      <c r="A55" s="4" t="n">
+      <c r="J55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56" ht="88" customHeight="1">
+      <c r="A56" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56" ht="88" customHeight="1">
-      <c r="A56" s="4" t="n">
+      <c r="J56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57" ht="88" customHeight="1">
+      <c r="A57" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57" ht="88" customHeight="1">
-      <c r="A57" s="4" t="n">
+      <c r="J57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58" ht="88" customHeight="1">
+      <c r="A58" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58" ht="88" customHeight="1">
-      <c r="A58" s="4" t="n">
+      <c r="J58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59" ht="88" customHeight="1">
+      <c r="A59" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J58" s="11" t="inlineStr"/>
-    </row>
-    <row r="59" ht="88" customHeight="1">
-      <c r="A59" s="4" t="n">
+      <c r="J59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60" ht="88" customHeight="1">
+      <c r="A60" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J59" s="11" t="inlineStr">
+      <c r="J60" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="88" customHeight="1">
-      <c r="A60" s="4" t="n">
+    <row r="61" ht="88" customHeight="1">
+      <c r="A61" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61" ht="88" customHeight="1">
-      <c r="A61" s="4" t="n">
+      <c r="J61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62" ht="88" customHeight="1">
+      <c r="A62" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62" ht="88" customHeight="1">
-      <c r="A62" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -5320,197 +5325,224 @@
     </row>
     <row r="63" ht="88" customHeight="1">
       <c r="A63" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64" ht="88" customHeight="1">
+      <c r="A64" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64" ht="88" customHeight="1">
-      <c r="A64" s="4" t="n">
+      <c r="J64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65" ht="88" customHeight="1">
+      <c r="A65" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J64" s="11" t="inlineStr">
+      <c r="J65" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="88" customHeight="1">
-      <c r="A65" s="4" t="n">
+    <row r="66" ht="88" customHeight="1">
+      <c r="A66" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J65" s="11" t="inlineStr"/>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="J66" s="11" t="inlineStr"/>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B68" s="4">
-        <f>COUNTIF(H5:H65,"完了")</f>
-        <v/>
-      </c>
-      <c r="C68" s="5" t="inlineStr"/>
-      <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="5" t="inlineStr"/>
-      <c r="G68" s="5" t="inlineStr"/>
-      <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="5" t="inlineStr"/>
-      <c r="J68" s="5" t="inlineStr"/>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B69" s="4">
-        <f>COUNTIF(H5:H65,"実施中")</f>
+        <f>COUNTIF(H5:H66,"完了")</f>
         <v/>
       </c>
       <c r="C69" s="5" t="inlineStr"/>
@@ -5523,13 +5555,13 @@
       <c r="J69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B70" s="4">
-        <f>COUNTIF(H5:H65,"確認待ち")</f>
+        <f>COUNTIF(H5:H66,"実施中")</f>
         <v/>
       </c>
       <c r="C70" s="5" t="inlineStr"/>
@@ -5542,13 +5574,13 @@
       <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B71" s="4">
-        <f>COUNTIF(H5:H65,"未着手")</f>
+        <f>COUNTIF(H5:H66,"確認待ち")</f>
         <v/>
       </c>
       <c r="C71" s="5" t="inlineStr"/>
@@ -5561,13 +5593,13 @@
       <c r="J71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B72" s="4">
-        <f>COUNTIF(H5:H65,"対象外")</f>
+        <f>COUNTIF(H5:H66,"未着手")</f>
         <v/>
       </c>
       <c r="C72" s="5" t="inlineStr"/>
@@ -5579,53 +5611,53 @@
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr"/>
     </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B73" s="4">
+        <f>COUNTIF(H5:H66,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C73" s="5" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr"/>
+      <c r="I73" s="5" t="inlineStr"/>
+      <c r="J73" s="5" t="inlineStr"/>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr"/>
-      <c r="D74" s="3" t="inlineStr"/>
-      <c r="E74" s="3" t="inlineStr"/>
-      <c r="F74" s="3" t="inlineStr"/>
-      <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B75" s="4">
-        <f>COUNTIF(G5:G65,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C75" s="5" t="inlineStr"/>
-      <c r="D75" s="5" t="inlineStr"/>
-      <c r="E75" s="5" t="inlineStr"/>
-      <c r="F75" s="5" t="inlineStr"/>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="5" t="inlineStr"/>
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B76" s="4">
-        <f>COUNTIF(G5:G65,"発注者・3町")</f>
+        <f>COUNTIF(G5:G66,"発注者")</f>
         <v/>
       </c>
       <c r="C76" s="5" t="inlineStr"/>
@@ -5640,11 +5672,11 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B77" s="4">
-        <f>COUNTIF(G5:G65,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G66,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C77" s="5" t="inlineStr"/>
@@ -5659,11 +5691,11 @@
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B78" s="4">
-        <f>COUNTIF(G5:G65,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G66,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C78" s="5" t="inlineStr"/>
@@ -5678,11 +5710,11 @@
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B79" s="4">
-        <f>COUNTIF(G5:G65,"北海道")</f>
+        <f>COUNTIF(G5:G66,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C79" s="5" t="inlineStr"/>
@@ -5694,8 +5726,27 @@
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="5" t="inlineStr"/>
     </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="16" t="inlineStr">
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B80" s="4">
+        <f>COUNTIF(G5:G66,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C80" s="5" t="inlineStr"/>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5703,11 +5754,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A82:J82"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A81:J81"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H65">
+  <conditionalFormatting sqref="H5:H66">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5746,7 +5797,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>社人研推計の町別・男女5歳階級別表の入手</t>
+          <t>社人研推計の町別データの入手（完了）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -2533,19 +2533,19 @@
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8.31</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>町別の補正の向きが3町で異なるため、按分のままでは町別の議論に用いにくい。3町計の推計には影響しない</t>
+          <t>令和8年8月31日に結果表3-1〜3-4をご提供いただき解消した。按分をやめて公表値に置き換えた結果、町別の補正方向が4件変わった（東川町の75歳以上は「上方に補正」から「補正しない」へ、美瑛町の75歳以上は「補正しない」から「上方に補正」へ）。3町計の補正係数と保険料の試算には影響しない</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,1538 +2500,1544 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(4)(5)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日に「人口推計は社人研ではなく総合戦略上の人口で行ってほしい」とのご指示をいただいた。ご指示をそのまま実行するには次の制約がある。①総合戦略の目標は総人口のみで、介護保険の推計に必要な年齢階級別の内訳がない。②美瑛町は総合戦略に人口目標そのものが設定されていない。③東神楽町の目標（9,500人維持）は令和8年中に割り込む見込みで、東川町の目標（8,635人）は実績が既に91人上回っている。受託者は、総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、ご指示の趣旨に沿うものとして成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,684円・案B（社人研＋補正）6,593円・案C 6,789円、第1段階から第3段階まで通して再計算した案Cは6,755円である。①案Cでよいか、②美瑛町の人口目標の有無、③東川町・東神楽町の目標値の扱い、④年齢階級別の内訳の作り方の4件をご確認いただきたい。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>人口推計の基礎の変更_総合戦略ベース
+将来推計 第1〜3段階
+計画素案 第2章第1節・第6章</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>4件は一体の判断である。9月中にご確認いただければ10月の3町協議に間に合う。成果品は案Cに置き換え済みであり、案A・案Bは対比の記録として残している</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>社人研推計の町別データの入手（完了）</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>計画素案 第2章第1節の町別75歳以上人口は、令和2年国勢調査の町別75歳以上を起点に3町計の後期高齢者比の推移で按分した推計値であり、公表値ではない（本文に［要確認］を付している）。国立社会保障・人口問題研究所「日本の地域別将来推計人口」（令和5年推計）の市区町村別・男女5歳階級別表を入手できれば、按分をやめて公表値に置き換えられる。受託者の作業環境は外部サイトへ接続できないため、①発注者において当該表をダウンロードしご提供いただけないか。②又は見える化システムから町別のA系列を出力いただけないか。いずれも難しい場合は、按分による推計値である旨を本文の注記として残す。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>計画素案 第2章第1節
 人口推計の補正 05シート</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>R8.8.31</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>令和8年8月31日に結果表3-1〜3-4をご提供いただき解消した。按分をやめて公表値に置き換えた結果、町別の補正方向が4件変わった（東川町の75歳以上は「上方に補正」から「補正しない」へ、美瑛町の75歳以上は「補正しない」から「上方に補正」へ）。3町計の補正係数と保険料の試算には影響しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>交付金の評価項目と19施策の割当て</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>資料提供依頼No.13（施策・事業実績）の受領前に判定できる範囲を示すため、保険者機能強化推進交付金等の大項目別得点53項目を19施策に割り当て、暫定の判定を行った。結果は、取組あり・改善4施策、横ばい7施策、低下4施策、交付金では判定できない4施策（1-4虐待防止、2-4住まいと生活支援、4-2事業者の適正・円滑な運営、5-1災害・感染症対策）である。①割当ては受託者によるものであり、ご確認をお願いしたい。②1つの交付金項目が複数の施策に対応する場合がある（介護人材の確保・定着の取組状況は4-1と4-4の双方）。この扱いで相違ないか。③交付金に該当項目がない4施策は、実績がなければ判定できないことをご承知おきいただきたい。</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>第9期施策別評価表 06シート</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>交付金は取組の有無と要件の充足を測るものであり、事業量・対象実人数・決算額を測るものではない。プロセス評価の代替にはならない</t>
         </is>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1">
       <c r="A7" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>交付金の評価項目と19施策の割当て</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>資料提供依頼No.13（施策・事業実績）の受領前に判定できる範囲を示すため、保険者機能強化推進交付金等の大項目別得点53項目を19施策に割り当て、暫定の判定を行った。結果は、取組あり・改善4施策、横ばい7施策、低下4施策、交付金では判定できない4施策（1-4虐待防止、2-4住まいと生活支援、4-2事業者の適正・円滑な運営、5-1災害・感染症対策）である。①割当ては受託者によるものであり、ご確認をお願いしたい。②1つの交付金項目が複数の施策に対応する場合がある（介護人材の確保・定着の取組状況は4-1と4-4の双方）。この扱いで相違ないか。③交付金に該当項目がない4施策は、実績がなければ判定できないことをご承知おきいただきたい。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>第9期施策別評価表 06シート</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>交付金は取組の有無と要件の充足を測るものであり、事業量・対象実人数・決算額を測るものではない。プロセス評価の代替にはならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>令和8年8月28日及び31日の受領資料により、将来推計 第3段階（給付費と保険料）の暫定算定を行った。第9期の算定を再現すると公表値6,428円と一致する。この式に第10期の前提を入れた基本ケースは月額6,684円で、第9期の条例基準額6,400円を284円上回る。次の4件について受託者案のご確認をお願いしたい。①給付費の採用値を見える化の自然体推計（9,267百万円）とすること。第9期の実績年率で置くと月額は6,229円となり455円下がる。②予定保険料収納率を99.0％のままとするか、現年度分の実績（99.8％台）に即した水準に改めるか。③調整交付金の見込交付割合を第9期計画と同水準（7.375％）とすること。交付実績は第7期90％・第8期88％で計画を下回っている。④第1号被保険者負担割合は政令待ちのため第9期と同じ23％で置くこと。</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月28日及び31日の受領資料により、将来推計 第3段階（給付費と保険料）の暫定算定を行った。第9期の算定を再現すると公表値6,428円と一致する。この式に第10期の前提を入れた基本ケースは月額6,755円で、第9期の条例基準額6,400円を355円上回る。次の4件について受託者案のご確認をお願いしたい。①給付費の採用値を見える化の自然体推計とすること。人口の基礎の変更（No.63）に合わせて認定者数の比で置き直し、9,267百万円を9,484百万円としている。第9期の実績年率で置くと月額は6,159円となり596円下がる。②予定保険料収納率を99.0％のままとするか、現年度分の実績（99.8％台）に即した水準に改めるか。③調整交付金の見込交付割合を第9期計画と同水準（7.375％）とすること。交付実績は第7期90％・第8期88％で計画を下回っている。④第1号被保険者負担割合は政令待ちのため第9期と同じ23％で置くこと。</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>将来推計 第3段階 05・06シート
 計画素案 第6章第6節</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>第10期の保険料水準の決定に直結する。水準そのものより「どの前提でその水準になるか」を示すことが要る</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>調整交付金の算定基礎の確認</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の調整交付金相当額492,515,476円を5％で割り戻すと9,850,309,520円となり、標準給付費見込額9,519,211,524円との差331,097,996円（年110,365,999円）が介護予防・日常生活支援総合事業費に当たると考えられる。同じ基礎に対する調整交付金見込額の割合は7.3755％で、第9期計画の見込交付割合（令和6年度7.51％・令和7年度7.43％・令和8年度7.19％）の平均と一致する。①調整交付金の算定基礎に包括的支援事業費及び任意事業費を含めない扱いで相違ないか。②第9期計画の総合事業費の年額110,365,999円で相違ないか（令和6年度決算は101,274,621円）。</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>将来推計 第3段階 00・03シート</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>この扱いにより第9期の算定を再現でき、公表値6,428円と一致した。第10期の算定でも同じ扱いによる</t>
         </is>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
       <c r="A9" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>調整交付金の算定基礎の確認</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の調整交付金相当額492,515,476円を5％で割り戻すと9,850,309,520円となり、標準給付費見込額9,519,211,524円との差331,097,996円（年110,365,999円）が介護予防・日常生活支援総合事業費に当たると考えられる。同じ基礎に対する調整交付金見込額の割合は7.3755％で、第9期計画の見込交付割合（令和6年度7.51％・令和7年度7.43％・令和8年度7.19％）の平均と一致する。①調整交付金の算定基礎に包括的支援事業費及び任意事業費を含めない扱いで相違ないか。②第9期計画の総合事業費の年額110,365,999円で相違ないか（令和6年度決算は101,274,621円）。</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第3段階 00・03シート</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>この扱いにより第9期の算定を再現でき、公表値6,428円と一致した。第10期の算定でも同じ扱いによる</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>見える化システムの総括表により、第8期は3か年とも計画（延べ72人）に対し実績0人、第9期も令和6年度は計画60人に対し実績0人、令和7年度は実績7人であることが確定した。第7期には実績があった（平成30年度4人・令和元年度18人・令和2年度28人）ため、その後に供給が失われたとみられる。①この間の事業所の状況（撤退・休止の別と時期）。②第10期に引き続き計画に位置づけるか、位置づける場合の整備の見通し。③位置づけない場合、24時間対応の必要量をどのサービスで満たすとするか。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>見える化総括表の受領点検 02シート
 計画素案 第4章</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>2期続けて計画に位置づけながら実績が伴っていない。代表KPI H12（必要サービス未充足率）の設定にも関わる</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>見える化システムの総括表により、次の2件が確定した。①認知症対応型通所介護は第9期の計画値が0であるが、令和6・7年度とも延べ12人・約124万円の実績がある。第8期は令和5年度に計画12人・実績12人であった。②介護療養型医療施設は令和6年度に延べ1人・325,178円の実績がある（同施設は令和5年度末で廃止）。①について、第10期の計画値の置き方（0のままとするか実績相当を計上するか）をご相談したい。②は経過的なものとして第10期には計上しない扱いでよいか。</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>見える化総括表の受領点検 02シート
 計画素案 第4章</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>計画値が0だと対計画比が算出されず、評価の対象から漏れる。第10期で同じ状態を繰り返さないための確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>令和8年8月31日に受領したPDF6件（074021_2021.pdf〜074021_2026.pdf）は、表紙及び各帳票に「北塩原村」と印字されており、大雪地区広域連合の資料ではない。帳票の構成は令和8年8月28日に受領した大雪地区広域連合の集計帳票と同じである。①出力の際の団体の指定をご確認いただきたい。②受託者は他団体の資料として用いず、作業終了後に消去する。③大雪地区広域連合の同帳票は令和6〜8年度分を受領済みである。令和3〜5年度分をご提供いただければ、第8期の認定事務の推移まで遡って確認できる。</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>見える化総括表の受領点検 00シート</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>他団体の資料を成果品に用いない。第8期の認定所要日数の推移は第9期の評価の材料になる</t>
         </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
       <c r="A12" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日に受領したPDF6件（074021_2021.pdf〜074021_2026.pdf）は、表紙及び各帳票に「北塩原村」と印字されており、大雪地区広域連合の資料ではない。帳票の構成は令和8年8月28日に受領した大雪地区広域連合の集計帳票と同じである。①出力の際の団体の指定をご確認いただきたい。②受託者は他団体の資料として用いず、作業終了後に消去する。③大雪地区広域連合の同帳票は令和6〜8年度分を受領済みである。令和3〜5年度分をご提供いただければ、第8期の認定事務の推移まで遡って確認できる。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>見える化総括表の受領点検 00シート</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>他団体の資料を成果品に用いない。第8期の認定所要日数の推移は第9期の評価の材料になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>令和8年8月31日に受領した編集後の議事録の文書プロパティに、作成者として個人名が再度入っていた。令和8年8月28日の校正で法人名に是正した箇所である。Word で保存すると作成者が自動で入るためと思われる。構成3町へ展開される文書であり、送付前の是正を要する。Word の「ファイル」→「情報」→「問題のチェック」→「ドキュメント検査」で個人情報を削除してから保存する運用をご提案する。受託者側では生成時に自動で整備している。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>本文には現れないため、通読では気づかない</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>編集後の議事録について、次の3件をご提案する。いずれも発注者が意図して編集された箇所に関わるため、受託者の判断では変えず、本文は受領版のままとしている。①「必要書類の確認」で2つの合意事項が1文になり文の途中で主語が変わるため、2文に分ける。②「業務進捗」の並列の読点を「及び」に改める。③「実態が確認された」を「実態があることを確認」に改め、他の記述の簡潔体に揃える。このままで差し支えないとのご判断であれば、受領版の表記のままで確定する。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>文意は変わらない。読みやすさと文体の統一に関するもの</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に受領した基金条例の第5条第3項は、剰余金の積立てを「当該計画期間における介護保険事業計画で算定する介護保険料必要収納額の100分の10に相当する額まで」としている。第9期の保険料収納必要額2,051,968,467円（3か年計）の100分の10は205,196,846円であり、令和6年度末の基金残高231,689,018円はこれを26,492,172円上回る。①令和6年度に実質収支142,873,961円が生じながら積立てが運用益232,197円のみであったのは、上限に達しているためという理解で相違ないか。②「100分の10に相当する額まで」は、各年度の積立額の上限ではなく基金残高の上限を定めたものという解釈で相違ないか。③条例にいう「介護保険事業計画で算定する介護保険料必要収納額」は第9期計画の3か年計2,051,968,467円を指すか。④第10期の保険料算定において基金をどこまで取り崩す方針とするか。受託者の案は、条例上の上限に収まる水準まで取り崩して保険料の上昇を抑制することである。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>基金条例の確認 02シート
 素案 第6章第6節
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>第10期の保険料の水準に影響する。条例の受領により判明した</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に令和6年度決算書（介護保険特別会計）を受領し、年報の様式4と対照した結果、歳入10項目・歳出12項目のすべてで金額が一致した。次の3点のご確認をお願いする。①【解決済】基金の名称は、令和8年8月28日に受領した大雪地区広域連合基金条例の別表により「介護保険事業財政調整基金」と確定した。年報の「介護給付費準備基金」は国の様式上の呼称である。計画本文には条例上の名称を用いる。②決算書の地域支援事業費に「一般介護予防事業費」の項がなく、年報の様式4でも同項は0円である。総合事業の実施状況に関する調査では介護予防普及啓発事業を3町とも実施しているため、どの科目で執行されているか。③保険料の不納欠損額が決算書646,812円・年報645,312円、収入未済額が決算書1,361,675円・年報1,363,175円で、区分が1,500円分だけ異なる。調定額・収納額は一致する。計画本文に用いる値をどちらとするか。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>令和6年度決算書の受領点検 03シート
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>いずれも金額の総額に影響しない。名称と科目の確認である</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>年報月報の受領点検 04シート</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>計画本文への影響はない。記録として残すもの</t>
         </is>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1">
       <c r="A17" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>月報の値の接続のずれ（ご報告）</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>月報4か月分は画像の目視により値を確定した。文字認識では誤りが生じたため採用していない。確定にあたり、次の3件の接続のずれを確認した。①6月報の前月末9,087人に対し5月報の当月末は9,086人で1人多い。②7月報の前月末9,067人に対し6月報の当月末は9,068人で1人少ない。③6月の施設サービス受給者数は、施設種別の合計285人に対し総数が284人で1人少ない。①②は遡及訂正、③は同一月に2施設を利用した者の名寄せによるものと解している。いずれも各月の内部計算は成立しており、受託者としては値そのものの誤りではないと考えているが、念のためご確認いただきたい。なお4月報の前月末は令和7年度の年報の年度末と完全に一致し、年報と月報は接続している。</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>年報月報の受領点検 04シート</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>計画本文への影響はない。記録として残すもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に年報（令和6・7年度）と月報（令和8年4〜7月）を受領した。次の4点のご確認をお願いする。①令和7年度の年報は様式4・様式4の2・様式4の3及び経理状況が全項目0で未入力である。決算の整理が済み次第ご提供いただきたい。令和7年度末の介護給付費準備基金の残高が第10期の保険料算定に必要である。②第9期の標準月額保険料は令和6年度6,400円である。令和7年度の欄は未入力であった。3か年とも6,400円で相違ないか。③保険料収納率の実績は現年度分で99.885％（令和6年度）・99.866％（令和7年度）である。計画作成支援ツールの予定収納率99％と、第10期でどちらを用いるか。④重度要介護認定率について、年報による算定は6.38％、中間報告の記載は6.3％で0.08ポイントの差がある。計画本文に用いる値をどちらとするか。判定は変わらない。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>①は第10期の保険料算定を止めている。最優先</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>中間報告会議の議事録の記載の確認【回答済】</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日付の議事録を校正した（15件）。ご確認をお願いした4件について令和8年8月28日にご回答をいただいた。①開催日は令和8年8月26日（水）が正しい。受託者の記録を令和8年8月25日から改めた（本表・進捗報告書ほか）。②年報・月報は令和8年8月27日に発注者において受領され、受託者へは後日ご送付いただく。資料No.21・22は引き続き未受領とする。③会議の目的に掲げた業務進捗の報告を議事録の本文に記載する。④出席者は村田の欠席で相違ない。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>中間報告会議議事録
 業務工程管理表
 必要事項の一覧</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="88" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に市町村Ⅰ・Ⅱ・Ⅲの3表を受領した。①生活支援コーディネーターと協議体の数について、東川町・東神楽町は総数の欄に、美瑛町は圏域別（第1層・第2層）の欄に記入されている。記入欄の違いによるものか、配置の考え方の違いによるものか。3町計はコーディネーター11人・協議体8とみてよいか。②訪問型・通所型従前相当の利用者延べ人数が、東川町のみ「−」と回答されている。未把握と解してよいか。③代表KPI H05の総合事業ベースの参加率の分母について、見える化A系列の令和6年（9,346人）を用いているが、住民基本台帳の値に置き換えるべきか。④令和7年度分の調査回答の写しをご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>第9期の通いの場と地域支援事業の評価に用いる</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日に町別3ファイルを受領した。①ファイルに町名の記載がないため、施設・居住系の利用者数により東神楽町・東川町・美瑛町と特定した。この対応で相違ないか。②美瑛町の施設サービス居住費が471,272円と他町（618万円・761万円）に比べ小さく、短期入所の食費が18,492,717円と他町（5万円・27万円）に比べ大きい。施設の利用者数は美瑛町が最も多いため、入力のご確認。③保険料収納必要額の欄は令和6年度のみである。令和7年度分が確定次第ご提供いただきたい。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検 04シート
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>第3段階（給付費・保険料）の算定に用いる</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>3町の給付費総額の合計が、大雪地区広域連合の給付費総額を129,580,267円（4.20％）上回る。令和6年度・令和8年度は完全に一致する。【美瑛町】令和7年度のファイルは利用回数のシート名が「（東神楽）」となっており、他年度と異なる手順で作成された可能性がある。【大雪】又は【美瑛町】の令和7年度のファイルの再作成をご検討いただきたい。</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>解消するまでは令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用いる</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="4" t="n">
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>給付実績データに含まれる個人情報の取扱い</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の給付実績データ9ファイルの第1シートには、被保険者番号・氏名・性別・生年月日・住民コード・世帯番号・住所コード・郵便番号が含まれている（5万7千〜5万9千行）。①個票を含むファイルの送付が意図されたものか。集計シートのみで足りる場合は次回以降は集計シートのみで作業できる。②受託者における保管期間と廃棄の方法。③町別ファイルの第1シートが広域連合の全件である点。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>給付実績データの受領点検
 将来推計 第2・3段階</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>R8.8.28</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="n">
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>令和6年度の給付費実績3,084,937,834円に対し、第9期計画の標準給付費見込額3,127,780,210円との乖離は▲1.37％、総給付費2,924,324,000円との乖離は＋5.49％である。目標±5％以内との関係で結果が変わるため、いずれを分母とするかのご決定をお願いする。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>計画素案 第4章 資料1
 中間報告 第3節</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>受託者案は標準給付費見込額。計画期間を通じた財政運営の指標であるため</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="88" customHeight="1">
-      <c r="A24" s="4" t="n">
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>認定に要する日数の扱い</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>受領した要介護認定 集計帳票によると、申請日から二次判定日までの平均所要日数は、新規で令和6年度45.4日・令和7年度46.7日である。介護保険法第27条第11項は申請から30日以内の処分を定めている。本件を第9期の評価及び第10期の課題として扱うかのご確認。なお主治医意見書の入手日は3年度とも未入力であり、申請から意見書入手までの日数は算定できない。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>中間報告 第3節
 計画素案 第2章・第5章</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>令和8年8月28日受領の集計帳票により判明</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="88" customHeight="1">
-      <c r="A25" s="4" t="n">
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せにおいて、①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなった。特に、第9期の目標指標をそのまま継続するのか、新設するのかについて、骨子案 第4節（第9期計画の評価概要）・第5節（基本理念・基本目標）・第6節（成果指標の枠組み）をご覧いただきたい。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>計画骨子案
 施策体系新旧対照表
 計画素案 第4章・第5章</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>同打合せで期限を令和8年9月2日（水）と設定。令和8年8月28日の発注者のご指示により、議事録に①②を加え、期限を明記した（校正No.14・15）</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="4" t="n">
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>同一の施設が複数のサービスで登録されており、同じ職員がサービスごとに計上されている（重複の候補8組・252人）。供給制約の推定に用いる従業員数を、延べとするか施設単位の実人数とするかのご確認。同打合せでは、受託者が方法を提案するか、重複の候補の一覧に発注者がご記入いただくかの2案が挙げられた。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>従業員数の重複計上の整理
 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>受託者の案は施設単位の実人数。「従業員数の重複計上の整理」01シートに確認欄を設けて両案に対応した</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="88" customHeight="1">
-      <c r="A27" s="4" t="n">
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>令和8年度の実績の推定方法</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>令和8年度は本業務の期間中に確定しない。同打合せにおいて、月報により各月の推移を把握したうえで、見える化システムによる試算（人口、高齢化率、年齢区分別の認定率等）により推定する方針でご了承をいただいた。本欄は、その方針を記録として残すものである。</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>計画素案 第6章
 将来推計 第1〜3段階</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>R8.8.26</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="88" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料への工程表の反映</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>キックオフ会議資料</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
         </is>
       </c>
     </row>
     <row r="29" ht="88" customHeight="1">
       <c r="A29" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料への工程表の反映</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料に、委員会の開催時期を含む工程表（第1回〜第4回の策定委員会、令和9年1〜3月のパブリックコメント）を反映した版をご提供する。3町へ展開し、工程に相違がないかをご確認いただく。</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>同打合せでご依頼をいただいた。反映する工程表は発注者ご作成の予定表による</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>厚生労働大臣が定める特別地域（特別地域加算の対象地域）の告示に、東川町・美瑛町が掲載されているかどうか。第10期から創設される特定地域（中山間・人口減少地域）の基準①に直結し、該当すれば人員基準の緩和や特定地域居宅サービス等事業が使える。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第9節
 追加調査報告書 01シート</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
-      <c r="A30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr"/>
     </row>
     <row r="31" ht="88" customHeight="1">
       <c r="A31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」とされている。当広域連合が意向を示す時期と手続、及び制度の適用単位が市町村か保険者かの確認。</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>仕様書４（4）は「必要に応じ全国平均、北海道平均及び類似保険者との比較分析を行う」としているが、見える化のδ3系列（地域比較）は当広域連合のデータ登録がなく出力できない。健康とくらしの調査の同規模保険者40（人口5万未満・集計数82,106票）との比較により、住民の心身の状態と社会参加の領域は比較分析を実施済み（調査クロス集計・分析19〜21シート）。残るのは給付・供給面の類似保険者比較であり、比較対象の保険者と選定条件（人口規模、高齢化率、施設整備状況、財政力等）の決定を要する。</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第2節
 分析資料</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領しているとの確認を得た。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれていない。このためH12・H16は基準値を算定できない。在宅介護実態調査（H07・H08）は実施されていない。調査クロス集計・分析の結果、H07（主介護者）・H08（支援者の不在）は健康とくらしの調査の大雪独自設問により算定できることが判明したが、指標の定義変更を伴う。①代理指標へ振り替える、②指標から外す、③2問に絞って事業所へ照会する、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・資料1
 全16KPIの4項目</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="J33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>第9期の施策・事業実績</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>第9期計画（令和6〜8年度）の施策・事業実績、事業量、対象実人数、予算・決算。19施策の達成度を判定するために必要。記入様式を別冊「資料提供依頼_第9期の施策事業実績」として作成した（5区分14項目・7シート）。既存資料の写しでも足りる。</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第2節・第3節・第5節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="88" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="J34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>交付金の評価調書</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜6年度分）。0点となっている10項目について、取組自体がないのか、取組はあるが要件を満たさないのかの判別に必要。特に推進Ⅰ「評価結果を関係者間で共有し取組を検討」と「今年度の評価得点」。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 追加調査報告書 02シート</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="88" customHeight="1">
-      <c r="A35" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>素案 第1章第6節・第3章第4節</t>
-        </is>
-      </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -4051,1310 +4057,1310 @@
     </row>
     <row r="36" ht="88" customHeight="1">
       <c r="A36" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPIについて令和6・7年度に実績を算定した資料の有無、運営協議会への報告の有無と議事録、及び介護保険法第117条に基づく北海道への報告の実績。</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第6節・第3章第4節</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>令和8年8月4日に第10期分102ファイルを受領し点検・集計した。重大6件（同一法人による職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハと見える化の乖離、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の取扱いと、事業所への照会の要否・方法の確認を要する。</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第5・6節
 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="88" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>4調査の対象者の範囲（要介護度、年齢、居所等）、配布数、回収数、回収率。標本規模に応じた分析の深度（クロス集計の可否）の判断に必要。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第4〜6節
 クロス集計表</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="88" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標⑥と同じ「採用率と離職率の差」を算定するため、各年9月30日現在の在籍者数と、年間の採用者数・退職者数。H14の基準値となる。</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節
 H14の基準値</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="88" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>町別の人口・世帯データ</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>①住民基本台帳による町別・年齢4区分別人口（0〜39歳／40〜64歳／65〜74歳／75歳以上）令和6〜8年 各年10月1日現在、②町別高齢化率 令和6〜8年、③令和7年国勢調査による町別の高齢者を含む世帯（公表され次第）。あわせて、見える化の地域分析で市区町村を選択して人口系列（A1〜A4）を出力できるかの確認。</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第1節
 図1・図2・図3</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>①美瑛町4地区を含む6圏域別の面積・人口・高齢者人口・認定者数・受給者数・給付費（令和8年10月1日現在）。仕様書４（4）が求める圏域別の地域特性分析に必要。②健康とくらしの調査の分析地域1（小学校区12地区）と6圏域の対応関係。美馬牛小学校区は美馬牛地区に対応すると考えられるが、美瑛・美沢・明徳・美瑛東の各小学校区と旭・北西地区、朗根内地区、市街地・周辺地区との対応が確定しない。対応が確定すれば、見える化のデータを待たずに圏域別分析ができる。</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="88" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日に北海道の介護保険事業所一覧により解消。124件を整理した】、②中山間地域等居住者サービス提供加算・特別地域加算の算定事業所と件数、③3町の除雪計画における優先路線と冬期の通行支障の実績。残るのは②③である。</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="88" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="J42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎とする系列</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>総人口・第1号被保険者数について、①国立社会保障・人口問題研究所推計（見える化の初期値）をそのまま用いるか、②3町の総合計画等による推計人口に差し替えるかの決定。②の場合は5歳階級別・男女別の推計値が必要。東川町は25年以上人口増を続けており、社人研推計との乖離が大きい。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="88" customHeight="1">
-      <c r="A43" s="4" t="n">
+      <c r="J43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>令和3〜8年度の各月の認定者数。推計ガイドは9月末を目安としつつ「年度内平均値に近い月を選択する」としているため、当広域連合の月次推移を確認して基準月を選定する。</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 将来推計</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="88" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="J44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>保険料算定の前提</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>①介護給付費準備基金の残高推移と取崩実績（第7期〜第9期）、②保険料収納率の実績（第7期〜第9期）、③所得段階別被保険者数、④地域支援事業費の区分別内訳（総合事業・包括的支援事業・任意事業）。</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第3節・第6節
 保険料算定表</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="88" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="J45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>第9期は、3町の高齢者福祉計画のうち事業の数値目標を設定していたのは東川町のみで、広域連合の代表KPIの検証への参画を明記していたのも東川町のみであった。第10期では3町の計画に共通指標を掲載していただく合意が、資料2の実効性の前提となる。あわせて3町の第10期計画の検討資料、策定工程、担当課の確認。</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>素案 資料2
 3町協議資料</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46" ht="88" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="J46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>骨子案の内容の確認</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に骨子案を作成した（11節22表）。第10節に決定・確認を要する事項12件を整理している。章立て、基本理念、5つの基本目標、代表KPI16項目の枠組み及び算定の枠組みについて、ご意向を確認する。</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>骨子案
 素案の次稿</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="88" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="J47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>(8)(9)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>①介護保険事業計画策定委員会（運営協議会）の開催日程、審議事項、資料提出期限、②パブリックコメントの実施期間、③町別値・少数値の公表基準。工程の確定と資料作成の逆算に必要。</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>委員会資料原案
 パブリックコメント資料</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="88" customHeight="1">
-      <c r="A48" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>素案 第6章第4節</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr"/>
     </row>
     <row r="49" ht="88" customHeight="1">
       <c r="A49" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>上川中部高齢者保健福祉圏域に関する北海道の調整方針、圏域連絡協議会の資料、及び圏域単位の協議の場の設置予定。24時間対応サービスの確保方策（第6章第4節）の検討に必要。</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>成果品の仕様</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>①本文100頁程度に対する章別のページ配分、②図表の本文掲載点数の上限、③概要版の頁数と体裁、④印刷・製本の入稿期限。図表集は33シート133点あり、本文に何点まで掲載するかの決定を要する。</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>計画書（印刷200部）
 概要版</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50" ht="88" customHeight="1">
-      <c r="A50" s="4" t="n">
+      <c r="J50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>北海道の評価指標には「市町村数」を単位とするものが多く、1保険者である当広域連合にはそのまま適用できない。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示しているかどうか。示されていない場合は、①日常生活圏域数、②実数・率、③3町のうち実施している町数のいずれに置き換えるかの決定を要する。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>素案 第1章第6節
 追加調査報告書 04シート</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>発注者・北海道</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="A51" s="4" t="n">
+      <c r="J51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>①地域密着型通所介護4事業所の定員、登録者数、延べ利用者数（令和4〜8年度）、②施設・居住系サービスの入所者数・空床・休止床。地域密着型通所介護は事業所数4で不変、従事者は増加しているのに給付費が27.0％減少しており、稼働率の低下が疑われる。第10期基本指針案の別表 七が求める入所率・稼働率の把握にも必要。</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>素案 第2章第3節・第6章第4節
 図21・図22</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52" ht="88" customHeight="1">
-      <c r="A52" s="4" t="n">
+      <c r="J52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護、看護小規模多機能型居宅介護の3種別は制度創設以来13年間、区域内に事業所がない。①区域内に整備する、②区域外（旭川市）の事業所の利用により確保する、③特定地域居宅サービス等事業として広域連合が実施する、④整備しない、のいずれかの決定を要する。決定しないと第6章第2節の地域密着型サービスの見込量が確定しない。</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第4節
 見込量表（3種別）</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="88" customHeight="1">
-      <c r="A53" s="4" t="n">
+      <c r="J53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>計画素案で［要協議］としている代表KPIの令和11年度目標値。基準値が確定している指標については目標水準の考え方（維持・改善・低下抑制）の決定を、調査結果を要する指標については調査データの受領後の設定を要する。認定率や利用率は一律に低下を目標とせず、適正水準と要因を評価する方針としている。</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54" ht="88" customHeight="1">
-      <c r="A54" s="4" t="n">
+      <c r="J54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>見える化システムのJ系列（認知症）及びL20〜L26（診療報酬側の連携指標）は当広域連合のデータ登録がなく取得できない。①認知症初期集中支援チームの訪問実績、認知症地域支援推進員の配置人数、認知症カフェの箇所数等（3町）、②医療側からの連携の実施状況（上川中部圏域の医療機関又は北海道の医療計画・地域医療構想の資料）。</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>素案 第5章 基本目標1・5
 図表集 認知症・医療連携</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>発注者・3町・北海道</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="88" customHeight="1">
-      <c r="A55" s="4" t="n">
+      <c r="J55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56" ht="88" customHeight="1">
+      <c r="A56" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>第9期からの変化を検定するため、令和4年度調査の有効回答数（指標別）と集計表。現在は有効回答数を4,700と仮定して2標本の検定を行っており、4,000〜5,000の範囲では判定が変わらないことを確認しているが、確定値による検証を要する。</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 14シート
 素案 第2章第4節</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56" ht="88" customHeight="1">
-      <c r="A56" s="4" t="n">
+      <c r="J56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57" ht="88" customHeight="1">
+      <c r="A57" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>調査対象者の範囲の確認</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>令和7年度 健康とくらしの調査の対象者は「一般高齢者＋総合事業対象者」であり、要支援者・要介護者を含まないことを調査報告書で確認した。この理解で相違ないか、及び第10期の各調査（在宅生活改善・居所変更・介護人材）の対象者の範囲。母集団が異なる指標を併記する際の前提となる。</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>調査クロス集計・分析 13・14シート
 H06・H11の基準値</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57" ht="88" customHeight="1">
-      <c r="A57" s="4" t="n">
+      <c r="J57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58" ht="88" customHeight="1">
+      <c r="A58" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>将来推計の認定者数に最も大きく影響する決定事項。交付金の成果指標では、長期的な要介護度の変化が要介護1・2で全国の0.86倍、要介護3〜5で全国の0.51倍と良好である一方、単年度変化率の前年度との差は軽度＋9.34（全国▲1.95）、中重度＋6.33（全国＋0.15）と全国と逆方向に動いている。①長期の良好な実績を将来に延長する、②直近の反転を反映する、③全国並みの重度化速度に収束すると置く、のいずれかの決定を要する。</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第1節
 認定者数・給付費の推計</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58" ht="88" customHeight="1">
-      <c r="A58" s="4" t="n">
+      <c r="J58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59" ht="88" customHeight="1">
+      <c r="A59" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>長期的な要介護度の変化が全国より良好である要因の特定に必要。施設及び居住系サービスの受給率が全国比1.08と高く、施設入所により在宅の重度化が見えにくくなっている可能性がある。介護老人福祉施設の定員が234人から160人へ減少しているため、この経路によるものであれば同じ実績は続かない。</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>重度化の速度の前提
 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J58" s="11" t="inlineStr"/>
-    </row>
-    <row r="59" ht="88" customHeight="1">
-      <c r="A59" s="4" t="n">
+      <c r="J59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60" ht="88" customHeight="1">
+      <c r="A60" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>交付金の推進Ⅱ（公正・公平な給付）は全国の39.0％で全8目標中最低であり、ケアプラン点検の実施割合と医療情報との突合の実施割合がいずれも0点である。第10期にこれらを実施するか、実施する場合に給付費の推計へ政策効果として見込むかの決定を要する。</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第2節・第5章・第7章
 給付費の推計</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60" ht="88" customHeight="1">
-      <c r="A60" s="4" t="n">
+      <c r="J60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61" ht="88" customHeight="1">
+      <c r="A61" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>第7期の保険料基準額</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>見える化システムの値は6,077円であるが、計画素案では当初5,900円としていた。剰余の累計＋159円／月は6,077円を前提としたときにのみ整合する（(6,077－6,024)×3＝159）。条例による第7期の基準額の確認を要する。</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>素案 第6章第6節
 保険料の推移</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="J61" s="11" t="inlineStr">
         <is>
           <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="88" customHeight="1">
-      <c r="A61" s="4" t="n">
+    <row r="62" ht="88" customHeight="1">
+      <c r="A62" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>第10期の標準段階数、標準乗率、公費軽減の乗率及び第1号被保険者負担割合。政令改正により定まるため告示後の確認を要する。当広域連合の現行16段階の乗率との相対的な関係が変わる可能性がある。</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の算定</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>国の情報</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>告示後</t>
         </is>
       </c>
-      <c r="J61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62" ht="88" customHeight="1">
-      <c r="A62" s="4" t="n">
+      <c r="J62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63" ht="88" customHeight="1">
+      <c r="A63" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>第9段階の乗率の経緯</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>第9段階（合計所得320万円以上420万円未満）の乗率1.63は国標準1.70を下回っている。低所得者対策とは性格が異なるため、この設定の経緯と考え方の確認を要する。第8期の9段階制における乗率を引き継いだ可能性がある。</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>第10期の段階設計
 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63" ht="88" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -5371,197 +5377,224 @@
     </row>
     <row r="64" ht="88" customHeight="1">
       <c r="A64" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者の第9期の所得段階数と乗率。多段階化の状況を比較するために必要。北海道の資料又は各保険者の保険料条例による。</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65" ht="88" customHeight="1">
+      <c r="A65" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>①令和5〜8年度の所得段階別被保険者数（各年度）、②第7期〜第9期の保険料収納率（可能であれば所得段階別）、③公費軽減の対象者数と適用率。第9期計画は3年間の推計値のみを掲載しており実績が確認できない。低所得層の収納率が低い場合、軽減の効果と滞納対策の必要性を検証できる。</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>所得段階別被保険者数の推計
 保険料の算定
 素案 第6章第7節</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J64" s="11" t="inlineStr"/>
-    </row>
-    <row r="65" ht="88" customHeight="1">
-      <c r="A65" s="4" t="n">
+      <c r="J65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66" ht="88" customHeight="1">
+      <c r="A66" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>年齢階級別・要介護度別の認定率</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）及び要介護度別の認定率。第9期の評価で「年齢層をそろえると認定率は低下している」としているが、根拠は合計・75歳以上・85歳以上の3系列のみで、65〜74歳を確認していない。また性・年齢調整済み要介護2以上認定率（W144）は上昇しており、整合を実証するには要介護度別の推移が必要（自己点検記録 No.1）。</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見7</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="J65" s="11" t="inlineStr">
+      <c r="J66" s="11" t="inlineStr">
         <is>
           <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="88" customHeight="1">
-      <c r="A66" s="4" t="n">
+    <row r="67" ht="88" customHeight="1">
+      <c r="A67" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>現在用いている令和5年調査（令和6年度分指標）は評価対象が主に令和4年度の実施状況であり、第9期ではなく第8期の取組を反映している。第9期の評価とするには令和6年・令和7年調査の得点が必要（自己点検記録 No.2）。取得できない場合は「第8期の取組を反映した評価」と明記して用いる。</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>素案 第3章第4節
 妥当性検証 所見18・19</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J66" s="11" t="inlineStr"/>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="J67" s="11" t="inlineStr"/>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr"/>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B69" s="4">
-        <f>COUNTIF(H5:H66,"完了")</f>
-        <v/>
-      </c>
-      <c r="C69" s="5" t="inlineStr"/>
-      <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr"/>
-      <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="5" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="5" t="inlineStr"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
       <c r="B70" s="4">
-        <f>COUNTIF(H5:H66,"実施中")</f>
+        <f>COUNTIF(H5:H67,"完了")</f>
         <v/>
       </c>
       <c r="C70" s="5" t="inlineStr"/>
@@ -5574,13 +5607,13 @@
       <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B71" s="4">
-        <f>COUNTIF(H5:H66,"確認待ち")</f>
+        <f>COUNTIF(H5:H67,"実施中")</f>
         <v/>
       </c>
       <c r="C71" s="5" t="inlineStr"/>
@@ -5593,13 +5626,13 @@
       <c r="J71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B72" s="4">
-        <f>COUNTIF(H5:H66,"未着手")</f>
+        <f>COUNTIF(H5:H67,"確認待ち")</f>
         <v/>
       </c>
       <c r="C72" s="5" t="inlineStr"/>
@@ -5612,13 +5645,13 @@
       <c r="J72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B73" s="4">
-        <f>COUNTIF(H5:H66,"対象外")</f>
+        <f>COUNTIF(H5:H67,"未着手")</f>
         <v/>
       </c>
       <c r="C73" s="5" t="inlineStr"/>
@@ -5630,53 +5663,53 @@
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr"/>
     </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B74" s="4">
+        <f>COUNTIF(H5:H67,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C74" s="5" t="inlineStr"/>
+      <c r="D74" s="5" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr"/>
+      <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="5" t="inlineStr"/>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="B76" s="4">
-        <f>COUNTIF(G5:G66,"発注者")</f>
-        <v/>
-      </c>
-      <c r="C76" s="5" t="inlineStr"/>
-      <c r="D76" s="5" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr"/>
-      <c r="F76" s="5" t="inlineStr"/>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr"/>
-      <c r="I76" s="5" t="inlineStr"/>
-      <c r="J76" s="5" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="B77" s="4">
-        <f>COUNTIF(G5:G66,"発注者・3町")</f>
+        <f>COUNTIF(G5:G67,"発注者")</f>
         <v/>
       </c>
       <c r="C77" s="5" t="inlineStr"/>
@@ -5691,11 +5724,11 @@
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="B78" s="4">
-        <f>COUNTIF(G5:G66,"発注者・北海道")</f>
+        <f>COUNTIF(G5:G67,"発注者・3町")</f>
         <v/>
       </c>
       <c r="C78" s="5" t="inlineStr"/>
@@ -5710,11 +5743,11 @@
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="B79" s="4">
-        <f>COUNTIF(G5:G66,"発注者・3町・北海道")</f>
+        <f>COUNTIF(G5:G67,"発注者・北海道")</f>
         <v/>
       </c>
       <c r="C79" s="5" t="inlineStr"/>
@@ -5729,11 +5762,11 @@
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="B80" s="4">
-        <f>COUNTIF(G5:G66,"北海道")</f>
+        <f>COUNTIF(G5:G67,"発注者・3町・北海道")</f>
         <v/>
       </c>
       <c r="C80" s="5" t="inlineStr"/>
@@ -5745,8 +5778,27 @@
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr"/>
     </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="16" t="inlineStr">
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B81" s="4">
+        <f>COUNTIF(G5:G67,"北海道")</f>
+        <v/>
+      </c>
+      <c r="C81" s="5" t="inlineStr"/>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr"/>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="16" t="inlineStr">
         <is>
           <t>注1）本シートの確認事項は、計画素案の本文には注記として記載しない。本文には確定していない数値を［要協議］［要確認］［要内訳］として残すにとどめ、その解消に必要な作業は本シートで管理する。注2）「止めている成果物」が確定しない限り、当該成果物を含む工程は完了しない。01シートの「未了の理由・次の作業」及び02シートの「備考・次工程への条件」と対応する。注3）確認事項の詳細な背景と根拠は、妥当性検証報告書及び追加調査報告書に記載している。発注者への依頼文としては確認依頼書（第8版）を別途提出している。</t>
         </is>
@@ -5754,11 +5806,11 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A82:J82"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H66">
+  <conditionalFormatting sqref="H5:H67">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -5797,7 +5849,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_業務工程管理表.xlsx
+++ b/output/第10期計画_業務工程管理表.xlsx
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2500,3139 +2500,3204 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>(6)(7)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>広域連合において行うべき事業の優先順位</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日に「大雪地区広域事務組合において行うべき事業を優先順位をもとに整理してほしい。出来れば富良野市のサービス事業一覧のようなものができるとありがたい」とのご指示をいただき、富良野市のサービスガイドと鹿児島県の生活支援体制整備事業取組事例集を参照して20件を整理した。義務・欠落・実行・効果・主体の5項目を各3点で採点し、優先度A4件・B7件・C9件に分けている。①優先順位の考え方（5項目の採点）でよいか。地域の事情による重み付け（冬期の除雪等）を加えるべきか。②優先度Aの4件（総合事業の事業評価・生活支援体制整備の区域共通運営・24時間対応サービスの確保方策・包括的支援事業と任意事業の実績管理）と、これに準ずる2件（高齢者福祉サービスの一覧化・介護給付適正化）でよいか。③3町の介護保険外の高齢者福祉サービス（緊急通報・除雪・配食・外出支援・介護用品券・成年後見支援等）の事業名・対象・内容・利用料を3町からご提供いただきたい。④本表を令和8年10月・11月の3町協議の資料として用いるか。⑤サービスガイドを成果品として作るか。作る場合、住民配布用の冊子とするか内部管理用の一覧にとどめるか。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>広域連合において行うべき事業の優先順位
+介護高齢者福祉サービスガイド_構成案
+計画素案 第5章・第6章第3節2</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>③は資料提供のお願いである。受託者が照会様式（富良野市ガイド17〜18頁の項目立て）を用意する。事業所の所在地・電話番号は、個人情報を保管しない方針により受託者は保有していないため、発注者において追記いただく必要がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護、夜間対応型訪問介護及び看護小規模多機能型居宅介護は、制度創設以来13年間、区域内に事業所が存在しない。サービスガイドを住民に配布する場合、①「区域内に事業所がありません」と明記するか、②記載自体を省くか、③上川中部圏域の他保険者の事業所を利用できる旨を案内するか。富良野市のガイドは、訪問入浴介護について「市内に事業所はありませんが上記の事業所が利用できます」と明記する扱いをしている。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>介護高齢者福祉サービスガイド_構成案
+計画素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>第10期計画の確保方策（第6章第4節の3案）の決定と一体の判断である。整備しないことを決めるのであれば、他保険者の事業所の利用の案内は住民にとって必要になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>(4)(5)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>令和8年8月31日に「人口推計は社人研ではなく総合戦略上の人口で行ってほしい」とのご指示をいただいた。ご指示をそのまま実行するには次の制約がある。①総合戦略の目標は総人口のみで、介護保険の推計に必要な年齢階級別の内訳がない。②美瑛町は総合戦略に人口目標そのものが設定されていない。③東神楽町の目標（9,500人維持）は令和8年中に割り込む見込みで、東川町の目標（8,635人）は実績が既に91人上回っている。受託者は、総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、ご指示の趣旨に沿うものとして成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,684円・案B（社人研＋補正）6,593円・案C 6,789円、第1段階から第3段階まで通して再計算した案Cは6,755円である。①案Cでよいか、②美瑛町の人口目標の有無、③東川町・東神楽町の目標値の扱い、④年齢階級別の内訳の作り方の4件をご確認いただきたい。</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎の変更_総合戦略ベース
 将来推計 第1〜3段階
 計画素案 第2章第1節・第6章</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>4件は一体の判断である。9月中にご確認いただければ10月の3町協議に間に合う。成果品は案Cに置き換え済みであり、案A・案Bは対比の記録として残している</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>社人研推計の町別データの入手（完了）</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>計画素案 第2章第1節の町別75歳以上人口は、令和2年国勢調査の町別75歳以上を起点に3町計の後期高齢者比の推移で按分した推計値であり、公表値ではない（本文に［要確認］を付している）。国立社会保障・人口問題研究所「日本の地域別将来推計人口」（令和5年推計）の市区町村別・男女5歳階級別表を入手できれば、按分をやめて公表値に置き換えられる。受託者の作業環境は外部サイトへ接続できないため、①発注者において当該表をダウンロードしご提供いただけないか。②又は見える化システムから町別のA系列を出力いただけないか。いずれも難しい場合は、按分による推計値である旨を本文の注記として残す。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>計画素案 第2章第1節
 人口推計の補正 05シート</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>R8.8.31</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>令和8年8月31日に結果表3-1〜3-4をご提供いただき解消した。按分をやめて公表値に置き換えた結果、町別の補正方向が4件変わった（東川町の75歳以上は「上方に補正」から「補正しない」へ、美瑛町の75歳以上は「補正しない」から「上方に補正」へ）。3町計の補正係数と保険料の試算には影響しない</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="88" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>資料提供依頼No.13（施策・事業実績）の受領前に判定できる範囲を示すため、保険者機能強化推進交付金等の大項目別得点53項目を19施策に割り当て、暫定の判定を行った。結果は、取組あり・改善4施策、横ばい7施策、低下4施策、交付金では判定できない4施策（1-4虐待防止、2-4住まいと生活支援、4-2事業者の適正・円滑な運営、5-1災害・感染症対策）である。①割当ては受託者によるものであり、ご確認をお願いした